--- a/design/tables/ArtFrame.xlsx
+++ b/design/tables/ArtFrame.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtFrame" sheetId="1" r:id="R267fe136ebde44e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtFrame" sheetId="1" r:id="Ra261cf00fce9495e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1414,6 +1414,186 @@
       <x:c r="I40" s="2" t="str"/>
       <x:c r="J40" s="2" t="str"/>
     </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>staffEvolution</x:v>
+      </x:c>
+      <x:c r="C41" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D41" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E41" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F41" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G41" t="str">
+        <x:v>sprout_heavy</x:v>
+      </x:c>
+      <x:c r="H41" t="str">
+        <x:v>sprout_heavy</x:v>
+      </x:c>
+      <x:c r="I41" t="str">
+        <x:v>sprout_heavy</x:v>
+      </x:c>
+      <x:c r="J41" t="str"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>staffEvolution</x:v>
+      </x:c>
+      <x:c r="C42" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E42" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F42" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G42" t="str">
+        <x:v>sprout_burst</x:v>
+      </x:c>
+      <x:c r="H42" t="str">
+        <x:v>sprout_burst</x:v>
+      </x:c>
+      <x:c r="I42" t="str">
+        <x:v>sprout_burst</x:v>
+      </x:c>
+      <x:c r="J42" t="str"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>staffEvolution</x:v>
+      </x:c>
+      <x:c r="C43" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="D43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E43" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F43" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G43" t="str">
+        <x:v>frost_deep</x:v>
+      </x:c>
+      <x:c r="H43" t="str">
+        <x:v>frost_deep</x:v>
+      </x:c>
+      <x:c r="I43" t="str">
+        <x:v>frost_deep</x:v>
+      </x:c>
+      <x:c r="J43" t="str"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>staffEvolution</x:v>
+      </x:c>
+      <x:c r="C44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D44" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="E44" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F44" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G44" t="str">
+        <x:v>frost_dual</x:v>
+      </x:c>
+      <x:c r="H44" t="str">
+        <x:v>frost_dual</x:v>
+      </x:c>
+      <x:c r="I44" t="str">
+        <x:v>frost_dual</x:v>
+      </x:c>
+      <x:c r="J44" t="str"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>staffEvolution</x:v>
+      </x:c>
+      <x:c r="C45" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D45" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="E45" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F45" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G45" t="str">
+        <x:v>bloom_focus</x:v>
+      </x:c>
+      <x:c r="H45" t="str">
+        <x:v>bloom_focus</x:v>
+      </x:c>
+      <x:c r="I45" t="str">
+        <x:v>bloom_focus</x:v>
+      </x:c>
+      <x:c r="J45" t="str"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>staffEvolution</x:v>
+      </x:c>
+      <x:c r="C46" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="D46" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="E46" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F46" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G46" t="str">
+        <x:v>bloom_wide</x:v>
+      </x:c>
+      <x:c r="H46" t="str">
+        <x:v>bloom_wide</x:v>
+      </x:c>
+      <x:c r="I46" t="str">
+        <x:v>bloom_wide</x:v>
+      </x:c>
+      <x:c r="J46" t="str"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/ArtFrame.xlsx
+++ b/design/tables/ArtFrame.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtFrame" sheetId="1" r:id="Ra261cf00fce9495e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtFrame" sheetId="1" r:id="R84bd9abbddb949ec"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -32,8 +32,18 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF243C32"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF243C32"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -50,6 +60,11 @@
         <x:fgColor rgb="FF34564C"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -57,7 +72,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="8">
+  <x:cellXfs count="17">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -77,6 +92,29 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -452,1147 +490,1447 @@
         <x:v>scenery</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="15" hidden="0" customHeight="1">
-      <x:c r="A6" s="7" t="n">
+    <x:row r="6" ht="48" hidden="0" customHeight="1">
+      <x:c r="A6" s="14" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B6" s="2" t="str">
+      <x:c r="B6" s="15" t="str">
         <x:v>staff</x:v>
       </x:c>
-      <x:c r="C6" s="7" t="n">
+      <x:c r="C6" s="14" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D6" s="7" t="n">
+      <x:c r="D6" s="14" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E6" s="7" t="n">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="F6" s="7" t="n">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="G6" s="2" t="str">
+      <x:c r="E6" s="14" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="F6" s="14" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G6" s="15" t="str">
         <x:v>doubao</x:v>
       </x:c>
-      <x:c r="H6" s="2" t="str">
+      <x:c r="H6" s="15" t="str">
         <x:v>sprout</x:v>
       </x:c>
-      <x:c r="I6" s="2" t="str">
+      <x:c r="I6" s="15" t="str">
         <x:v>sprout</x:v>
       </x:c>
-      <x:c r="J6" s="2" t="str"/>
-    </x:row>
-    <x:row r="7" ht="15" hidden="0" customHeight="1">
-      <x:c r="A7" s="7" t="n">
+      <x:c r="J6" s="15" t="str"/>
+    </x:row>
+    <x:row r="7" ht="48" hidden="0" customHeight="1">
+      <x:c r="A7" s="14" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B7" s="2" t="str">
+      <x:c r="B7" s="15" t="str">
         <x:v>staff</x:v>
       </x:c>
-      <x:c r="C7" s="7" t="n">
+      <x:c r="C7" s="14" t="n">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="D7" s="7" t="n">
+      <x:c r="D7" s="14" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E7" s="7" t="n">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="F7" s="7" t="n">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="G7" s="2" t="str">
+      <x:c r="E7" s="14" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G7" s="15" t="str">
         <x:v>mianmian</x:v>
       </x:c>
-      <x:c r="H7" s="2" t="str">
+      <x:c r="H7" s="15" t="str">
         <x:v>frost</x:v>
       </x:c>
-      <x:c r="I7" s="2" t="str">
+      <x:c r="I7" s="15" t="str">
         <x:v>frost</x:v>
       </x:c>
-      <x:c r="J7" s="2" t="str"/>
-    </x:row>
-    <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="7" t="n">
+      <x:c r="J7" s="15" t="str"/>
+    </x:row>
+    <x:row r="8" ht="48" hidden="0" customHeight="1">
+      <x:c r="A8" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B8" s="2" t="str">
+      <x:c r="B8" s="15" t="str">
         <x:v>staff</x:v>
       </x:c>
-      <x:c r="C8" s="7" t="n">
+      <x:c r="C8" s="14" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D8" s="7" t="n">
+      <x:c r="D8" s="14" t="n">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="E8" s="7" t="n">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="F8" s="7" t="n">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="G8" s="2" t="str">
+      <x:c r="E8" s="14" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="str">
         <x:v>buding</x:v>
       </x:c>
-      <x:c r="H8" s="2" t="str">
+      <x:c r="H8" s="15" t="str">
         <x:v>bloom</x:v>
       </x:c>
-      <x:c r="I8" s="2" t="str">
+      <x:c r="I8" s="15" t="str">
         <x:v>bloom</x:v>
       </x:c>
-      <x:c r="J8" s="2" t="str"/>
-    </x:row>
-    <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="7" t="n">
+      <x:c r="J8" s="15" t="str"/>
+    </x:row>
+    <x:row r="9" ht="48" hidden="0" customHeight="1">
+      <x:c r="A9" s="14" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B9" s="2" t="str">
+      <x:c r="B9" s="15" t="str">
         <x:v>props</x:v>
       </x:c>
-      <x:c r="C9" s="7" t="n">
+      <x:c r="C9" s="14" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D9" s="7" t="n">
+      <x:c r="D9" s="14" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E9" s="7" t="n">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="F9" s="7" t="n">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="G9" s="2" t="str">
+      <x:c r="E9" s="14" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="str">
         <x:v>pad</x:v>
       </x:c>
-      <x:c r="H9" s="2" t="str"/>
-      <x:c r="I9" s="2" t="str"/>
-      <x:c r="J9" s="2" t="str"/>
-    </x:row>
-    <x:row r="10" ht="15" hidden="0" customHeight="1">
-      <x:c r="A10" s="7" t="n">
+      <x:c r="H9" s="15" t="str"/>
+      <x:c r="I9" s="15" t="str"/>
+      <x:c r="J9" s="15" t="str"/>
+    </x:row>
+    <x:row r="10" ht="48" hidden="0" customHeight="1">
+      <x:c r="A10" s="14" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B10" s="2" t="str">
+      <x:c r="B10" s="15" t="str">
         <x:v>props</x:v>
       </x:c>
-      <x:c r="C10" s="7" t="n">
+      <x:c r="C10" s="14" t="n">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="D10" s="7" t="n">
+      <x:c r="D10" s="14" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E10" s="7" t="n">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="F10" s="7" t="n">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="G10" s="2" t="str">
+      <x:c r="E10" s="14" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="str">
         <x:v>crate</x:v>
       </x:c>
-      <x:c r="H10" s="2" t="str"/>
-      <x:c r="I10" s="2" t="str"/>
-      <x:c r="J10" s="2" t="str"/>
-    </x:row>
-    <x:row r="11" ht="15" hidden="0" customHeight="1">
-      <x:c r="A11" s="7" t="n">
+      <x:c r="H10" s="15" t="str"/>
+      <x:c r="I10" s="15" t="str"/>
+      <x:c r="J10" s="15" t="str"/>
+    </x:row>
+    <x:row r="11" ht="48" hidden="0" customHeight="1">
+      <x:c r="A11" s="14" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B11" s="2" t="str">
+      <x:c r="B11" s="15" t="str">
         <x:v>props</x:v>
       </x:c>
-      <x:c r="C11" s="7" t="n">
+      <x:c r="C11" s="14" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D11" s="7" t="n">
+      <x:c r="D11" s="14" t="n">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="E11" s="7" t="n">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="F11" s="7" t="n">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="G11" s="2" t="str">
+      <x:c r="E11" s="14" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="str">
         <x:v>basket</x:v>
       </x:c>
-      <x:c r="H11" s="2" t="str"/>
-      <x:c r="I11" s="2" t="str"/>
-      <x:c r="J11" s="2" t="str"/>
-    </x:row>
-    <x:row r="12" ht="15" hidden="0" customHeight="1">
-      <x:c r="A12" s="7" t="n">
+      <x:c r="H11" s="15" t="str"/>
+      <x:c r="I11" s="15" t="str"/>
+      <x:c r="J11" s="15" t="str"/>
+    </x:row>
+    <x:row r="12" ht="48" hidden="0" customHeight="1">
+      <x:c r="A12" s="14" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B12" s="2" t="str">
+      <x:c r="B12" s="15" t="str">
         <x:v>props</x:v>
       </x:c>
-      <x:c r="C12" s="7" t="n">
+      <x:c r="C12" s="14" t="n">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="D12" s="7" t="n">
+      <x:c r="D12" s="14" t="n">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="E12" s="7" t="n">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="F12" s="7" t="n">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="G12" s="2" t="str">
+      <x:c r="E12" s="14" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="str">
         <x:v>plant</x:v>
       </x:c>
-      <x:c r="H12" s="2" t="str"/>
-      <x:c r="I12" s="2" t="str"/>
-      <x:c r="J12" s="2" t="str"/>
-    </x:row>
-    <x:row r="13" ht="15" hidden="0" customHeight="1">
-      <x:c r="A13" s="7" t="n">
+      <x:c r="H12" s="15" t="str"/>
+      <x:c r="I12" s="15" t="str"/>
+      <x:c r="J12" s="15" t="str"/>
+    </x:row>
+    <x:row r="13" ht="48" hidden="0" customHeight="1">
+      <x:c r="A13" s="14" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B13" s="2" t="str">
+      <x:c r="B13" s="15" t="str">
         <x:v>enemies</x:v>
       </x:c>
-      <x:c r="C13" s="7" t="n">
+      <x:c r="C13" s="14" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D13" s="7" t="n">
+      <x:c r="D13" s="14" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E13" s="7" t="n">
+      <x:c r="E13" s="14" t="n">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F13" s="7" t="n">
+      <x:c r="F13" s="14" t="n">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="G13" s="2" t="str">
+      <x:c r="G13" s="15" t="str">
         <x:v>enemy_normal</x:v>
       </x:c>
-      <x:c r="H13" s="2" t="str">
+      <x:c r="H13" s="15" t="str">
         <x:v>enemy_normal</x:v>
       </x:c>
-      <x:c r="I13" s="2" t="str"/>
-      <x:c r="J13" s="2" t="str"/>
-    </x:row>
-    <x:row r="14" ht="15" hidden="0" customHeight="1">
-      <x:c r="A14" s="7" t="n">
+      <x:c r="I13" s="15" t="str"/>
+      <x:c r="J13" s="15" t="str"/>
+    </x:row>
+    <x:row r="14" ht="48" hidden="0" customHeight="1">
+      <x:c r="A14" s="14" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B14" s="2" t="str">
+      <x:c r="B14" s="15" t="str">
         <x:v>enemies</x:v>
       </x:c>
-      <x:c r="C14" s="7" t="n">
+      <x:c r="C14" s="14" t="n">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="D14" s="7" t="n">
+      <x:c r="D14" s="14" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E14" s="7" t="n">
+      <x:c r="E14" s="14" t="n">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F14" s="7" t="n">
+      <x:c r="F14" s="14" t="n">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="G14" s="2" t="str">
+      <x:c r="G14" s="15" t="str">
         <x:v>enemy_swift</x:v>
       </x:c>
-      <x:c r="H14" s="2" t="str">
+      <x:c r="H14" s="15" t="str">
         <x:v>enemy_swift</x:v>
       </x:c>
-      <x:c r="I14" s="2" t="str"/>
-      <x:c r="J14" s="2" t="str"/>
-    </x:row>
-    <x:row r="15" ht="15" hidden="0" customHeight="1">
-      <x:c r="A15" s="7" t="n">
+      <x:c r="I14" s="15" t="str"/>
+      <x:c r="J14" s="15" t="str"/>
+    </x:row>
+    <x:row r="15" ht="48" hidden="0" customHeight="1">
+      <x:c r="A15" s="14" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B15" s="2" t="str">
+      <x:c r="B15" s="15" t="str">
         <x:v>enemies</x:v>
       </x:c>
-      <x:c r="C15" s="7" t="n">
+      <x:c r="C15" s="14" t="n">
         <x:v>340</x:v>
       </x:c>
-      <x:c r="D15" s="7" t="n">
+      <x:c r="D15" s="14" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E15" s="7" t="n">
+      <x:c r="E15" s="14" t="n">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F15" s="7" t="n">
+      <x:c r="F15" s="14" t="n">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="G15" s="2" t="str">
+      <x:c r="G15" s="15" t="str">
         <x:v>enemy_tank</x:v>
       </x:c>
-      <x:c r="H15" s="2" t="str">
+      <x:c r="H15" s="15" t="str">
         <x:v>enemy_tank</x:v>
       </x:c>
-      <x:c r="I15" s="2" t="str"/>
-      <x:c r="J15" s="2" t="str"/>
-    </x:row>
-    <x:row r="16" ht="15" hidden="0" customHeight="1">
-      <x:c r="A16" s="7" t="n">
+      <x:c r="I15" s="15" t="str"/>
+      <x:c r="J15" s="15" t="str"/>
+    </x:row>
+    <x:row r="16" ht="48" hidden="0" customHeight="1">
+      <x:c r="A16" s="14" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B16" s="2" t="str">
+      <x:c r="B16" s="15" t="str">
         <x:v>enemies</x:v>
       </x:c>
-      <x:c r="C16" s="7" t="n">
+      <x:c r="C16" s="14" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D16" s="7" t="n">
+      <x:c r="D16" s="14" t="n">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="E16" s="7" t="n">
+      <x:c r="E16" s="14" t="n">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F16" s="7" t="n">
+      <x:c r="F16" s="14" t="n">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="G16" s="2" t="str">
+      <x:c r="G16" s="15" t="str">
         <x:v>enemy_normal_hit</x:v>
       </x:c>
-      <x:c r="H16" s="2" t="str"/>
-      <x:c r="I16" s="2" t="str"/>
-      <x:c r="J16" s="2" t="str"/>
-    </x:row>
-    <x:row r="17" ht="15" hidden="0" customHeight="1">
-      <x:c r="A17" s="7" t="n">
+      <x:c r="H16" s="15" t="str"/>
+      <x:c r="I16" s="15" t="str"/>
+      <x:c r="J16" s="15" t="str"/>
+    </x:row>
+    <x:row r="17" ht="48" hidden="0" customHeight="1">
+      <x:c r="A17" s="14" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B17" s="2" t="str">
+      <x:c r="B17" s="15" t="str">
         <x:v>enemies</x:v>
       </x:c>
-      <x:c r="C17" s="7" t="n">
+      <x:c r="C17" s="14" t="n">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="D17" s="7" t="n">
+      <x:c r="D17" s="14" t="n">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="E17" s="7" t="n">
+      <x:c r="E17" s="14" t="n">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F17" s="7" t="n">
+      <x:c r="F17" s="14" t="n">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="G17" s="2" t="str">
+      <x:c r="G17" s="15" t="str">
         <x:v>enemy_swift_hit</x:v>
       </x:c>
-      <x:c r="H17" s="2" t="str"/>
-      <x:c r="I17" s="2" t="str"/>
-      <x:c r="J17" s="2" t="str"/>
-    </x:row>
-    <x:row r="18" ht="15" hidden="0" customHeight="1">
-      <x:c r="A18" s="7" t="n">
+      <x:c r="H17" s="15" t="str"/>
+      <x:c r="I17" s="15" t="str"/>
+      <x:c r="J17" s="15" t="str"/>
+    </x:row>
+    <x:row r="18" ht="48" hidden="0" customHeight="1">
+      <x:c r="A18" s="14" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B18" s="2" t="str">
+      <x:c r="B18" s="15" t="str">
         <x:v>enemies</x:v>
       </x:c>
-      <x:c r="C18" s="7" t="n">
+      <x:c r="C18" s="14" t="n">
         <x:v>340</x:v>
       </x:c>
-      <x:c r="D18" s="7" t="n">
+      <x:c r="D18" s="14" t="n">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="E18" s="7" t="n">
+      <x:c r="E18" s="14" t="n">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F18" s="7" t="n">
+      <x:c r="F18" s="14" t="n">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="G18" s="2" t="str">
+      <x:c r="G18" s="15" t="str">
         <x:v>enemy_tank_hit</x:v>
       </x:c>
-      <x:c r="H18" s="2" t="str"/>
-      <x:c r="I18" s="2" t="str"/>
-      <x:c r="J18" s="2" t="str"/>
-    </x:row>
-    <x:row r="19" ht="15" hidden="0" customHeight="1">
-      <x:c r="A19" s="7" t="n">
+      <x:c r="H18" s="15" t="str"/>
+      <x:c r="I18" s="15" t="str"/>
+      <x:c r="J18" s="15" t="str"/>
+    </x:row>
+    <x:row r="19" ht="48" hidden="0" customHeight="1">
+      <x:c r="A19" s="14" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B19" s="2" t="str">
+      <x:c r="B19" s="15" t="str">
         <x:v>staffNew</x:v>
       </x:c>
-      <x:c r="C19" s="7" t="n">
+      <x:c r="C19" s="14" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D19" s="7" t="n">
+      <x:c r="D19" s="14" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E19" s="7" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="F19" s="7" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="G19" s="2" t="str">
+      <x:c r="E19" s="14" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G19" s="15" t="str">
         <x:v>scope</x:v>
       </x:c>
-      <x:c r="H19" s="2" t="str">
+      <x:c r="H19" s="15" t="str">
         <x:v>scope</x:v>
       </x:c>
-      <x:c r="I19" s="2" t="str">
+      <x:c r="I19" s="15" t="str">
         <x:v>scope</x:v>
       </x:c>
-      <x:c r="J19" s="2" t="str"/>
-    </x:row>
-    <x:row r="20" ht="15" hidden="0" customHeight="1">
-      <x:c r="A20" s="7" t="n">
+      <x:c r="J19" s="15" t="str"/>
+    </x:row>
+    <x:row r="20" ht="48" hidden="0" customHeight="1">
+      <x:c r="A20" s="14" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B20" s="2" t="str">
+      <x:c r="B20" s="15" t="str">
         <x:v>staffNew</x:v>
       </x:c>
-      <x:c r="C20" s="7" t="n">
+      <x:c r="C20" s="14" t="n">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="D20" s="7" t="n">
+      <x:c r="D20" s="14" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E20" s="7" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="F20" s="7" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="G20" s="2" t="str">
+      <x:c r="E20" s="14" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G20" s="15" t="str">
         <x:v>spark</x:v>
       </x:c>
-      <x:c r="H20" s="2" t="str">
+      <x:c r="H20" s="15" t="str">
         <x:v>spark</x:v>
       </x:c>
-      <x:c r="I20" s="2" t="str">
+      <x:c r="I20" s="15" t="str">
         <x:v>spark</x:v>
       </x:c>
-      <x:c r="J20" s="2" t="str"/>
-    </x:row>
-    <x:row r="21" ht="15" hidden="0" customHeight="1">
-      <x:c r="A21" s="7" t="n">
+      <x:c r="J20" s="15" t="str"/>
+    </x:row>
+    <x:row r="21" ht="48" hidden="0" customHeight="1">
+      <x:c r="A21" s="14" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B21" s="2" t="str">
+      <x:c r="B21" s="15" t="str">
         <x:v>staffNew</x:v>
       </x:c>
-      <x:c r="C21" s="7" t="n">
+      <x:c r="C21" s="14" t="n">
         <x:v>336</x:v>
       </x:c>
-      <x:c r="D21" s="7" t="n">
+      <x:c r="D21" s="14" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E21" s="7" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="F21" s="7" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="G21" s="2" t="str">
+      <x:c r="E21" s="14" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G21" s="15" t="str">
         <x:v>ember</x:v>
       </x:c>
-      <x:c r="H21" s="2" t="str">
+      <x:c r="H21" s="15" t="str">
         <x:v>ember</x:v>
       </x:c>
-      <x:c r="I21" s="2" t="str">
+      <x:c r="I21" s="15" t="str">
         <x:v>ember</x:v>
       </x:c>
-      <x:c r="J21" s="2" t="str"/>
-    </x:row>
-    <x:row r="22" ht="15" hidden="0" customHeight="1">
-      <x:c r="A22" s="7" t="n">
+      <x:c r="J21" s="15" t="str"/>
+    </x:row>
+    <x:row r="22" ht="48" hidden="0" customHeight="1">
+      <x:c r="A22" s="14" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B22" s="2" t="str">
+      <x:c r="B22" s="15" t="str">
         <x:v>staffNew</x:v>
       </x:c>
-      <x:c r="C22" s="7" t="n">
+      <x:c r="C22" s="14" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D22" s="7" t="n">
+      <x:c r="D22" s="14" t="n">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="E22" s="7" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="F22" s="7" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="G22" s="2" t="str">
+      <x:c r="E22" s="14" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G22" s="15" t="str">
         <x:v>mint</x:v>
       </x:c>
-      <x:c r="H22" s="2" t="str">
+      <x:c r="H22" s="15" t="str">
         <x:v>mint</x:v>
       </x:c>
-      <x:c r="I22" s="2" t="str">
+      <x:c r="I22" s="15" t="str">
         <x:v>mint</x:v>
       </x:c>
-      <x:c r="J22" s="2" t="str"/>
-    </x:row>
-    <x:row r="23" ht="15" hidden="0" customHeight="1">
-      <x:c r="A23" s="7" t="n">
+      <x:c r="J22" s="15" t="str"/>
+    </x:row>
+    <x:row r="23" ht="48" hidden="0" customHeight="1">
+      <x:c r="A23" s="14" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B23" s="2" t="str">
+      <x:c r="B23" s="15" t="str">
         <x:v>staffNew</x:v>
       </x:c>
-      <x:c r="C23" s="7" t="n">
+      <x:c r="C23" s="14" t="n">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="D23" s="7" t="n">
+      <x:c r="D23" s="14" t="n">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="E23" s="7" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="F23" s="7" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="G23" s="2" t="str">
+      <x:c r="E23" s="14" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G23" s="15" t="str">
         <x:v>fan</x:v>
       </x:c>
-      <x:c r="H23" s="2" t="str">
+      <x:c r="H23" s="15" t="str">
         <x:v>fan</x:v>
       </x:c>
-      <x:c r="I23" s="2" t="str">
+      <x:c r="I23" s="15" t="str">
         <x:v>fan</x:v>
       </x:c>
-      <x:c r="J23" s="2" t="str"/>
-    </x:row>
-    <x:row r="24" ht="15" hidden="0" customHeight="1">
-      <x:c r="A24" s="7" t="n">
+      <x:c r="J23" s="15" t="str"/>
+    </x:row>
+    <x:row r="24" ht="48" hidden="0" customHeight="1">
+      <x:c r="A24" s="14" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B24" s="2" t="str">
+      <x:c r="B24" s="15" t="str">
         <x:v>enemiesNew</x:v>
       </x:c>
-      <x:c r="C24" s="7" t="n">
+      <x:c r="C24" s="14" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D24" s="7" t="n">
+      <x:c r="D24" s="14" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E24" s="7" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="F24" s="7" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="G24" s="2" t="str">
+      <x:c r="E24" s="14" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G24" s="15" t="str">
         <x:v>enemy_shield</x:v>
       </x:c>
-      <x:c r="H24" s="2" t="str">
+      <x:c r="H24" s="15" t="str">
         <x:v>enemy_shield</x:v>
       </x:c>
-      <x:c r="I24" s="2" t="str"/>
-      <x:c r="J24" s="2" t="str"/>
-    </x:row>
-    <x:row r="25" ht="15" hidden="0" customHeight="1">
-      <x:c r="A25" s="7" t="n">
+      <x:c r="I24" s="15" t="str"/>
+      <x:c r="J24" s="15" t="str"/>
+    </x:row>
+    <x:row r="25" ht="48" hidden="0" customHeight="1">
+      <x:c r="A25" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B25" s="2" t="str">
+      <x:c r="B25" s="15" t="str">
         <x:v>enemiesNew</x:v>
       </x:c>
-      <x:c r="C25" s="7" t="n">
+      <x:c r="C25" s="14" t="n">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="D25" s="7" t="n">
+      <x:c r="D25" s="14" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E25" s="7" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="F25" s="7" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="G25" s="2" t="str">
+      <x:c r="E25" s="14" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G25" s="15" t="str">
         <x:v>enemy_jelly</x:v>
       </x:c>
-      <x:c r="H25" s="2" t="str">
+      <x:c r="H25" s="15" t="str">
         <x:v>enemy_jelly</x:v>
       </x:c>
-      <x:c r="I25" s="2" t="str"/>
-      <x:c r="J25" s="2" t="str"/>
-    </x:row>
-    <x:row r="26" ht="15" hidden="0" customHeight="1">
-      <x:c r="A26" s="7" t="n">
+      <x:c r="I25" s="15" t="str"/>
+      <x:c r="J25" s="15" t="str"/>
+    </x:row>
+    <x:row r="26" ht="48" hidden="0" customHeight="1">
+      <x:c r="A26" s="14" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B26" s="2" t="str">
+      <x:c r="B26" s="15" t="str">
         <x:v>enemiesNew</x:v>
       </x:c>
-      <x:c r="C26" s="7" t="n">
+      <x:c r="C26" s="14" t="n">
         <x:v>336</x:v>
       </x:c>
-      <x:c r="D26" s="7" t="n">
+      <x:c r="D26" s="14" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E26" s="7" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="F26" s="7" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="G26" s="2" t="str">
+      <x:c r="E26" s="14" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G26" s="15" t="str">
         <x:v>enemy_runner</x:v>
       </x:c>
-      <x:c r="H26" s="2" t="str">
+      <x:c r="H26" s="15" t="str">
         <x:v>enemy_runner</x:v>
       </x:c>
-      <x:c r="I26" s="2" t="str"/>
-      <x:c r="J26" s="2" t="str"/>
-    </x:row>
-    <x:row r="27" ht="15" hidden="0" customHeight="1">
-      <x:c r="A27" s="7" t="n">
+      <x:c r="I26" s="15" t="str"/>
+      <x:c r="J26" s="15" t="str"/>
+    </x:row>
+    <x:row r="27" ht="48" hidden="0" customHeight="1">
+      <x:c r="A27" s="14" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B27" s="2" t="str">
+      <x:c r="B27" s="15" t="str">
         <x:v>enemiesNew</x:v>
       </x:c>
-      <x:c r="C27" s="7" t="n">
+      <x:c r="C27" s="14" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D27" s="7" t="n">
+      <x:c r="D27" s="14" t="n">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="E27" s="7" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="F27" s="7" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="G27" s="2" t="str">
+      <x:c r="E27" s="14" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G27" s="15" t="str">
         <x:v>enemy_postmaster</x:v>
       </x:c>
-      <x:c r="H27" s="2" t="str">
+      <x:c r="H27" s="15" t="str">
         <x:v>enemy_postmaster</x:v>
       </x:c>
-      <x:c r="I27" s="2" t="str"/>
-      <x:c r="J27" s="2" t="str"/>
-    </x:row>
-    <x:row r="28" ht="15" hidden="0" customHeight="1">
-      <x:c r="A28" s="7" t="n">
+      <x:c r="I27" s="15" t="str"/>
+      <x:c r="J27" s="15" t="str"/>
+    </x:row>
+    <x:row r="28" ht="48" hidden="0" customHeight="1">
+      <x:c r="A28" s="14" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B28" s="2" t="str">
+      <x:c r="B28" s="15" t="str">
         <x:v>enemiesNew</x:v>
       </x:c>
-      <x:c r="C28" s="7" t="n">
+      <x:c r="C28" s="14" t="n">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="D28" s="7" t="n">
+      <x:c r="D28" s="14" t="n">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="E28" s="7" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="F28" s="7" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="G28" s="2" t="str">
+      <x:c r="E28" s="14" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F28" s="14" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G28" s="15" t="str">
         <x:v>enemy_lantern</x:v>
       </x:c>
-      <x:c r="H28" s="2" t="str">
+      <x:c r="H28" s="15" t="str">
         <x:v>enemy_lantern</x:v>
       </x:c>
-      <x:c r="I28" s="2" t="str"/>
-      <x:c r="J28" s="2" t="str"/>
-    </x:row>
-    <x:row r="29" ht="15" hidden="0" customHeight="1">
-      <x:c r="A29" s="7" t="n">
+      <x:c r="I28" s="15" t="str"/>
+      <x:c r="J28" s="15" t="str"/>
+    </x:row>
+    <x:row r="29" ht="48" hidden="0" customHeight="1">
+      <x:c r="A29" s="14" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B29" s="2" t="str">
+      <x:c r="B29" s="15" t="str">
         <x:v>enemiesNew</x:v>
       </x:c>
-      <x:c r="C29" s="7" t="n">
+      <x:c r="C29" s="14" t="n">
         <x:v>336</x:v>
       </x:c>
-      <x:c r="D29" s="7" t="n">
+      <x:c r="D29" s="14" t="n">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="E29" s="7" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="F29" s="7" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="G29" s="2" t="str">
+      <x:c r="E29" s="14" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G29" s="15" t="str">
         <x:v>enemy_chef</x:v>
       </x:c>
-      <x:c r="H29" s="2" t="str">
+      <x:c r="H29" s="15" t="str">
         <x:v>enemy_chef</x:v>
       </x:c>
-      <x:c r="I29" s="2" t="str"/>
-      <x:c r="J29" s="2" t="str"/>
-    </x:row>
-    <x:row r="30" ht="15" hidden="0" customHeight="1">
-      <x:c r="A30" s="7" t="n">
+      <x:c r="I29" s="15" t="str"/>
+      <x:c r="J29" s="15" t="str"/>
+    </x:row>
+    <x:row r="30" ht="48" hidden="0" customHeight="1">
+      <x:c r="A30" s="14" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B30" s="2" t="str">
+      <x:c r="B30" s="15" t="str">
         <x:v>enemiesNew</x:v>
       </x:c>
-      <x:c r="C30" s="7" t="n">
+      <x:c r="C30" s="14" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D30" s="7" t="n">
+      <x:c r="D30" s="14" t="n">
         <x:v>336</x:v>
       </x:c>
-      <x:c r="E30" s="7" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="F30" s="7" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="G30" s="2" t="str">
+      <x:c r="E30" s="14" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F30" s="14" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G30" s="15" t="str">
         <x:v>enemy_clock</x:v>
       </x:c>
-      <x:c r="H30" s="2" t="str">
+      <x:c r="H30" s="15" t="str">
         <x:v>enemy_clock</x:v>
       </x:c>
-      <x:c r="I30" s="2" t="str"/>
-      <x:c r="J30" s="2" t="str"/>
-    </x:row>
-    <x:row r="31" ht="15" hidden="0" customHeight="1">
-      <x:c r="A31" s="7" t="n">
+      <x:c r="I30" s="15" t="str"/>
+      <x:c r="J30" s="15" t="str"/>
+    </x:row>
+    <x:row r="31" ht="48" hidden="0" customHeight="1">
+      <x:c r="A31" s="14" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B31" s="2" t="str">
+      <x:c r="B31" s="15" t="str">
         <x:v>ui</x:v>
       </x:c>
-      <x:c r="C31" s="7" t="n">
+      <x:c r="C31" s="14" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D31" s="7" t="n">
+      <x:c r="D31" s="14" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E31" s="7" t="n">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="F31" s="7" t="n">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="G31" s="2" t="str"/>
-      <x:c r="H31" s="2" t="str"/>
-      <x:c r="I31" s="2" t="str">
+      <x:c r="E31" s="14" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="F31" s="14" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G31" s="15" t="str"/>
+      <x:c r="H31" s="15" t="str"/>
+      <x:c r="I31" s="15" t="str">
         <x:v>freeze</x:v>
       </x:c>
-      <x:c r="J31" s="2" t="str"/>
-    </x:row>
-    <x:row r="32" ht="15" hidden="0" customHeight="1">
-      <x:c r="A32" s="7" t="n">
+      <x:c r="J31" s="15" t="str"/>
+    </x:row>
+    <x:row r="32" ht="48" hidden="0" customHeight="1">
+      <x:c r="A32" s="14" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B32" s="2" t="str">
+      <x:c r="B32" s="15" t="str">
         <x:v>ui</x:v>
       </x:c>
-      <x:c r="C32" s="7" t="n">
+      <x:c r="C32" s="14" t="n">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="D32" s="7" t="n">
+      <x:c r="D32" s="14" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E32" s="7" t="n">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="F32" s="7" t="n">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="G32" s="2" t="str"/>
-      <x:c r="H32" s="2" t="str"/>
-      <x:c r="I32" s="2" t="str">
+      <x:c r="E32" s="14" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="F32" s="14" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G32" s="15" t="str"/>
+      <x:c r="H32" s="15" t="str"/>
+      <x:c r="I32" s="15" t="str">
         <x:v>clear</x:v>
       </x:c>
-      <x:c r="J32" s="2" t="str"/>
-    </x:row>
-    <x:row r="33" ht="15" hidden="0" customHeight="1">
-      <x:c r="A33" s="7" t="n">
+      <x:c r="J32" s="15" t="str"/>
+    </x:row>
+    <x:row r="33" ht="48" hidden="0" customHeight="1">
+      <x:c r="A33" s="14" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B33" s="2" t="str">
+      <x:c r="B33" s="15" t="str">
         <x:v>ui</x:v>
       </x:c>
-      <x:c r="C33" s="7" t="n">
+      <x:c r="C33" s="14" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D33" s="7" t="n">
+      <x:c r="D33" s="14" t="n">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="E33" s="7" t="n">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="F33" s="7" t="n">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="G33" s="2" t="str"/>
-      <x:c r="H33" s="2" t="str"/>
-      <x:c r="I33" s="2" t="str">
+      <x:c r="E33" s="14" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="F33" s="14" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G33" s="15" t="str"/>
+      <x:c r="H33" s="15" t="str"/>
+      <x:c r="I33" s="15" t="str">
         <x:v>cash</x:v>
       </x:c>
-      <x:c r="J33" s="2" t="str"/>
-    </x:row>
-    <x:row r="34" ht="15" hidden="0" customHeight="1">
-      <x:c r="A34" s="7" t="n">
+      <x:c r="J33" s="15" t="str"/>
+    </x:row>
+    <x:row r="34" ht="48" hidden="0" customHeight="1">
+      <x:c r="A34" s="14" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B34" s="2" t="str">
+      <x:c r="B34" s="15" t="str">
         <x:v>scenery</x:v>
       </x:c>
-      <x:c r="C34" s="7" t="n">
+      <x:c r="C34" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D34" s="7" t="n">
+      <x:c r="D34" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E34" s="7" t="n">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="F34" s="7" t="n">
+      <x:c r="E34" s="14" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F34" s="14" t="n">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="G34" s="2" t="str"/>
-      <x:c r="H34" s="2" t="str"/>
-      <x:c r="I34" s="2" t="str"/>
-      <x:c r="J34" s="2" t="str">
+      <x:c r="G34" s="15" t="str"/>
+      <x:c r="H34" s="15" t="str"/>
+      <x:c r="I34" s="15" t="str"/>
+      <x:c r="J34" s="15" t="str">
         <x:v>entry</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="15" hidden="0" customHeight="1">
-      <x:c r="A35" s="7" t="n">
+    <x:row r="35" ht="48" hidden="0" customHeight="1">
+      <x:c r="A35" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B35" s="2" t="str">
+      <x:c r="B35" s="15" t="str">
         <x:v>scenery</x:v>
       </x:c>
-      <x:c r="C35" s="7" t="n">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="D35" s="7" t="n">
+      <x:c r="C35" s="14" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D35" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E35" s="7" t="n">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="F35" s="7" t="n">
+      <x:c r="E35" s="14" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F35" s="14" t="n">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="G35" s="2" t="str"/>
-      <x:c r="H35" s="2" t="str"/>
-      <x:c r="I35" s="2" t="str"/>
-      <x:c r="J35" s="2" t="str">
+      <x:c r="G35" s="15" t="str"/>
+      <x:c r="H35" s="15" t="str"/>
+      <x:c r="I35" s="15" t="str"/>
+      <x:c r="J35" s="15" t="str">
         <x:v>goal</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="15" hidden="0" customHeight="1">
-      <x:c r="A36" s="7" t="n">
+    <x:row r="36" ht="48" hidden="0" customHeight="1">
+      <x:c r="A36" s="14" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B36" s="2" t="str">
+      <x:c r="B36" s="15" t="str">
         <x:v>scenery</x:v>
       </x:c>
-      <x:c r="C36" s="7" t="n">
+      <x:c r="C36" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D36" s="7" t="n">
+      <x:c r="D36" s="14" t="n">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="E36" s="7" t="n">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="F36" s="7" t="n">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="G36" s="2" t="str"/>
-      <x:c r="H36" s="2" t="str"/>
-      <x:c r="I36" s="2" t="str"/>
-      <x:c r="J36" s="2" t="str">
+      <x:c r="E36" s="14" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="F36" s="14" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G36" s="15" t="str"/>
+      <x:c r="H36" s="15" t="str"/>
+      <x:c r="I36" s="15" t="str"/>
+      <x:c r="J36" s="15" t="str">
         <x:v>planter</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="15" hidden="0" customHeight="1">
-      <x:c r="A37" s="7" t="n">
+    <x:row r="37" ht="48" hidden="0" customHeight="1">
+      <x:c r="A37" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B37" s="2" t="str">
+      <x:c r="B37" s="15" t="str">
         <x:v>scenery</x:v>
       </x:c>
-      <x:c r="C37" s="7" t="n">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="D37" s="7" t="n">
+      <x:c r="C37" s="14" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="D37" s="14" t="n">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="E37" s="7" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="F37" s="7" t="n">
+      <x:c r="E37" s="14" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F37" s="14" t="n">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="G37" s="2" t="str"/>
-      <x:c r="H37" s="2" t="str"/>
-      <x:c r="I37" s="2" t="str"/>
-      <x:c r="J37" s="2" t="str">
+      <x:c r="G37" s="15" t="str"/>
+      <x:c r="H37" s="15" t="str"/>
+      <x:c r="I37" s="15" t="str"/>
+      <x:c r="J37" s="15" t="str">
         <x:v>tree</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="15" hidden="0" customHeight="1">
-      <x:c r="A38" s="7" t="n">
+    <x:row r="38" ht="48" hidden="0" customHeight="1">
+      <x:c r="A38" s="14" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B38" s="2" t="str">
+      <x:c r="B38" s="15" t="str">
         <x:v>scenery</x:v>
       </x:c>
-      <x:c r="C38" s="7" t="n">
+      <x:c r="C38" s="14" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D38" s="7" t="n">
+      <x:c r="D38" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E38" s="7" t="n">
+      <x:c r="E38" s="14" t="n">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="F38" s="7" t="n">
+      <x:c r="F38" s="14" t="n">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="G38" s="2" t="str"/>
-      <x:c r="H38" s="2" t="str">
+      <x:c r="G38" s="15" t="str"/>
+      <x:c r="H38" s="15" t="str">
         <x:v>entry</x:v>
       </x:c>
-      <x:c r="I38" s="2" t="str"/>
-      <x:c r="J38" s="2" t="str"/>
-    </x:row>
-    <x:row r="39" ht="15" hidden="0" customHeight="1">
-      <x:c r="A39" s="7" t="n">
+      <x:c r="I38" s="15" t="str"/>
+      <x:c r="J38" s="15" t="str"/>
+    </x:row>
+    <x:row r="39" ht="48" hidden="0" customHeight="1">
+      <x:c r="A39" s="14" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B39" s="2" t="str">
+      <x:c r="B39" s="15" t="str">
         <x:v>scenery</x:v>
       </x:c>
-      <x:c r="C39" s="7" t="n">
+      <x:c r="C39" s="14" t="n">
         <x:v>272</x:v>
       </x:c>
-      <x:c r="D39" s="7" t="n">
+      <x:c r="D39" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E39" s="7" t="n">
+      <x:c r="E39" s="14" t="n">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="F39" s="7" t="n">
+      <x:c r="F39" s="14" t="n">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="G39" s="2" t="str"/>
-      <x:c r="H39" s="2" t="str">
+      <x:c r="G39" s="15" t="str"/>
+      <x:c r="H39" s="15" t="str">
         <x:v>shop</x:v>
       </x:c>
-      <x:c r="I39" s="2" t="str"/>
-      <x:c r="J39" s="2" t="str"/>
-    </x:row>
-    <x:row r="40" ht="15" hidden="0" customHeight="1">
-      <x:c r="A40" s="7" t="n">
+      <x:c r="I39" s="15" t="str"/>
+      <x:c r="J39" s="15" t="str"/>
+    </x:row>
+    <x:row r="40" ht="48" hidden="0" customHeight="1">
+      <x:c r="A40" s="14" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B40" s="2" t="str">
+      <x:c r="B40" s="15" t="str">
         <x:v>scenery</x:v>
       </x:c>
-      <x:c r="C40" s="7" t="n">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="D40" s="7" t="n">
+      <x:c r="C40" s="14" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="D40" s="14" t="n">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="E40" s="7" t="n">
+      <x:c r="E40" s="14" t="n">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="F40" s="7" t="n">
+      <x:c r="F40" s="14" t="n">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="G40" s="2" t="str"/>
-      <x:c r="H40" s="2" t="str">
+      <x:c r="G40" s="15" t="str"/>
+      <x:c r="H40" s="15" t="str">
         <x:v>tree</x:v>
       </x:c>
-      <x:c r="I40" s="2" t="str"/>
-      <x:c r="J40" s="2" t="str"/>
-    </x:row>
-    <x:row r="41">
-      <x:c r="A41" t="n">
+      <x:c r="I40" s="15" t="str"/>
+      <x:c r="J40" s="15" t="str"/>
+    </x:row>
+    <x:row r="41" ht="48" customHeight="1">
+      <x:c r="A41" s="16" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B41" t="str">
+      <x:c r="B41" s="16" t="str">
         <x:v>staffEvolution</x:v>
       </x:c>
-      <x:c r="C41" t="n">
+      <x:c r="C41" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D41" t="n">
+      <x:c r="D41" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E41" t="n">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="F41" t="n">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="G41" t="str">
+      <x:c r="E41" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F41" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G41" s="16" t="str">
         <x:v>sprout_heavy</x:v>
       </x:c>
-      <x:c r="H41" t="str">
+      <x:c r="H41" s="16" t="str">
         <x:v>sprout_heavy</x:v>
       </x:c>
-      <x:c r="I41" t="str">
+      <x:c r="I41" s="16" t="str">
         <x:v>sprout_heavy</x:v>
       </x:c>
-      <x:c r="J41" t="str"/>
-    </x:row>
-    <x:row r="42">
-      <x:c r="A42" t="n">
+      <x:c r="J41" s="16" t="str"/>
+    </x:row>
+    <x:row r="42" ht="48" customHeight="1">
+      <x:c r="A42" s="16" t="n">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B42" t="str">
+      <x:c r="B42" s="16" t="str">
         <x:v>staffEvolution</x:v>
       </x:c>
-      <x:c r="C42" t="n">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="D42" t="n">
+      <x:c r="C42" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D42" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E42" t="n">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="F42" t="n">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="G42" t="str">
+      <x:c r="E42" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F42" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G42" s="16" t="str">
         <x:v>sprout_burst</x:v>
       </x:c>
-      <x:c r="H42" t="str">
+      <x:c r="H42" s="16" t="str">
         <x:v>sprout_burst</x:v>
       </x:c>
-      <x:c r="I42" t="str">
+      <x:c r="I42" s="16" t="str">
         <x:v>sprout_burst</x:v>
       </x:c>
-      <x:c r="J42" t="str"/>
-    </x:row>
-    <x:row r="43">
-      <x:c r="A43" t="n">
+      <x:c r="J42" s="16" t="str"/>
+    </x:row>
+    <x:row r="43" ht="48" customHeight="1">
+      <x:c r="A43" s="16" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="B43" t="str">
+      <x:c r="B43" s="16" t="str">
         <x:v>staffEvolution</x:v>
       </x:c>
-      <x:c r="C43" t="n">
+      <x:c r="C43" s="16" t="n">
         <x:v>512</x:v>
       </x:c>
-      <x:c r="D43" t="n">
+      <x:c r="D43" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E43" t="n">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="F43" t="n">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="G43" t="str">
+      <x:c r="E43" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F43" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G43" s="16" t="str">
         <x:v>frost_deep</x:v>
       </x:c>
-      <x:c r="H43" t="str">
+      <x:c r="H43" s="16" t="str">
         <x:v>frost_deep</x:v>
       </x:c>
-      <x:c r="I43" t="str">
+      <x:c r="I43" s="16" t="str">
         <x:v>frost_deep</x:v>
       </x:c>
-      <x:c r="J43" t="str"/>
-    </x:row>
-    <x:row r="44">
-      <x:c r="A44" t="n">
+      <x:c r="J43" s="16" t="str"/>
+    </x:row>
+    <x:row r="44" ht="48" customHeight="1">
+      <x:c r="A44" s="16" t="n">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B44" t="str">
+      <x:c r="B44" s="16" t="str">
         <x:v>staffEvolution</x:v>
       </x:c>
-      <x:c r="C44" t="n">
+      <x:c r="C44" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D44" t="n">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="E44" t="n">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="F44" t="n">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="G44" t="str">
+      <x:c r="D44" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="E44" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F44" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G44" s="16" t="str">
         <x:v>frost_dual</x:v>
       </x:c>
-      <x:c r="H44" t="str">
+      <x:c r="H44" s="16" t="str">
         <x:v>frost_dual</x:v>
       </x:c>
-      <x:c r="I44" t="str">
+      <x:c r="I44" s="16" t="str">
         <x:v>frost_dual</x:v>
       </x:c>
-      <x:c r="J44" t="str"/>
-    </x:row>
-    <x:row r="45">
-      <x:c r="A45" t="n">
+      <x:c r="J44" s="16" t="str"/>
+    </x:row>
+    <x:row r="45" ht="48" customHeight="1">
+      <x:c r="A45" s="16" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B45" t="str">
+      <x:c r="B45" s="16" t="str">
         <x:v>staffEvolution</x:v>
       </x:c>
-      <x:c r="C45" t="n">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="D45" t="n">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="E45" t="n">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="F45" t="n">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="G45" t="str">
+      <x:c r="C45" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D45" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="E45" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F45" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G45" s="16" t="str">
         <x:v>bloom_focus</x:v>
       </x:c>
-      <x:c r="H45" t="str">
+      <x:c r="H45" s="16" t="str">
         <x:v>bloom_focus</x:v>
       </x:c>
-      <x:c r="I45" t="str">
+      <x:c r="I45" s="16" t="str">
         <x:v>bloom_focus</x:v>
       </x:c>
-      <x:c r="J45" t="str"/>
-    </x:row>
-    <x:row r="46">
-      <x:c r="A46" t="n">
+      <x:c r="J45" s="16" t="str"/>
+    </x:row>
+    <x:row r="46" ht="48" customHeight="1">
+      <x:c r="A46" s="16" t="n">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="B46" t="str">
+      <x:c r="B46" s="16" t="str">
         <x:v>staffEvolution</x:v>
       </x:c>
-      <x:c r="C46" t="n">
+      <x:c r="C46" s="16" t="n">
         <x:v>512</x:v>
       </x:c>
-      <x:c r="D46" t="n">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="E46" t="n">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="F46" t="n">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="G46" t="str">
+      <x:c r="D46" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="E46" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F46" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G46" s="16" t="str">
         <x:v>bloom_wide</x:v>
       </x:c>
-      <x:c r="H46" t="str">
+      <x:c r="H46" s="16" t="str">
         <x:v>bloom_wide</x:v>
       </x:c>
-      <x:c r="I46" t="str">
+      <x:c r="I46" s="16" t="str">
         <x:v>bloom_wide</x:v>
       </x:c>
-      <x:c r="J46" t="str"/>
+      <x:c r="J46" s="16" t="str"/>
+    </x:row>
+    <x:row r="47" ht="48" customHeight="1">
+      <x:c r="A47" s="16" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B47" s="16" t="str">
+        <x:v>staffEvolutionExpansion</x:v>
+      </x:c>
+      <x:c r="C47" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D47" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E47" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F47" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G47" s="16" t="str">
+        <x:v>scope_precision</x:v>
+      </x:c>
+      <x:c r="H47" s="16" t="str">
+        <x:v>scope_precision</x:v>
+      </x:c>
+      <x:c r="I47" s="16" t="str">
+        <x:v>scope_precision</x:v>
+      </x:c>
+      <x:c r="J47" s="16" t="str"/>
+    </x:row>
+    <x:row r="48" ht="48" customHeight="1">
+      <x:c r="A48" s="16" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B48" s="16" t="str">
+        <x:v>staffEvolutionExpansion</x:v>
+      </x:c>
+      <x:c r="C48" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D48" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E48" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F48" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G48" s="16" t="str">
+        <x:v>scope_pierce</x:v>
+      </x:c>
+      <x:c r="H48" s="16" t="str">
+        <x:v>scope_pierce</x:v>
+      </x:c>
+      <x:c r="I48" s="16" t="str">
+        <x:v>scope_pierce</x:v>
+      </x:c>
+      <x:c r="J48" s="16" t="str"/>
+    </x:row>
+    <x:row r="49" ht="48" customHeight="1">
+      <x:c r="A49" s="16" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B49" s="16" t="str">
+        <x:v>staffEvolutionExpansion</x:v>
+      </x:c>
+      <x:c r="C49" s="16" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="D49" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E49" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F49" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G49" s="16" t="str">
+        <x:v>spark_focus</x:v>
+      </x:c>
+      <x:c r="H49" s="16" t="str">
+        <x:v>spark_focus</x:v>
+      </x:c>
+      <x:c r="I49" s="16" t="str">
+        <x:v>spark_focus</x:v>
+      </x:c>
+      <x:c r="J49" s="16" t="str"/>
+    </x:row>
+    <x:row r="50" ht="48" customHeight="1">
+      <x:c r="A50" s="16" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B50" s="16" t="str">
+        <x:v>staffEvolutionExpansion</x:v>
+      </x:c>
+      <x:c r="C50" s="16" t="n">
+        <x:v>768</x:v>
+      </x:c>
+      <x:c r="D50" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E50" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F50" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G50" s="16" t="str">
+        <x:v>spark_chain</x:v>
+      </x:c>
+      <x:c r="H50" s="16" t="str">
+        <x:v>spark_chain</x:v>
+      </x:c>
+      <x:c r="I50" s="16" t="str">
+        <x:v>spark_chain</x:v>
+      </x:c>
+      <x:c r="J50" s="16" t="str"/>
+    </x:row>
+    <x:row r="51" ht="48" customHeight="1">
+      <x:c r="A51" s="16" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B51" s="16" t="str">
+        <x:v>staffEvolutionExpansion</x:v>
+      </x:c>
+      <x:c r="C51" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D51" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="E51" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F51" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G51" s="16" t="str">
+        <x:v>ember_scorch</x:v>
+      </x:c>
+      <x:c r="H51" s="16" t="str">
+        <x:v>ember_scorch</x:v>
+      </x:c>
+      <x:c r="I51" s="16" t="str">
+        <x:v>ember_scorch</x:v>
+      </x:c>
+      <x:c r="J51" s="16" t="str"/>
+    </x:row>
+    <x:row r="52" ht="48" customHeight="1">
+      <x:c r="A52" s="16" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B52" s="16" t="str">
+        <x:v>staffEvolutionExpansion</x:v>
+      </x:c>
+      <x:c r="C52" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D52" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="E52" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F52" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G52" s="16" t="str">
+        <x:v>ember_burst</x:v>
+      </x:c>
+      <x:c r="H52" s="16" t="str">
+        <x:v>ember_burst</x:v>
+      </x:c>
+      <x:c r="I52" s="16" t="str">
+        <x:v>ember_burst</x:v>
+      </x:c>
+      <x:c r="J52" s="16" t="str"/>
+    </x:row>
+    <x:row r="53" ht="48" customHeight="1">
+      <x:c r="A53" s="16" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B53" s="16" t="str">
+        <x:v>staffEvolutionExpansion</x:v>
+      </x:c>
+      <x:c r="C53" s="16" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="D53" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="E53" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F53" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G53" s="16" t="str">
+        <x:v>mint_focus</x:v>
+      </x:c>
+      <x:c r="H53" s="16" t="str">
+        <x:v>mint_focus</x:v>
+      </x:c>
+      <x:c r="I53" s="16" t="str">
+        <x:v>mint_focus</x:v>
+      </x:c>
+      <x:c r="J53" s="16" t="str"/>
+    </x:row>
+    <x:row r="54" ht="48" customHeight="1">
+      <x:c r="A54" s="16" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B54" s="16" t="str">
+        <x:v>staffEvolutionExpansion</x:v>
+      </x:c>
+      <x:c r="C54" s="16" t="n">
+        <x:v>768</x:v>
+      </x:c>
+      <x:c r="D54" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="E54" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F54" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G54" s="16" t="str">
+        <x:v>mint_dual</x:v>
+      </x:c>
+      <x:c r="H54" s="16" t="str">
+        <x:v>mint_dual</x:v>
+      </x:c>
+      <x:c r="I54" s="16" t="str">
+        <x:v>mint_dual</x:v>
+      </x:c>
+      <x:c r="J54" s="16" t="str"/>
+    </x:row>
+    <x:row r="55" ht="48" customHeight="1">
+      <x:c r="A55" s="16" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B55" s="16" t="str">
+        <x:v>staffEvolutionExpansion</x:v>
+      </x:c>
+      <x:c r="C55" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D55" s="16" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="E55" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F55" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G55" s="16" t="str">
+        <x:v>fan_spread</x:v>
+      </x:c>
+      <x:c r="H55" s="16" t="str">
+        <x:v>fan_spread</x:v>
+      </x:c>
+      <x:c r="I55" s="16" t="str">
+        <x:v>fan_spread</x:v>
+      </x:c>
+      <x:c r="J55" s="16" t="str"/>
+    </x:row>
+    <x:row r="56" ht="48" customHeight="1">
+      <x:c r="A56" s="16" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B56" s="16" t="str">
+        <x:v>staffEvolutionExpansion</x:v>
+      </x:c>
+      <x:c r="C56" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D56" s="16" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="E56" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F56" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G56" s="16" t="str">
+        <x:v>fan_volley</x:v>
+      </x:c>
+      <x:c r="H56" s="16" t="str">
+        <x:v>fan_volley</x:v>
+      </x:c>
+      <x:c r="I56" s="16" t="str">
+        <x:v>fan_volley</x:v>
+      </x:c>
+      <x:c r="J56" s="16" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/design/tables/ArtFrame.xlsx
+++ b/design/tables/ArtFrame.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtFrame" sheetId="1" r:id="R84bd9abbddb949ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtFrame" sheetId="1" r:id="Re7d4404bddc64085"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1932,6 +1932,838 @@
       </x:c>
       <x:c r="J56" s="16" t="str"/>
     </x:row>
+    <x:row r="57">
+      <x:c r="A57" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B57" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C57" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D57" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E57" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F57" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G57" t="str"/>
+      <x:c r="H57" t="str"/>
+      <x:c r="I57" t="str">
+        <x:v>perk_S01</x:v>
+      </x:c>
+      <x:c r="J57" t="str"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B58" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C58" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D58" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E58" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F58" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G58" t="str"/>
+      <x:c r="H58" t="str"/>
+      <x:c r="I58" t="str">
+        <x:v>perk_S02</x:v>
+      </x:c>
+      <x:c r="J58" t="str"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B59" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C59" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="D59" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E59" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F59" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G59" t="str"/>
+      <x:c r="H59" t="str"/>
+      <x:c r="I59" t="str">
+        <x:v>perk_S03</x:v>
+      </x:c>
+      <x:c r="J59" t="str"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B60" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C60" t="n">
+        <x:v>768</x:v>
+      </x:c>
+      <x:c r="D60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E60" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F60" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G60" t="str"/>
+      <x:c r="H60" t="str"/>
+      <x:c r="I60" t="str">
+        <x:v>perk_S04</x:v>
+      </x:c>
+      <x:c r="J60" t="str"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B61" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C61" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D61" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="E61" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F61" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G61" t="str"/>
+      <x:c r="H61" t="str"/>
+      <x:c r="I61" t="str">
+        <x:v>perk_S05</x:v>
+      </x:c>
+      <x:c r="J61" t="str"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B62" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C62" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D62" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="E62" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F62" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G62" t="str"/>
+      <x:c r="H62" t="str"/>
+      <x:c r="I62" t="str">
+        <x:v>perk_S06</x:v>
+      </x:c>
+      <x:c r="J62" t="str"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B63" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C63" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="D63" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="E63" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F63" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G63" t="str"/>
+      <x:c r="H63" t="str"/>
+      <x:c r="I63" t="str">
+        <x:v>perk_S07</x:v>
+      </x:c>
+      <x:c r="J63" t="str"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B64" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C64" t="n">
+        <x:v>768</x:v>
+      </x:c>
+      <x:c r="D64" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="E64" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F64" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G64" t="str"/>
+      <x:c r="H64" t="str"/>
+      <x:c r="I64" t="str">
+        <x:v>perk_S08</x:v>
+      </x:c>
+      <x:c r="J64" t="str"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B65" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C65" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D65" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="E65" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F65" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G65" t="str"/>
+      <x:c r="H65" t="str"/>
+      <x:c r="I65" t="str">
+        <x:v>perk_G01</x:v>
+      </x:c>
+      <x:c r="J65" t="str"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B66" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C66" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D66" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="E66" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F66" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G66" t="str"/>
+      <x:c r="H66" t="str"/>
+      <x:c r="I66" t="str">
+        <x:v>perk_G02</x:v>
+      </x:c>
+      <x:c r="J66" t="str"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B67" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C67" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="D67" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="E67" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F67" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G67" t="str"/>
+      <x:c r="H67" t="str"/>
+      <x:c r="I67" t="str">
+        <x:v>perk_G03</x:v>
+      </x:c>
+      <x:c r="J67" t="str"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B68" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C68" t="n">
+        <x:v>768</x:v>
+      </x:c>
+      <x:c r="D68" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="E68" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F68" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G68" t="str"/>
+      <x:c r="H68" t="str"/>
+      <x:c r="I68" t="str">
+        <x:v>perk_G04</x:v>
+      </x:c>
+      <x:c r="J68" t="str"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B69" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C69" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D69" t="n">
+        <x:v>768</x:v>
+      </x:c>
+      <x:c r="E69" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F69" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G69" t="str"/>
+      <x:c r="H69" t="str"/>
+      <x:c r="I69" t="str">
+        <x:v>perk_G05</x:v>
+      </x:c>
+      <x:c r="J69" t="str"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B70" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C70" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D70" t="n">
+        <x:v>768</x:v>
+      </x:c>
+      <x:c r="E70" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F70" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G70" t="str"/>
+      <x:c r="H70" t="str"/>
+      <x:c r="I70" t="str">
+        <x:v>perk_G06</x:v>
+      </x:c>
+      <x:c r="J70" t="str"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B71" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C71" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="D71" t="n">
+        <x:v>768</x:v>
+      </x:c>
+      <x:c r="E71" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F71" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G71" t="str"/>
+      <x:c r="H71" t="str"/>
+      <x:c r="I71" t="str">
+        <x:v>perk_E01</x:v>
+      </x:c>
+      <x:c r="J71" t="str"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B72" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C72" t="n">
+        <x:v>768</x:v>
+      </x:c>
+      <x:c r="D72" t="n">
+        <x:v>768</x:v>
+      </x:c>
+      <x:c r="E72" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F72" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G72" t="str"/>
+      <x:c r="H72" t="str"/>
+      <x:c r="I72" t="str">
+        <x:v>perk_E02</x:v>
+      </x:c>
+      <x:c r="J72" t="str"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B73" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C73" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D73" t="n">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="E73" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F73" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G73" t="str"/>
+      <x:c r="H73" t="str"/>
+      <x:c r="I73" t="str">
+        <x:v>perk_E03</x:v>
+      </x:c>
+      <x:c r="J73" t="str"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B74" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C74" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D74" t="n">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="E74" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F74" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G74" t="str"/>
+      <x:c r="H74" t="str"/>
+      <x:c r="I74" t="str">
+        <x:v>perk_E04</x:v>
+      </x:c>
+      <x:c r="J74" t="str"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B75" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C75" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="D75" t="n">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="E75" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F75" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G75" t="str"/>
+      <x:c r="H75" t="str"/>
+      <x:c r="I75" t="str">
+        <x:v>perk_E05</x:v>
+      </x:c>
+      <x:c r="J75" t="str"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B76" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C76" t="n">
+        <x:v>768</x:v>
+      </x:c>
+      <x:c r="D76" t="n">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="E76" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F76" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G76" t="str"/>
+      <x:c r="H76" t="str"/>
+      <x:c r="I76" t="str">
+        <x:v>perk_E06</x:v>
+      </x:c>
+      <x:c r="J76" t="str"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B77" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D77" t="n">
+        <x:v>1280</x:v>
+      </x:c>
+      <x:c r="E77" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F77" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G77" t="str"/>
+      <x:c r="H77" t="str"/>
+      <x:c r="I77" t="str">
+        <x:v>perk_X01</x:v>
+      </x:c>
+      <x:c r="J77" t="str"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B78" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C78" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D78" t="n">
+        <x:v>1280</x:v>
+      </x:c>
+      <x:c r="E78" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F78" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G78" t="str"/>
+      <x:c r="H78" t="str"/>
+      <x:c r="I78" t="str">
+        <x:v>perk_X02</x:v>
+      </x:c>
+      <x:c r="J78" t="str"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B79" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C79" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="D79" t="n">
+        <x:v>1280</x:v>
+      </x:c>
+      <x:c r="E79" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F79" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G79" t="str"/>
+      <x:c r="H79" t="str"/>
+      <x:c r="I79" t="str">
+        <x:v>perk_X03</x:v>
+      </x:c>
+      <x:c r="J79" t="str"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B80" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C80" t="n">
+        <x:v>768</x:v>
+      </x:c>
+      <x:c r="D80" t="n">
+        <x:v>1280</x:v>
+      </x:c>
+      <x:c r="E80" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F80" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G80" t="str"/>
+      <x:c r="H80" t="str"/>
+      <x:c r="I80" t="str">
+        <x:v>perk_X04</x:v>
+      </x:c>
+      <x:c r="J80" t="str"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B81" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C81" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D81" t="n">
+        <x:v>1536</x:v>
+      </x:c>
+      <x:c r="E81" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F81" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G81" t="str"/>
+      <x:c r="H81" t="str"/>
+      <x:c r="I81" t="str">
+        <x:v>perk_X05</x:v>
+      </x:c>
+      <x:c r="J81" t="str"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B82" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C82" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D82" t="n">
+        <x:v>1536</x:v>
+      </x:c>
+      <x:c r="E82" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F82" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G82" t="str"/>
+      <x:c r="H82" t="str"/>
+      <x:c r="I82" t="str">
+        <x:v>perk_X06</x:v>
+      </x:c>
+      <x:c r="J82" t="str"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B83" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C83" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="D83" t="n">
+        <x:v>1536</x:v>
+      </x:c>
+      <x:c r="E83" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F83" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G83" t="str"/>
+      <x:c r="H83" t="str"/>
+      <x:c r="I83" t="str">
+        <x:v>perk_F01</x:v>
+      </x:c>
+      <x:c r="J83" t="str"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B84" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C84" t="n">
+        <x:v>768</x:v>
+      </x:c>
+      <x:c r="D84" t="n">
+        <x:v>1536</x:v>
+      </x:c>
+      <x:c r="E84" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F84" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G84" t="str"/>
+      <x:c r="H84" t="str"/>
+      <x:c r="I84" t="str">
+        <x:v>perk_F02</x:v>
+      </x:c>
+      <x:c r="J84" t="str"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B85" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C85" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D85" t="n">
+        <x:v>1792</x:v>
+      </x:c>
+      <x:c r="E85" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F85" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G85" t="str"/>
+      <x:c r="H85" t="str"/>
+      <x:c r="I85" t="str">
+        <x:v>perk_F03</x:v>
+      </x:c>
+      <x:c r="J85" t="str"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B86" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C86" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D86" t="n">
+        <x:v>1792</x:v>
+      </x:c>
+      <x:c r="E86" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F86" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G86" t="str"/>
+      <x:c r="H86" t="str"/>
+      <x:c r="I86" t="str">
+        <x:v>perk_F04</x:v>
+      </x:c>
+      <x:c r="J86" t="str"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B87" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C87" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="D87" t="n">
+        <x:v>1792</x:v>
+      </x:c>
+      <x:c r="E87" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F87" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G87" t="str"/>
+      <x:c r="H87" t="str"/>
+      <x:c r="I87" t="str">
+        <x:v>perk_F05</x:v>
+      </x:c>
+      <x:c r="J87" t="str"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B88" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C88" t="n">
+        <x:v>768</x:v>
+      </x:c>
+      <x:c r="D88" t="n">
+        <x:v>1792</x:v>
+      </x:c>
+      <x:c r="E88" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F88" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G88" t="str"/>
+      <x:c r="H88" t="str"/>
+      <x:c r="I88" t="str">
+        <x:v>perk_F06</x:v>
+      </x:c>
+      <x:c r="J88" t="str"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/ArtFrame.xlsx
+++ b/design/tables/ArtFrame.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtFrame" sheetId="1" r:id="Re7d4404bddc64085"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtFrame" sheetId="1" r:id="Re19a5a8bece74f3c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="5">
+  <x:fonts count="8">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -42,8 +42,23 @@
       <x:color rgb="FF243C32"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -65,6 +80,16 @@
         <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7EEE7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF33574A"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -72,7 +97,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
+  <x:cellXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -116,6 +141,22 @@
     <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -328,6 +369,7 @@
     <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="68" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="48" customHeight="1">
@@ -361,6 +403,9 @@
       <x:c r="J1" s="6" t="str">
         <x:v>场景帧键</x:v>
       </x:c>
+      <x:c r="K1" s="20" t="str">
+        <x:v>独立PNG原生切片路径</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
       <x:c r="A2" s="3" t="str">
@@ -393,6 +438,9 @@
       <x:c r="J2" s="3" t="str">
         <x:v>client</x:v>
       </x:c>
+      <x:c r="K2" s="21" t="str">
+        <x:v>client</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
       <x:c r="A3" s="3" t="str">
@@ -425,6 +473,9 @@
       <x:c r="J3" s="3" t="str">
         <x:v>string</x:v>
       </x:c>
+      <x:c r="K3" s="21" t="str">
+        <x:v>string</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="40" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -457,6 +508,9 @@
       <x:c r="J4" s="6" t="str">
         <x:v>场景帧键</x:v>
       </x:c>
+      <x:c r="K4" s="21" t="str">
+        <x:v>资源路径</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
       <x:c r="A5" s="5" t="str">
@@ -489,6 +543,9 @@
       <x:c r="J5" s="5" t="str">
         <x:v>scenery</x:v>
       </x:c>
+      <x:c r="K5" s="24" t="str">
+        <x:v>assetPath</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="48" hidden="0" customHeight="1">
       <x:c r="A6" s="14" t="n">
@@ -519,6 +576,9 @@
         <x:v>sprout</x:v>
       </x:c>
       <x:c r="J6" s="15" t="str"/>
+      <x:c r="K6" t="str">
+        <x:v>gameplay/towers/characters/sprout/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="48" hidden="0" customHeight="1">
       <x:c r="A7" s="14" t="n">
@@ -549,6 +609,9 @@
         <x:v>frost</x:v>
       </x:c>
       <x:c r="J7" s="15" t="str"/>
+      <x:c r="K7" t="str">
+        <x:v>gameplay/towers/characters/frost/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="48" hidden="0" customHeight="1">
       <x:c r="A8" s="14" t="n">
@@ -579,6 +642,9 @@
         <x:v>bloom</x:v>
       </x:c>
       <x:c r="J8" s="15" t="str"/>
+      <x:c r="K8" t="str">
+        <x:v>gameplay/towers/characters/bloom/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="48" hidden="0" customHeight="1">
       <x:c r="A9" s="14" t="n">
@@ -605,6 +671,9 @@
       <x:c r="H9" s="15" t="str"/>
       <x:c r="I9" s="15" t="str"/>
       <x:c r="J9" s="15" t="str"/>
+      <x:c r="K9" t="str">
+        <x:v>gameplay/obstacles/pad/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="48" hidden="0" customHeight="1">
       <x:c r="A10" s="14" t="n">
@@ -631,6 +700,9 @@
       <x:c r="H10" s="15" t="str"/>
       <x:c r="I10" s="15" t="str"/>
       <x:c r="J10" s="15" t="str"/>
+      <x:c r="K10" t="str">
+        <x:v>gameplay/obstacles/crate/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="48" hidden="0" customHeight="1">
       <x:c r="A11" s="14" t="n">
@@ -657,6 +729,9 @@
       <x:c r="H11" s="15" t="str"/>
       <x:c r="I11" s="15" t="str"/>
       <x:c r="J11" s="15" t="str"/>
+      <x:c r="K11" t="str">
+        <x:v>gameplay/obstacles/basket/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="48" hidden="0" customHeight="1">
       <x:c r="A12" s="14" t="n">
@@ -683,6 +758,9 @@
       <x:c r="H12" s="15" t="str"/>
       <x:c r="I12" s="15" t="str"/>
       <x:c r="J12" s="15" t="str"/>
+      <x:c r="K12" t="str">
+        <x:v>gameplay/obstacles/plant/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="48" hidden="0" customHeight="1">
       <x:c r="A13" s="14" t="n">
@@ -711,6 +789,9 @@
       </x:c>
       <x:c r="I13" s="15" t="str"/>
       <x:c r="J13" s="15" t="str"/>
+      <x:c r="K13" t="str">
+        <x:v>gameplay/enemies/characters/enemy_normal/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="48" hidden="0" customHeight="1">
       <x:c r="A14" s="14" t="n">
@@ -739,6 +820,9 @@
       </x:c>
       <x:c r="I14" s="15" t="str"/>
       <x:c r="J14" s="15" t="str"/>
+      <x:c r="K14" t="str">
+        <x:v>gameplay/enemies/characters/enemy_swift/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="48" hidden="0" customHeight="1">
       <x:c r="A15" s="14" t="n">
@@ -767,6 +851,9 @@
       </x:c>
       <x:c r="I15" s="15" t="str"/>
       <x:c r="J15" s="15" t="str"/>
+      <x:c r="K15" t="str">
+        <x:v>gameplay/enemies/characters/enemy_tank/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="48" hidden="0" customHeight="1">
       <x:c r="A16" s="14" t="n">
@@ -793,6 +880,9 @@
       <x:c r="H16" s="15" t="str"/>
       <x:c r="I16" s="15" t="str"/>
       <x:c r="J16" s="15" t="str"/>
+      <x:c r="K16" t="str">
+        <x:v>gameplay/enemies/characters/enemy_normal_hit/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="48" hidden="0" customHeight="1">
       <x:c r="A17" s="14" t="n">
@@ -819,6 +909,9 @@
       <x:c r="H17" s="15" t="str"/>
       <x:c r="I17" s="15" t="str"/>
       <x:c r="J17" s="15" t="str"/>
+      <x:c r="K17" t="str">
+        <x:v>gameplay/enemies/characters/enemy_swift_hit/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="48" hidden="0" customHeight="1">
       <x:c r="A18" s="14" t="n">
@@ -845,6 +938,9 @@
       <x:c r="H18" s="15" t="str"/>
       <x:c r="I18" s="15" t="str"/>
       <x:c r="J18" s="15" t="str"/>
+      <x:c r="K18" t="str">
+        <x:v>gameplay/enemies/characters/enemy_tank_hit/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="48" hidden="0" customHeight="1">
       <x:c r="A19" s="14" t="n">
@@ -875,6 +971,9 @@
         <x:v>scope</x:v>
       </x:c>
       <x:c r="J19" s="15" t="str"/>
+      <x:c r="K19" t="str">
+        <x:v>gameplay/towers/characters/scope/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="48" hidden="0" customHeight="1">
       <x:c r="A20" s="14" t="n">
@@ -905,6 +1004,9 @@
         <x:v>spark</x:v>
       </x:c>
       <x:c r="J20" s="15" t="str"/>
+      <x:c r="K20" t="str">
+        <x:v>gameplay/towers/characters/spark/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="48" hidden="0" customHeight="1">
       <x:c r="A21" s="14" t="n">
@@ -935,6 +1037,9 @@
         <x:v>ember</x:v>
       </x:c>
       <x:c r="J21" s="15" t="str"/>
+      <x:c r="K21" t="str">
+        <x:v>gameplay/towers/characters/ember/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="48" hidden="0" customHeight="1">
       <x:c r="A22" s="14" t="n">
@@ -965,6 +1070,9 @@
         <x:v>mint</x:v>
       </x:c>
       <x:c r="J22" s="15" t="str"/>
+      <x:c r="K22" t="str">
+        <x:v>gameplay/towers/characters/mint/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="48" hidden="0" customHeight="1">
       <x:c r="A23" s="14" t="n">
@@ -995,6 +1103,9 @@
         <x:v>fan</x:v>
       </x:c>
       <x:c r="J23" s="15" t="str"/>
+      <x:c r="K23" t="str">
+        <x:v>gameplay/towers/characters/fan/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="48" hidden="0" customHeight="1">
       <x:c r="A24" s="14" t="n">
@@ -1023,6 +1134,9 @@
       </x:c>
       <x:c r="I24" s="15" t="str"/>
       <x:c r="J24" s="15" t="str"/>
+      <x:c r="K24" t="str">
+        <x:v>gameplay/enemies/characters/enemy_shield/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="48" hidden="0" customHeight="1">
       <x:c r="A25" s="14" t="n">
@@ -1051,6 +1165,9 @@
       </x:c>
       <x:c r="I25" s="15" t="str"/>
       <x:c r="J25" s="15" t="str"/>
+      <x:c r="K25" t="str">
+        <x:v>gameplay/enemies/characters/enemy_jelly/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="48" hidden="0" customHeight="1">
       <x:c r="A26" s="14" t="n">
@@ -1079,6 +1196,9 @@
       </x:c>
       <x:c r="I26" s="15" t="str"/>
       <x:c r="J26" s="15" t="str"/>
+      <x:c r="K26" t="str">
+        <x:v>gameplay/enemies/characters/enemy_runner/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="48" hidden="0" customHeight="1">
       <x:c r="A27" s="14" t="n">
@@ -1107,6 +1227,9 @@
       </x:c>
       <x:c r="I27" s="15" t="str"/>
       <x:c r="J27" s="15" t="str"/>
+      <x:c r="K27" t="str">
+        <x:v>gameplay/enemies/characters/enemy_postmaster/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="48" hidden="0" customHeight="1">
       <x:c r="A28" s="14" t="n">
@@ -1135,6 +1258,9 @@
       </x:c>
       <x:c r="I28" s="15" t="str"/>
       <x:c r="J28" s="15" t="str"/>
+      <x:c r="K28" t="str">
+        <x:v>gameplay/enemies/characters/enemy_lantern/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="48" hidden="0" customHeight="1">
       <x:c r="A29" s="14" t="n">
@@ -1163,6 +1289,9 @@
       </x:c>
       <x:c r="I29" s="15" t="str"/>
       <x:c r="J29" s="15" t="str"/>
+      <x:c r="K29" t="str">
+        <x:v>gameplay/enemies/characters/enemy_chef/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="48" hidden="0" customHeight="1">
       <x:c r="A30" s="14" t="n">
@@ -1191,6 +1320,9 @@
       </x:c>
       <x:c r="I30" s="15" t="str"/>
       <x:c r="J30" s="15" t="str"/>
+      <x:c r="K30" t="str">
+        <x:v>gameplay/enemies/characters/enemy_clock/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="48" hidden="0" customHeight="1">
       <x:c r="A31" s="14" t="n">
@@ -1217,6 +1349,9 @@
         <x:v>freeze</x:v>
       </x:c>
       <x:c r="J31" s="15" t="str"/>
+      <x:c r="K31" t="str">
+        <x:v>ui/icons/props/freeze/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="48" hidden="0" customHeight="1">
       <x:c r="A32" s="14" t="n">
@@ -1243,6 +1378,9 @@
         <x:v>clear</x:v>
       </x:c>
       <x:c r="J32" s="15" t="str"/>
+      <x:c r="K32" t="str">
+        <x:v>ui/icons/props/clear/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="48" hidden="0" customHeight="1">
       <x:c r="A33" s="14" t="n">
@@ -1269,6 +1407,9 @@
         <x:v>cash</x:v>
       </x:c>
       <x:c r="J33" s="15" t="str"/>
+      <x:c r="K33" t="str">
+        <x:v>ui/icons/props/cash/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="48" hidden="0" customHeight="1">
       <x:c r="A34" s="14" t="n">
@@ -1295,6 +1436,9 @@
       <x:c r="J34" s="15" t="str">
         <x:v>entry</x:v>
       </x:c>
+      <x:c r="K34" t="str">
+        <x:v>gameplay/scenery/entry/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="48" hidden="0" customHeight="1">
       <x:c r="A35" s="14" t="n">
@@ -1321,6 +1465,9 @@
       <x:c r="J35" s="15" t="str">
         <x:v>goal</x:v>
       </x:c>
+      <x:c r="K35" t="str">
+        <x:v>gameplay/scenery/goal/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="48" hidden="0" customHeight="1">
       <x:c r="A36" s="14" t="n">
@@ -1347,6 +1494,9 @@
       <x:c r="J36" s="15" t="str">
         <x:v>planter</x:v>
       </x:c>
+      <x:c r="K36" t="str">
+        <x:v>gameplay/scenery/planter/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="48" hidden="0" customHeight="1">
       <x:c r="A37" s="14" t="n">
@@ -1373,6 +1523,9 @@
       <x:c r="J37" s="15" t="str">
         <x:v>tree</x:v>
       </x:c>
+      <x:c r="K37" t="str">
+        <x:v>gameplay/scenery/tree/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="48" hidden="0" customHeight="1">
       <x:c r="A38" s="14" t="n">
@@ -1399,6 +1552,9 @@
       </x:c>
       <x:c r="I38" s="15" t="str"/>
       <x:c r="J38" s="15" t="str"/>
+      <x:c r="K38" t="str">
+        <x:v>gameplay/towers/characters/entry/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="48" hidden="0" customHeight="1">
       <x:c r="A39" s="14" t="n">
@@ -1425,6 +1581,9 @@
       </x:c>
       <x:c r="I39" s="15" t="str"/>
       <x:c r="J39" s="15" t="str"/>
+      <x:c r="K39" t="str">
+        <x:v>gameplay/towers/characters/shop/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="48" hidden="0" customHeight="1">
       <x:c r="A40" s="14" t="n">
@@ -1451,6 +1610,9 @@
       </x:c>
       <x:c r="I40" s="15" t="str"/>
       <x:c r="J40" s="15" t="str"/>
+      <x:c r="K40" t="str">
+        <x:v>gameplay/towers/characters/tree/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="48" customHeight="1">
       <x:c r="A41" s="16" t="n">
@@ -1481,6 +1643,9 @@
         <x:v>sprout_heavy</x:v>
       </x:c>
       <x:c r="J41" s="16" t="str"/>
+      <x:c r="K41" t="str">
+        <x:v>gameplay/towers/characters/sprout_heavy/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="48" customHeight="1">
       <x:c r="A42" s="16" t="n">
@@ -1511,6 +1676,9 @@
         <x:v>sprout_burst</x:v>
       </x:c>
       <x:c r="J42" s="16" t="str"/>
+      <x:c r="K42" t="str">
+        <x:v>gameplay/towers/characters/sprout_burst/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="48" customHeight="1">
       <x:c r="A43" s="16" t="n">
@@ -1541,6 +1709,9 @@
         <x:v>frost_deep</x:v>
       </x:c>
       <x:c r="J43" s="16" t="str"/>
+      <x:c r="K43" t="str">
+        <x:v>gameplay/towers/characters/frost_deep/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="48" customHeight="1">
       <x:c r="A44" s="16" t="n">
@@ -1571,6 +1742,9 @@
         <x:v>frost_dual</x:v>
       </x:c>
       <x:c r="J44" s="16" t="str"/>
+      <x:c r="K44" t="str">
+        <x:v>gameplay/towers/characters/frost_dual/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="48" customHeight="1">
       <x:c r="A45" s="16" t="n">
@@ -1601,6 +1775,9 @@
         <x:v>bloom_focus</x:v>
       </x:c>
       <x:c r="J45" s="16" t="str"/>
+      <x:c r="K45" t="str">
+        <x:v>gameplay/towers/characters/bloom_focus/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="48" customHeight="1">
       <x:c r="A46" s="16" t="n">
@@ -1631,6 +1808,9 @@
         <x:v>bloom_wide</x:v>
       </x:c>
       <x:c r="J46" s="16" t="str"/>
+      <x:c r="K46" t="str">
+        <x:v>gameplay/towers/characters/bloom_wide/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" ht="48" customHeight="1">
       <x:c r="A47" s="16" t="n">
@@ -1661,6 +1841,9 @@
         <x:v>scope_precision</x:v>
       </x:c>
       <x:c r="J47" s="16" t="str"/>
+      <x:c r="K47" t="str">
+        <x:v>gameplay/towers/characters/scope_precision/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="48" customHeight="1">
       <x:c r="A48" s="16" t="n">
@@ -1691,6 +1874,9 @@
         <x:v>scope_pierce</x:v>
       </x:c>
       <x:c r="J48" s="16" t="str"/>
+      <x:c r="K48" t="str">
+        <x:v>gameplay/towers/characters/scope_pierce/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" ht="48" customHeight="1">
       <x:c r="A49" s="16" t="n">
@@ -1721,6 +1907,9 @@
         <x:v>spark_focus</x:v>
       </x:c>
       <x:c r="J49" s="16" t="str"/>
+      <x:c r="K49" t="str">
+        <x:v>gameplay/towers/characters/spark_focus/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" ht="48" customHeight="1">
       <x:c r="A50" s="16" t="n">
@@ -1751,6 +1940,9 @@
         <x:v>spark_chain</x:v>
       </x:c>
       <x:c r="J50" s="16" t="str"/>
+      <x:c r="K50" t="str">
+        <x:v>gameplay/towers/characters/spark_chain/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="48" customHeight="1">
       <x:c r="A51" s="16" t="n">
@@ -1781,6 +1973,9 @@
         <x:v>ember_scorch</x:v>
       </x:c>
       <x:c r="J51" s="16" t="str"/>
+      <x:c r="K51" t="str">
+        <x:v>gameplay/towers/characters/ember_scorch/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="48" customHeight="1">
       <x:c r="A52" s="16" t="n">
@@ -1811,6 +2006,9 @@
         <x:v>ember_burst</x:v>
       </x:c>
       <x:c r="J52" s="16" t="str"/>
+      <x:c r="K52" t="str">
+        <x:v>gameplay/towers/characters/ember_burst/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" ht="48" customHeight="1">
       <x:c r="A53" s="16" t="n">
@@ -1841,6 +2039,9 @@
         <x:v>mint_focus</x:v>
       </x:c>
       <x:c r="J53" s="16" t="str"/>
+      <x:c r="K53" t="str">
+        <x:v>gameplay/towers/characters/mint_focus/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="54" ht="48" customHeight="1">
       <x:c r="A54" s="16" t="n">
@@ -1871,6 +2072,9 @@
         <x:v>mint_dual</x:v>
       </x:c>
       <x:c r="J54" s="16" t="str"/>
+      <x:c r="K54" t="str">
+        <x:v>gameplay/towers/characters/mint_dual/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="55" ht="48" customHeight="1">
       <x:c r="A55" s="16" t="n">
@@ -1901,6 +2105,9 @@
         <x:v>fan_spread</x:v>
       </x:c>
       <x:c r="J55" s="16" t="str"/>
+      <x:c r="K55" t="str">
+        <x:v>gameplay/towers/characters/fan_spread/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" ht="48" customHeight="1">
       <x:c r="A56" s="16" t="n">
@@ -1931,6 +2138,9 @@
         <x:v>fan_volley</x:v>
       </x:c>
       <x:c r="J56" s="16" t="str"/>
+      <x:c r="K56" t="str">
+        <x:v>gameplay/towers/characters/fan_volley/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" t="n">
@@ -1957,6 +2167,9 @@
         <x:v>perk_S01</x:v>
       </x:c>
       <x:c r="J57" t="str"/>
+      <x:c r="K57" t="str">
+        <x:v>ui/icons/perks/perk_S01/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" t="n">
@@ -1983,6 +2196,9 @@
         <x:v>perk_S02</x:v>
       </x:c>
       <x:c r="J58" t="str"/>
+      <x:c r="K58" t="str">
+        <x:v>ui/icons/perks/perk_S02/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" t="n">
@@ -2009,6 +2225,9 @@
         <x:v>perk_S03</x:v>
       </x:c>
       <x:c r="J59" t="str"/>
+      <x:c r="K59" t="str">
+        <x:v>ui/icons/perks/perk_S03/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" t="n">
@@ -2035,6 +2254,9 @@
         <x:v>perk_S04</x:v>
       </x:c>
       <x:c r="J60" t="str"/>
+      <x:c r="K60" t="str">
+        <x:v>ui/icons/perks/perk_S04/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" t="n">
@@ -2061,6 +2283,9 @@
         <x:v>perk_S05</x:v>
       </x:c>
       <x:c r="J61" t="str"/>
+      <x:c r="K61" t="str">
+        <x:v>ui/icons/perks/perk_S05/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" t="n">
@@ -2087,6 +2312,9 @@
         <x:v>perk_S06</x:v>
       </x:c>
       <x:c r="J62" t="str"/>
+      <x:c r="K62" t="str">
+        <x:v>ui/icons/perks/perk_S06/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" t="n">
@@ -2113,6 +2341,9 @@
         <x:v>perk_S07</x:v>
       </x:c>
       <x:c r="J63" t="str"/>
+      <x:c r="K63" t="str">
+        <x:v>ui/icons/perks/perk_S07/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" t="n">
@@ -2139,6 +2370,9 @@
         <x:v>perk_S08</x:v>
       </x:c>
       <x:c r="J64" t="str"/>
+      <x:c r="K64" t="str">
+        <x:v>ui/icons/perks/perk_S08/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" t="n">
@@ -2165,6 +2399,9 @@
         <x:v>perk_G01</x:v>
       </x:c>
       <x:c r="J65" t="str"/>
+      <x:c r="K65" t="str">
+        <x:v>ui/icons/perks/perk_G01/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" t="n">
@@ -2191,6 +2428,9 @@
         <x:v>perk_G02</x:v>
       </x:c>
       <x:c r="J66" t="str"/>
+      <x:c r="K66" t="str">
+        <x:v>ui/icons/perks/perk_G02/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" t="n">
@@ -2217,6 +2457,9 @@
         <x:v>perk_G03</x:v>
       </x:c>
       <x:c r="J67" t="str"/>
+      <x:c r="K67" t="str">
+        <x:v>ui/icons/perks/perk_G03/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" t="n">
@@ -2243,6 +2486,9 @@
         <x:v>perk_G04</x:v>
       </x:c>
       <x:c r="J68" t="str"/>
+      <x:c r="K68" t="str">
+        <x:v>ui/icons/perks/perk_G04/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" t="n">
@@ -2269,6 +2515,9 @@
         <x:v>perk_G05</x:v>
       </x:c>
       <x:c r="J69" t="str"/>
+      <x:c r="K69" t="str">
+        <x:v>ui/icons/perks/perk_G05/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" t="n">
@@ -2295,6 +2544,9 @@
         <x:v>perk_G06</x:v>
       </x:c>
       <x:c r="J70" t="str"/>
+      <x:c r="K70" t="str">
+        <x:v>ui/icons/perks/perk_G06/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" t="n">
@@ -2321,6 +2573,9 @@
         <x:v>perk_E01</x:v>
       </x:c>
       <x:c r="J71" t="str"/>
+      <x:c r="K71" t="str">
+        <x:v>ui/icons/perks/perk_E01/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" t="n">
@@ -2347,6 +2602,9 @@
         <x:v>perk_E02</x:v>
       </x:c>
       <x:c r="J72" t="str"/>
+      <x:c r="K72" t="str">
+        <x:v>ui/icons/perks/perk_E02/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" t="n">
@@ -2373,6 +2631,9 @@
         <x:v>perk_E03</x:v>
       </x:c>
       <x:c r="J73" t="str"/>
+      <x:c r="K73" t="str">
+        <x:v>ui/icons/perks/perk_E03/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" t="n">
@@ -2399,6 +2660,9 @@
         <x:v>perk_E04</x:v>
       </x:c>
       <x:c r="J74" t="str"/>
+      <x:c r="K74" t="str">
+        <x:v>ui/icons/perks/perk_E04/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" t="n">
@@ -2425,6 +2689,9 @@
         <x:v>perk_E05</x:v>
       </x:c>
       <x:c r="J75" t="str"/>
+      <x:c r="K75" t="str">
+        <x:v>ui/icons/perks/perk_E05/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" t="n">
@@ -2451,6 +2718,9 @@
         <x:v>perk_E06</x:v>
       </x:c>
       <x:c r="J76" t="str"/>
+      <x:c r="K76" t="str">
+        <x:v>ui/icons/perks/perk_E06/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" t="n">
@@ -2477,6 +2747,9 @@
         <x:v>perk_X01</x:v>
       </x:c>
       <x:c r="J77" t="str"/>
+      <x:c r="K77" t="str">
+        <x:v>ui/icons/perks/perk_X01/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" t="n">
@@ -2503,6 +2776,9 @@
         <x:v>perk_X02</x:v>
       </x:c>
       <x:c r="J78" t="str"/>
+      <x:c r="K78" t="str">
+        <x:v>ui/icons/perks/perk_X02/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" t="n">
@@ -2529,6 +2805,9 @@
         <x:v>perk_X03</x:v>
       </x:c>
       <x:c r="J79" t="str"/>
+      <x:c r="K79" t="str">
+        <x:v>ui/icons/perks/perk_X03/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" t="n">
@@ -2555,6 +2834,9 @@
         <x:v>perk_X04</x:v>
       </x:c>
       <x:c r="J80" t="str"/>
+      <x:c r="K80" t="str">
+        <x:v>ui/icons/perks/perk_X04/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" t="n">
@@ -2581,6 +2863,9 @@
         <x:v>perk_X05</x:v>
       </x:c>
       <x:c r="J81" t="str"/>
+      <x:c r="K81" t="str">
+        <x:v>ui/icons/perks/perk_X05/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" t="n">
@@ -2607,6 +2892,9 @@
         <x:v>perk_X06</x:v>
       </x:c>
       <x:c r="J82" t="str"/>
+      <x:c r="K82" t="str">
+        <x:v>ui/icons/perks/perk_X06/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" t="n">
@@ -2633,6 +2921,9 @@
         <x:v>perk_F01</x:v>
       </x:c>
       <x:c r="J83" t="str"/>
+      <x:c r="K83" t="str">
+        <x:v>ui/icons/perks/perk_F01/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" t="n">
@@ -2659,6 +2950,9 @@
         <x:v>perk_F02</x:v>
       </x:c>
       <x:c r="J84" t="str"/>
+      <x:c r="K84" t="str">
+        <x:v>ui/icons/perks/perk_F02/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" t="n">
@@ -2685,6 +2979,9 @@
         <x:v>perk_F03</x:v>
       </x:c>
       <x:c r="J85" t="str"/>
+      <x:c r="K85" t="str">
+        <x:v>ui/icons/perks/perk_F03/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" t="n">
@@ -2711,6 +3008,9 @@
         <x:v>perk_F04</x:v>
       </x:c>
       <x:c r="J86" t="str"/>
+      <x:c r="K86" t="str">
+        <x:v>ui/icons/perks/perk_F04/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" t="n">
@@ -2737,6 +3037,9 @@
         <x:v>perk_F05</x:v>
       </x:c>
       <x:c r="J87" t="str"/>
+      <x:c r="K87" t="str">
+        <x:v>ui/icons/perks/perk_F05/spriteFrame</x:v>
+      </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" t="n">
@@ -2763,6 +3066,9 @@
         <x:v>perk_F06</x:v>
       </x:c>
       <x:c r="J88" t="str"/>
+      <x:c r="K88" t="str">
+        <x:v>ui/icons/perks/perk_F06/spriteFrame</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/design/tables/ArtFrame.xlsx
+++ b/design/tables/ArtFrame.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtFrame" sheetId="1" r:id="Re19a5a8bece74f3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtFrame" sheetId="1" r:id="R298574afe9bc405b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -406,6 +406,12 @@
       <x:c r="K1" s="20" t="str">
         <x:v>独立PNG原生切片路径</x:v>
       </x:c>
+      <x:c r="L1" t="str">
+        <x:v>独立PNG画布宽</x:v>
+      </x:c>
+      <x:c r="M1" t="str">
+        <x:v>独立PNG画布高</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
       <x:c r="A2" s="3" t="str">
@@ -441,6 +447,12 @@
       <x:c r="K2" s="21" t="str">
         <x:v>client</x:v>
       </x:c>
+      <x:c r="L2" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="M2" t="str">
+        <x:v>client</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
       <x:c r="A3" s="3" t="str">
@@ -476,6 +488,12 @@
       <x:c r="K3" s="21" t="str">
         <x:v>string</x:v>
       </x:c>
+      <x:c r="L3" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="M3" t="str">
+        <x:v>int</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="40" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -511,6 +529,12 @@
       <x:c r="K4" s="21" t="str">
         <x:v>资源路径</x:v>
       </x:c>
+      <x:c r="L4" t="str">
+        <x:v>独立PNG画布宽</x:v>
+      </x:c>
+      <x:c r="M4" t="str">
+        <x:v>独立PNG画布高</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
       <x:c r="A5" s="5" t="str">
@@ -546,6 +570,12 @@
       <x:c r="K5" s="24" t="str">
         <x:v>assetPath</x:v>
       </x:c>
+      <x:c r="L5" t="str">
+        <x:v>canvasWidth</x:v>
+      </x:c>
+      <x:c r="M5" t="str">
+        <x:v>canvasHeight</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="48" hidden="0" customHeight="1">
       <x:c r="A6" s="14" t="n">
@@ -579,6 +609,12 @@
       <x:c r="K6" t="str">
         <x:v>gameplay/towers/characters/sprout/spriteFrame</x:v>
       </x:c>
+      <x:c r="L6" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M6" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="48" hidden="0" customHeight="1">
       <x:c r="A7" s="14" t="n">
@@ -612,6 +648,12 @@
       <x:c r="K7" t="str">
         <x:v>gameplay/towers/characters/frost/spriteFrame</x:v>
       </x:c>
+      <x:c r="L7" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M7" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="48" hidden="0" customHeight="1">
       <x:c r="A8" s="14" t="n">
@@ -644,6 +686,12 @@
       <x:c r="J8" s="15" t="str"/>
       <x:c r="K8" t="str">
         <x:v>gameplay/towers/characters/bloom/spriteFrame</x:v>
+      </x:c>
+      <x:c r="L8" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M8" t="n">
+        <x:v>256</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="48" hidden="0" customHeight="1">
@@ -674,6 +722,12 @@
       <x:c r="K9" t="str">
         <x:v>gameplay/obstacles/pad/spriteFrame</x:v>
       </x:c>
+      <x:c r="L9" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M9" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="48" hidden="0" customHeight="1">
       <x:c r="A10" s="14" t="n">
@@ -703,6 +757,12 @@
       <x:c r="K10" t="str">
         <x:v>gameplay/obstacles/crate/spriteFrame</x:v>
       </x:c>
+      <x:c r="L10" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M10" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="48" hidden="0" customHeight="1">
       <x:c r="A11" s="14" t="n">
@@ -732,6 +792,12 @@
       <x:c r="K11" t="str">
         <x:v>gameplay/obstacles/basket/spriteFrame</x:v>
       </x:c>
+      <x:c r="L11" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M11" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="48" hidden="0" customHeight="1">
       <x:c r="A12" s="14" t="n">
@@ -761,6 +827,12 @@
       <x:c r="K12" t="str">
         <x:v>gameplay/obstacles/plant/spriteFrame</x:v>
       </x:c>
+      <x:c r="L12" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M12" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="48" hidden="0" customHeight="1">
       <x:c r="A13" s="14" t="n">
@@ -792,6 +864,12 @@
       <x:c r="K13" t="str">
         <x:v>gameplay/enemies/characters/enemy_normal/spriteFrame</x:v>
       </x:c>
+      <x:c r="L13" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M13" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="48" hidden="0" customHeight="1">
       <x:c r="A14" s="14" t="n">
@@ -823,6 +901,12 @@
       <x:c r="K14" t="str">
         <x:v>gameplay/enemies/characters/enemy_swift/spriteFrame</x:v>
       </x:c>
+      <x:c r="L14" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M14" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="48" hidden="0" customHeight="1">
       <x:c r="A15" s="14" t="n">
@@ -853,6 +937,12 @@
       <x:c r="J15" s="15" t="str"/>
       <x:c r="K15" t="str">
         <x:v>gameplay/enemies/characters/enemy_tank/spriteFrame</x:v>
+      </x:c>
+      <x:c r="L15" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M15" t="n">
+        <x:v>256</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="48" hidden="0" customHeight="1">
@@ -883,6 +973,12 @@
       <x:c r="K16" t="str">
         <x:v>gameplay/enemies/characters/enemy_normal_hit/spriteFrame</x:v>
       </x:c>
+      <x:c r="L16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M16" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="48" hidden="0" customHeight="1">
       <x:c r="A17" s="14" t="n">
@@ -912,6 +1008,12 @@
       <x:c r="K17" t="str">
         <x:v>gameplay/enemies/characters/enemy_swift_hit/spriteFrame</x:v>
       </x:c>
+      <x:c r="L17" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M17" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="48" hidden="0" customHeight="1">
       <x:c r="A18" s="14" t="n">
@@ -941,6 +1043,12 @@
       <x:c r="K18" t="str">
         <x:v>gameplay/enemies/characters/enemy_tank_hit/spriteFrame</x:v>
       </x:c>
+      <x:c r="L18" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M18" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="48" hidden="0" customHeight="1">
       <x:c r="A19" s="14" t="n">
@@ -974,6 +1082,12 @@
       <x:c r="K19" t="str">
         <x:v>gameplay/towers/characters/scope/spriteFrame</x:v>
       </x:c>
+      <x:c r="L19" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M19" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="48" hidden="0" customHeight="1">
       <x:c r="A20" s="14" t="n">
@@ -1007,6 +1121,12 @@
       <x:c r="K20" t="str">
         <x:v>gameplay/towers/characters/spark/spriteFrame</x:v>
       </x:c>
+      <x:c r="L20" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M20" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="48" hidden="0" customHeight="1">
       <x:c r="A21" s="14" t="n">
@@ -1040,6 +1160,12 @@
       <x:c r="K21" t="str">
         <x:v>gameplay/towers/characters/ember/spriteFrame</x:v>
       </x:c>
+      <x:c r="L21" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M21" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="48" hidden="0" customHeight="1">
       <x:c r="A22" s="14" t="n">
@@ -1073,6 +1199,12 @@
       <x:c r="K22" t="str">
         <x:v>gameplay/towers/characters/mint/spriteFrame</x:v>
       </x:c>
+      <x:c r="L22" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M22" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="48" hidden="0" customHeight="1">
       <x:c r="A23" s="14" t="n">
@@ -1105,6 +1237,12 @@
       <x:c r="J23" s="15" t="str"/>
       <x:c r="K23" t="str">
         <x:v>gameplay/towers/characters/fan/spriteFrame</x:v>
+      </x:c>
+      <x:c r="L23" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M23" t="n">
+        <x:v>256</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="48" hidden="0" customHeight="1">
@@ -1137,6 +1275,12 @@
       <x:c r="K24" t="str">
         <x:v>gameplay/enemies/characters/enemy_shield/spriteFrame</x:v>
       </x:c>
+      <x:c r="L24" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M24" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="48" hidden="0" customHeight="1">
       <x:c r="A25" s="14" t="n">
@@ -1168,6 +1312,12 @@
       <x:c r="K25" t="str">
         <x:v>gameplay/enemies/characters/enemy_jelly/spriteFrame</x:v>
       </x:c>
+      <x:c r="L25" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M25" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="48" hidden="0" customHeight="1">
       <x:c r="A26" s="14" t="n">
@@ -1199,6 +1349,12 @@
       <x:c r="K26" t="str">
         <x:v>gameplay/enemies/characters/enemy_runner/spriteFrame</x:v>
       </x:c>
+      <x:c r="L26" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M26" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="48" hidden="0" customHeight="1">
       <x:c r="A27" s="14" t="n">
@@ -1230,6 +1386,12 @@
       <x:c r="K27" t="str">
         <x:v>gameplay/enemies/characters/enemy_postmaster/spriteFrame</x:v>
       </x:c>
+      <x:c r="L27" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M27" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="48" hidden="0" customHeight="1">
       <x:c r="A28" s="14" t="n">
@@ -1261,6 +1423,12 @@
       <x:c r="K28" t="str">
         <x:v>gameplay/enemies/characters/enemy_lantern/spriteFrame</x:v>
       </x:c>
+      <x:c r="L28" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M28" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="48" hidden="0" customHeight="1">
       <x:c r="A29" s="14" t="n">
@@ -1292,6 +1460,12 @@
       <x:c r="K29" t="str">
         <x:v>gameplay/enemies/characters/enemy_chef/spriteFrame</x:v>
       </x:c>
+      <x:c r="L29" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M29" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="48" hidden="0" customHeight="1">
       <x:c r="A30" s="14" t="n">
@@ -1323,6 +1497,12 @@
       <x:c r="K30" t="str">
         <x:v>gameplay/enemies/characters/enemy_clock/spriteFrame</x:v>
       </x:c>
+      <x:c r="L30" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M30" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="48" hidden="0" customHeight="1">
       <x:c r="A31" s="14" t="n">
@@ -1352,6 +1532,12 @@
       <x:c r="K31" t="str">
         <x:v>ui/icons/props/freeze/spriteFrame</x:v>
       </x:c>
+      <x:c r="L31" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M31" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="48" hidden="0" customHeight="1">
       <x:c r="A32" s="14" t="n">
@@ -1381,6 +1567,12 @@
       <x:c r="K32" t="str">
         <x:v>ui/icons/props/clear/spriteFrame</x:v>
       </x:c>
+      <x:c r="L32" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M32" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="48" hidden="0" customHeight="1">
       <x:c r="A33" s="14" t="n">
@@ -1409,6 +1601,12 @@
       <x:c r="J33" s="15" t="str"/>
       <x:c r="K33" t="str">
         <x:v>ui/icons/props/cash/spriteFrame</x:v>
+      </x:c>
+      <x:c r="L33" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M33" t="n">
+        <x:v>256</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="48" hidden="0" customHeight="1">
@@ -1439,6 +1637,12 @@
       <x:c r="K34" t="str">
         <x:v>gameplay/scenery/entry/spriteFrame</x:v>
       </x:c>
+      <x:c r="L34" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M34" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="48" hidden="0" customHeight="1">
       <x:c r="A35" s="14" t="n">
@@ -1468,6 +1672,12 @@
       <x:c r="K35" t="str">
         <x:v>gameplay/scenery/goal/spriteFrame</x:v>
       </x:c>
+      <x:c r="L35" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M35" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="48" hidden="0" customHeight="1">
       <x:c r="A36" s="14" t="n">
@@ -1497,6 +1707,12 @@
       <x:c r="K36" t="str">
         <x:v>gameplay/scenery/planter/spriteFrame</x:v>
       </x:c>
+      <x:c r="L36" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M36" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="48" hidden="0" customHeight="1">
       <x:c r="A37" s="14" t="n">
@@ -1526,6 +1742,12 @@
       <x:c r="K37" t="str">
         <x:v>gameplay/scenery/tree/spriteFrame</x:v>
       </x:c>
+      <x:c r="L37" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M37" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="48" hidden="0" customHeight="1">
       <x:c r="A38" s="14" t="n">
@@ -1555,6 +1777,12 @@
       <x:c r="K38" t="str">
         <x:v>gameplay/towers/characters/entry/spriteFrame</x:v>
       </x:c>
+      <x:c r="L38" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M38" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="48" hidden="0" customHeight="1">
       <x:c r="A39" s="14" t="n">
@@ -1584,6 +1812,12 @@
       <x:c r="K39" t="str">
         <x:v>gameplay/towers/characters/shop/spriteFrame</x:v>
       </x:c>
+      <x:c r="L39" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M39" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="48" hidden="0" customHeight="1">
       <x:c r="A40" s="14" t="n">
@@ -1613,6 +1847,12 @@
       <x:c r="K40" t="str">
         <x:v>gameplay/towers/characters/tree/spriteFrame</x:v>
       </x:c>
+      <x:c r="L40" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M40" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="48" customHeight="1">
       <x:c r="A41" s="16" t="n">
@@ -1646,6 +1886,12 @@
       <x:c r="K41" t="str">
         <x:v>gameplay/towers/characters/sprout_heavy/spriteFrame</x:v>
       </x:c>
+      <x:c r="L41" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M41" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="48" customHeight="1">
       <x:c r="A42" s="16" t="n">
@@ -1679,6 +1925,12 @@
       <x:c r="K42" t="str">
         <x:v>gameplay/towers/characters/sprout_burst/spriteFrame</x:v>
       </x:c>
+      <x:c r="L42" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M42" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="48" customHeight="1">
       <x:c r="A43" s="16" t="n">
@@ -1712,6 +1964,12 @@
       <x:c r="K43" t="str">
         <x:v>gameplay/towers/characters/frost_deep/spriteFrame</x:v>
       </x:c>
+      <x:c r="L43" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M43" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="48" customHeight="1">
       <x:c r="A44" s="16" t="n">
@@ -1745,6 +2003,12 @@
       <x:c r="K44" t="str">
         <x:v>gameplay/towers/characters/frost_dual/spriteFrame</x:v>
       </x:c>
+      <x:c r="L44" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M44" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="48" customHeight="1">
       <x:c r="A45" s="16" t="n">
@@ -1778,6 +2042,12 @@
       <x:c r="K45" t="str">
         <x:v>gameplay/towers/characters/bloom_focus/spriteFrame</x:v>
       </x:c>
+      <x:c r="L45" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M45" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="48" customHeight="1">
       <x:c r="A46" s="16" t="n">
@@ -1811,6 +2081,12 @@
       <x:c r="K46" t="str">
         <x:v>gameplay/towers/characters/bloom_wide/spriteFrame</x:v>
       </x:c>
+      <x:c r="L46" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M46" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" ht="48" customHeight="1">
       <x:c r="A47" s="16" t="n">
@@ -1844,6 +2120,12 @@
       <x:c r="K47" t="str">
         <x:v>gameplay/towers/characters/scope_precision/spriteFrame</x:v>
       </x:c>
+      <x:c r="L47" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M47" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="48" customHeight="1">
       <x:c r="A48" s="16" t="n">
@@ -1877,6 +2159,12 @@
       <x:c r="K48" t="str">
         <x:v>gameplay/towers/characters/scope_pierce/spriteFrame</x:v>
       </x:c>
+      <x:c r="L48" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M48" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" ht="48" customHeight="1">
       <x:c r="A49" s="16" t="n">
@@ -1910,6 +2198,12 @@
       <x:c r="K49" t="str">
         <x:v>gameplay/towers/characters/spark_focus/spriteFrame</x:v>
       </x:c>
+      <x:c r="L49" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M49" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" ht="48" customHeight="1">
       <x:c r="A50" s="16" t="n">
@@ -1943,6 +2237,12 @@
       <x:c r="K50" t="str">
         <x:v>gameplay/towers/characters/spark_chain/spriteFrame</x:v>
       </x:c>
+      <x:c r="L50" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M50" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="48" customHeight="1">
       <x:c r="A51" s="16" t="n">
@@ -1976,6 +2276,12 @@
       <x:c r="K51" t="str">
         <x:v>gameplay/towers/characters/ember_scorch/spriteFrame</x:v>
       </x:c>
+      <x:c r="L51" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M51" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="48" customHeight="1">
       <x:c r="A52" s="16" t="n">
@@ -2009,6 +2315,12 @@
       <x:c r="K52" t="str">
         <x:v>gameplay/towers/characters/ember_burst/spriteFrame</x:v>
       </x:c>
+      <x:c r="L52" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M52" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" ht="48" customHeight="1">
       <x:c r="A53" s="16" t="n">
@@ -2042,6 +2354,12 @@
       <x:c r="K53" t="str">
         <x:v>gameplay/towers/characters/mint_focus/spriteFrame</x:v>
       </x:c>
+      <x:c r="L53" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M53" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="54" ht="48" customHeight="1">
       <x:c r="A54" s="16" t="n">
@@ -2075,6 +2393,12 @@
       <x:c r="K54" t="str">
         <x:v>gameplay/towers/characters/mint_dual/spriteFrame</x:v>
       </x:c>
+      <x:c r="L54" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M54" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="55" ht="48" customHeight="1">
       <x:c r="A55" s="16" t="n">
@@ -2108,6 +2432,12 @@
       <x:c r="K55" t="str">
         <x:v>gameplay/towers/characters/fan_spread/spriteFrame</x:v>
       </x:c>
+      <x:c r="L55" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M55" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" ht="48" customHeight="1">
       <x:c r="A56" s="16" t="n">
@@ -2140,6 +2470,12 @@
       <x:c r="J56" s="16" t="str"/>
       <x:c r="K56" t="str">
         <x:v>gameplay/towers/characters/fan_volley/spriteFrame</x:v>
+      </x:c>
+      <x:c r="L56" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M56" t="n">
+        <x:v>256</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -2170,6 +2506,12 @@
       <x:c r="K57" t="str">
         <x:v>ui/icons/perks/perk_S01/spriteFrame</x:v>
       </x:c>
+      <x:c r="L57" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M57" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" t="n">
@@ -2199,6 +2541,12 @@
       <x:c r="K58" t="str">
         <x:v>ui/icons/perks/perk_S02/spriteFrame</x:v>
       </x:c>
+      <x:c r="L58" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M58" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" t="n">
@@ -2228,6 +2576,12 @@
       <x:c r="K59" t="str">
         <x:v>ui/icons/perks/perk_S03/spriteFrame</x:v>
       </x:c>
+      <x:c r="L59" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M59" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" t="n">
@@ -2257,6 +2611,12 @@
       <x:c r="K60" t="str">
         <x:v>ui/icons/perks/perk_S04/spriteFrame</x:v>
       </x:c>
+      <x:c r="L60" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M60" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" t="n">
@@ -2286,6 +2646,12 @@
       <x:c r="K61" t="str">
         <x:v>ui/icons/perks/perk_S05/spriteFrame</x:v>
       </x:c>
+      <x:c r="L61" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M61" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" t="n">
@@ -2315,6 +2681,12 @@
       <x:c r="K62" t="str">
         <x:v>ui/icons/perks/perk_S06/spriteFrame</x:v>
       </x:c>
+      <x:c r="L62" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M62" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" t="n">
@@ -2344,6 +2716,12 @@
       <x:c r="K63" t="str">
         <x:v>ui/icons/perks/perk_S07/spriteFrame</x:v>
       </x:c>
+      <x:c r="L63" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M63" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" t="n">
@@ -2373,6 +2751,12 @@
       <x:c r="K64" t="str">
         <x:v>ui/icons/perks/perk_S08/spriteFrame</x:v>
       </x:c>
+      <x:c r="L64" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M64" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" t="n">
@@ -2402,6 +2786,12 @@
       <x:c r="K65" t="str">
         <x:v>ui/icons/perks/perk_G01/spriteFrame</x:v>
       </x:c>
+      <x:c r="L65" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M65" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" t="n">
@@ -2431,6 +2821,12 @@
       <x:c r="K66" t="str">
         <x:v>ui/icons/perks/perk_G02/spriteFrame</x:v>
       </x:c>
+      <x:c r="L66" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M66" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" t="n">
@@ -2460,6 +2856,12 @@
       <x:c r="K67" t="str">
         <x:v>ui/icons/perks/perk_G03/spriteFrame</x:v>
       </x:c>
+      <x:c r="L67" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M67" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" t="n">
@@ -2489,6 +2891,12 @@
       <x:c r="K68" t="str">
         <x:v>ui/icons/perks/perk_G04/spriteFrame</x:v>
       </x:c>
+      <x:c r="L68" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M68" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" t="n">
@@ -2518,6 +2926,12 @@
       <x:c r="K69" t="str">
         <x:v>ui/icons/perks/perk_G05/spriteFrame</x:v>
       </x:c>
+      <x:c r="L69" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M69" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" t="n">
@@ -2547,6 +2961,12 @@
       <x:c r="K70" t="str">
         <x:v>ui/icons/perks/perk_G06/spriteFrame</x:v>
       </x:c>
+      <x:c r="L70" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M70" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" t="n">
@@ -2576,6 +2996,12 @@
       <x:c r="K71" t="str">
         <x:v>ui/icons/perks/perk_E01/spriteFrame</x:v>
       </x:c>
+      <x:c r="L71" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M71" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" t="n">
@@ -2605,6 +3031,12 @@
       <x:c r="K72" t="str">
         <x:v>ui/icons/perks/perk_E02/spriteFrame</x:v>
       </x:c>
+      <x:c r="L72" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M72" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" t="n">
@@ -2634,6 +3066,12 @@
       <x:c r="K73" t="str">
         <x:v>ui/icons/perks/perk_E03/spriteFrame</x:v>
       </x:c>
+      <x:c r="L73" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M73" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" t="n">
@@ -2663,6 +3101,12 @@
       <x:c r="K74" t="str">
         <x:v>ui/icons/perks/perk_E04/spriteFrame</x:v>
       </x:c>
+      <x:c r="L74" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M74" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" t="n">
@@ -2692,6 +3136,12 @@
       <x:c r="K75" t="str">
         <x:v>ui/icons/perks/perk_E05/spriteFrame</x:v>
       </x:c>
+      <x:c r="L75" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M75" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" t="n">
@@ -2721,6 +3171,12 @@
       <x:c r="K76" t="str">
         <x:v>ui/icons/perks/perk_E06/spriteFrame</x:v>
       </x:c>
+      <x:c r="L76" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M76" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" t="n">
@@ -2750,6 +3206,12 @@
       <x:c r="K77" t="str">
         <x:v>ui/icons/perks/perk_X01/spriteFrame</x:v>
       </x:c>
+      <x:c r="L77" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M77" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" t="n">
@@ -2779,6 +3241,12 @@
       <x:c r="K78" t="str">
         <x:v>ui/icons/perks/perk_X02/spriteFrame</x:v>
       </x:c>
+      <x:c r="L78" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M78" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" t="n">
@@ -2808,6 +3276,12 @@
       <x:c r="K79" t="str">
         <x:v>ui/icons/perks/perk_X03/spriteFrame</x:v>
       </x:c>
+      <x:c r="L79" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M79" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" t="n">
@@ -2837,6 +3311,12 @@
       <x:c r="K80" t="str">
         <x:v>ui/icons/perks/perk_X04/spriteFrame</x:v>
       </x:c>
+      <x:c r="L80" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M80" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" t="n">
@@ -2866,6 +3346,12 @@
       <x:c r="K81" t="str">
         <x:v>ui/icons/perks/perk_X05/spriteFrame</x:v>
       </x:c>
+      <x:c r="L81" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M81" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" t="n">
@@ -2895,6 +3381,12 @@
       <x:c r="K82" t="str">
         <x:v>ui/icons/perks/perk_X06/spriteFrame</x:v>
       </x:c>
+      <x:c r="L82" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M82" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" t="n">
@@ -2924,6 +3416,12 @@
       <x:c r="K83" t="str">
         <x:v>ui/icons/perks/perk_F01/spriteFrame</x:v>
       </x:c>
+      <x:c r="L83" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M83" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" t="n">
@@ -2953,6 +3451,12 @@
       <x:c r="K84" t="str">
         <x:v>ui/icons/perks/perk_F02/spriteFrame</x:v>
       </x:c>
+      <x:c r="L84" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M84" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" t="n">
@@ -2982,6 +3486,12 @@
       <x:c r="K85" t="str">
         <x:v>ui/icons/perks/perk_F03/spriteFrame</x:v>
       </x:c>
+      <x:c r="L85" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M85" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" t="n">
@@ -3011,6 +3521,12 @@
       <x:c r="K86" t="str">
         <x:v>ui/icons/perks/perk_F04/spriteFrame</x:v>
       </x:c>
+      <x:c r="L86" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M86" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" t="n">
@@ -3040,6 +3556,12 @@
       <x:c r="K87" t="str">
         <x:v>ui/icons/perks/perk_F05/spriteFrame</x:v>
       </x:c>
+      <x:c r="L87" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M87" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" t="n">
@@ -3069,6 +3591,12 @@
       <x:c r="K88" t="str">
         <x:v>ui/icons/perks/perk_F06/spriteFrame</x:v>
       </x:c>
+      <x:c r="L88" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M88" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/design/tables/ArtFrame.xlsx
+++ b/design/tables/ArtFrame.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtFrame" sheetId="1" r:id="R88b758cc32b44b16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtFrame" sheetId="1" r:id="R7a00b13d683b4237"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2163,6 +2163,198 @@
         <x:v>256</x:v>
       </x:c>
     </x:row>
+    <x:row r="89">
+      <x:c r="A89" t="n">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B89" t="str">
+        <x:v>sprout_level2</x:v>
+      </x:c>
+      <x:c r="C89" t="str">
+        <x:v>sprout_level2</x:v>
+      </x:c>
+      <x:c r="D89" t="str">
+        <x:v>sprout_level2</x:v>
+      </x:c>
+      <x:c r="E89" t="str"/>
+      <x:c r="F89" t="str">
+        <x:v>gameplay/towers/characters/sprout_level2/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G89" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H89" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B90" t="str">
+        <x:v>frost_level2</x:v>
+      </x:c>
+      <x:c r="C90" t="str">
+        <x:v>frost_level2</x:v>
+      </x:c>
+      <x:c r="D90" t="str">
+        <x:v>frost_level2</x:v>
+      </x:c>
+      <x:c r="E90" t="str"/>
+      <x:c r="F90" t="str">
+        <x:v>gameplay/towers/characters/frost_level2/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G90" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H90" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" t="n">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B91" t="str">
+        <x:v>bloom_level2</x:v>
+      </x:c>
+      <x:c r="C91" t="str">
+        <x:v>bloom_level2</x:v>
+      </x:c>
+      <x:c r="D91" t="str">
+        <x:v>bloom_level2</x:v>
+      </x:c>
+      <x:c r="E91" t="str"/>
+      <x:c r="F91" t="str">
+        <x:v>gameplay/towers/characters/bloom_level2/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G91" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H91" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" t="n">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B92" t="str">
+        <x:v>scope_level2</x:v>
+      </x:c>
+      <x:c r="C92" t="str">
+        <x:v>scope_level2</x:v>
+      </x:c>
+      <x:c r="D92" t="str">
+        <x:v>scope_level2</x:v>
+      </x:c>
+      <x:c r="E92" t="str"/>
+      <x:c r="F92" t="str">
+        <x:v>gameplay/towers/characters/scope_level2/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G92" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H92" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B93" t="str">
+        <x:v>spark_level2</x:v>
+      </x:c>
+      <x:c r="C93" t="str">
+        <x:v>spark_level2</x:v>
+      </x:c>
+      <x:c r="D93" t="str">
+        <x:v>spark_level2</x:v>
+      </x:c>
+      <x:c r="E93" t="str"/>
+      <x:c r="F93" t="str">
+        <x:v>gameplay/towers/characters/spark_level2/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G93" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H93" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B94" t="str">
+        <x:v>ember_level2</x:v>
+      </x:c>
+      <x:c r="C94" t="str">
+        <x:v>ember_level2</x:v>
+      </x:c>
+      <x:c r="D94" t="str">
+        <x:v>ember_level2</x:v>
+      </x:c>
+      <x:c r="E94" t="str"/>
+      <x:c r="F94" t="str">
+        <x:v>gameplay/towers/characters/ember_level2/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G94" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H94" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B95" t="str">
+        <x:v>mint_level2</x:v>
+      </x:c>
+      <x:c r="C95" t="str">
+        <x:v>mint_level2</x:v>
+      </x:c>
+      <x:c r="D95" t="str">
+        <x:v>mint_level2</x:v>
+      </x:c>
+      <x:c r="E95" t="str"/>
+      <x:c r="F95" t="str">
+        <x:v>gameplay/towers/characters/mint_level2/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G95" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H95" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B96" t="str">
+        <x:v>fan_level2</x:v>
+      </x:c>
+      <x:c r="C96" t="str">
+        <x:v>fan_level2</x:v>
+      </x:c>
+      <x:c r="D96" t="str">
+        <x:v>fan_level2</x:v>
+      </x:c>
+      <x:c r="E96" t="str"/>
+      <x:c r="F96" t="str">
+        <x:v>gameplay/towers/characters/fan_level2/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G96" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H96" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/ArtFrame.xlsx
+++ b/design/tables/ArtFrame.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtFrame" sheetId="1" r:id="R7a00b13d683b4237"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtFrame" sheetId="1" r:id="R09ebe73932184281"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2355,6 +2355,374 @@
         <x:v>256</x:v>
       </x:c>
     </x:row>
+    <x:row r="97">
+      <x:c r="A97" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B97" t="str">
+        <x:v>enemy_puff</x:v>
+      </x:c>
+      <x:c r="C97" t="str">
+        <x:v>enemy_puff</x:v>
+      </x:c>
+      <x:c r="D97" t="str"/>
+      <x:c r="E97" t="str"/>
+      <x:c r="F97" t="str">
+        <x:v>gameplay/enemies/characters/enemy_puff/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G97" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H97" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" t="n">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B98" t="str">
+        <x:v>enemy_pudding</x:v>
+      </x:c>
+      <x:c r="C98" t="str">
+        <x:v>enemy_pudding</x:v>
+      </x:c>
+      <x:c r="D98" t="str"/>
+      <x:c r="E98" t="str"/>
+      <x:c r="F98" t="str">
+        <x:v>gameplay/enemies/characters/enemy_pudding/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G98" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H98" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B99" t="str">
+        <x:v>enemy_biscuit</x:v>
+      </x:c>
+      <x:c r="C99" t="str">
+        <x:v>enemy_biscuit</x:v>
+      </x:c>
+      <x:c r="D99" t="str"/>
+      <x:c r="E99" t="str"/>
+      <x:c r="F99" t="str">
+        <x:v>gameplay/enemies/characters/enemy_biscuit/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G99" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H99" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B100" t="str">
+        <x:v>enemy_soda</x:v>
+      </x:c>
+      <x:c r="C100" t="str">
+        <x:v>enemy_soda</x:v>
+      </x:c>
+      <x:c r="D100" t="str"/>
+      <x:c r="E100" t="str"/>
+      <x:c r="F100" t="str">
+        <x:v>gameplay/enemies/characters/enemy_soda/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G100" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H100" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B101" t="str">
+        <x:v>enemy_coffee</x:v>
+      </x:c>
+      <x:c r="C101" t="str">
+        <x:v>enemy_coffee</x:v>
+      </x:c>
+      <x:c r="D101" t="str"/>
+      <x:c r="E101" t="str"/>
+      <x:c r="F101" t="str">
+        <x:v>gameplay/enemies/characters/enemy_coffee/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G101" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H101" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" t="n">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B102" t="str">
+        <x:v>enemy_tea</x:v>
+      </x:c>
+      <x:c r="C102" t="str">
+        <x:v>enemy_tea</x:v>
+      </x:c>
+      <x:c r="D102" t="str"/>
+      <x:c r="E102" t="str"/>
+      <x:c r="F102" t="str">
+        <x:v>gameplay/enemies/characters/enemy_tea/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G102" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H102" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="n">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B103" t="str">
+        <x:v>enemy_berrymilk</x:v>
+      </x:c>
+      <x:c r="C103" t="str">
+        <x:v>enemy_berrymilk</x:v>
+      </x:c>
+      <x:c r="D103" t="str"/>
+      <x:c r="E103" t="str"/>
+      <x:c r="F103" t="str">
+        <x:v>gameplay/enemies/characters/enemy_berrymilk/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G103" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H103" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="n">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B104" t="str">
+        <x:v>enemy_tin</x:v>
+      </x:c>
+      <x:c r="C104" t="str">
+        <x:v>enemy_tin</x:v>
+      </x:c>
+      <x:c r="D104" t="str"/>
+      <x:c r="E104" t="str"/>
+      <x:c r="F104" t="str">
+        <x:v>gameplay/enemies/characters/enemy_tin/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G104" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H104" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B105" t="str">
+        <x:v>enemy_juice</x:v>
+      </x:c>
+      <x:c r="C105" t="str">
+        <x:v>enemy_juice</x:v>
+      </x:c>
+      <x:c r="D105" t="str"/>
+      <x:c r="E105" t="str"/>
+      <x:c r="F105" t="str">
+        <x:v>gameplay/enemies/characters/enemy_juice/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G105" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H105" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B106" t="str">
+        <x:v>enemy_peach</x:v>
+      </x:c>
+      <x:c r="C106" t="str">
+        <x:v>enemy_peach</x:v>
+      </x:c>
+      <x:c r="D106" t="str"/>
+      <x:c r="E106" t="str"/>
+      <x:c r="F106" t="str">
+        <x:v>gameplay/enemies/characters/enemy_peach/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G106" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H106" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" t="n">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B107" t="str">
+        <x:v>enemy_grape</x:v>
+      </x:c>
+      <x:c r="C107" t="str">
+        <x:v>enemy_grape</x:v>
+      </x:c>
+      <x:c r="D107" t="str"/>
+      <x:c r="E107" t="str"/>
+      <x:c r="F107" t="str">
+        <x:v>gameplay/enemies/characters/enemy_grape/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G107" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H107" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" t="n">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B108" t="str">
+        <x:v>enemy_blue</x:v>
+      </x:c>
+      <x:c r="C108" t="str">
+        <x:v>enemy_blue</x:v>
+      </x:c>
+      <x:c r="D108" t="str"/>
+      <x:c r="E108" t="str"/>
+      <x:c r="F108" t="str">
+        <x:v>gameplay/enemies/characters/enemy_blue/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G108" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H108" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" t="n">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B109" t="str">
+        <x:v>enemy_ricebox</x:v>
+      </x:c>
+      <x:c r="C109" t="str">
+        <x:v>enemy_ricebox</x:v>
+      </x:c>
+      <x:c r="D109" t="str"/>
+      <x:c r="E109" t="str"/>
+      <x:c r="F109" t="str">
+        <x:v>gameplay/enemies/characters/enemy_ricebox/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G109" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H109" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" t="n">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B110" t="str">
+        <x:v>enemy_deliverybag</x:v>
+      </x:c>
+      <x:c r="C110" t="str">
+        <x:v>enemy_deliverybag</x:v>
+      </x:c>
+      <x:c r="D110" t="str"/>
+      <x:c r="E110" t="str"/>
+      <x:c r="F110" t="str">
+        <x:v>gameplay/enemies/characters/enemy_deliverybag/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G110" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H110" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" t="n">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B111" t="str"/>
+      <x:c r="C111" t="str"/>
+      <x:c r="D111" t="str">
+        <x:v>perk_R01</x:v>
+      </x:c>
+      <x:c r="E111" t="str"/>
+      <x:c r="F111" t="str">
+        <x:v>ui/icons/perks/perk_E01/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G111" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H111" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" t="n">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B112" t="str"/>
+      <x:c r="C112" t="str"/>
+      <x:c r="D112" t="str">
+        <x:v>perk_R02</x:v>
+      </x:c>
+      <x:c r="E112" t="str"/>
+      <x:c r="F112" t="str">
+        <x:v>ui/icons/perks/perk_S02/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G112" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H112" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" t="n">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B113" t="str"/>
+      <x:c r="C113" t="str"/>
+      <x:c r="D113" t="str">
+        <x:v>perk_R03</x:v>
+      </x:c>
+      <x:c r="E113" t="str"/>
+      <x:c r="F113" t="str">
+        <x:v>ui/icons/perks/perk_X02/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G113" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H113" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/ArtFrame.xlsx
+++ b/design/tables/ArtFrame.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtFrame" sheetId="1" r:id="R09ebe73932184281"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtFrame" sheetId="1" r:id="R06e7e425c5c948a1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2723,6 +2723,138 @@
         <x:v>256</x:v>
       </x:c>
     </x:row>
+    <x:row r="114">
+      <x:c r="A114" t="n">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B114" t="str">
+        <x:v>enemy_mochi</x:v>
+      </x:c>
+      <x:c r="C114" t="str">
+        <x:v>enemy_mochi</x:v>
+      </x:c>
+      <x:c r="D114" t="str"/>
+      <x:c r="E114" t="str"/>
+      <x:c r="F114" t="str">
+        <x:v>gameplay/enemies/characters/enemy_mochi/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G114" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H114" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B115" t="str">
+        <x:v>enemy_popcorn</x:v>
+      </x:c>
+      <x:c r="C115" t="str">
+        <x:v>enemy_popcorn</x:v>
+      </x:c>
+      <x:c r="D115" t="str"/>
+      <x:c r="E115" t="str"/>
+      <x:c r="F115" t="str">
+        <x:v>gameplay/enemies/characters/enemy_popcorn/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G115" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H115" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" t="n">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B116" t="str">
+        <x:v>enemy_noodlecup</x:v>
+      </x:c>
+      <x:c r="C116" t="str">
+        <x:v>enemy_noodlecup</x:v>
+      </x:c>
+      <x:c r="D116" t="str"/>
+      <x:c r="E116" t="str"/>
+      <x:c r="F116" t="str">
+        <x:v>gameplay/enemies/characters/enemy_noodlecup/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G116" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H116" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" t="n">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B117" t="str">
+        <x:v>enemy_frostdonut</x:v>
+      </x:c>
+      <x:c r="C117" t="str">
+        <x:v>enemy_frostdonut</x:v>
+      </x:c>
+      <x:c r="D117" t="str"/>
+      <x:c r="E117" t="str"/>
+      <x:c r="F117" t="str">
+        <x:v>gameplay/enemies/characters/enemy_frostdonut/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G117" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H117" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" t="n">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B118" t="str">
+        <x:v>enemy_freezer</x:v>
+      </x:c>
+      <x:c r="C118" t="str">
+        <x:v>enemy_freezer</x:v>
+      </x:c>
+      <x:c r="D118" t="str"/>
+      <x:c r="E118" t="str"/>
+      <x:c r="F118" t="str">
+        <x:v>gameplay/enemies/characters/enemy_freezer/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G118" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H118" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" t="n">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B119" t="str">
+        <x:v>enemy_vending</x:v>
+      </x:c>
+      <x:c r="C119" t="str">
+        <x:v>enemy_vending</x:v>
+      </x:c>
+      <x:c r="D119" t="str"/>
+      <x:c r="E119" t="str"/>
+      <x:c r="F119" t="str">
+        <x:v>gameplay/enemies/characters/enemy_vending/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G119" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H119" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/ArtFrame.xlsx
+++ b/design/tables/ArtFrame.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtFrame" sheetId="1" r:id="R06e7e425c5c948a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtFrame" sheetId="1" r:id="R105571836db64488"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2855,6 +2855,86 @@
         <x:v>256</x:v>
       </x:c>
     </x:row>
+    <x:row r="120">
+      <x:c r="A120" t="n">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B120" t="str"/>
+      <x:c r="C120" t="str"/>
+      <x:c r="D120" t="str">
+        <x:v>tech_boss</x:v>
+      </x:c>
+      <x:c r="E120" t="str"/>
+      <x:c r="F120" t="str">
+        <x:v>ui/windows/technology/tech_boss/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G120" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H120" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" t="n">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B121" t="str"/>
+      <x:c r="C121" t="str"/>
+      <x:c r="D121" t="str">
+        <x:v>tech_clear</x:v>
+      </x:c>
+      <x:c r="E121" t="str"/>
+      <x:c r="F121" t="str">
+        <x:v>ui/windows/technology/tech_clear/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G121" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H121" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" t="n">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B122" t="str"/>
+      <x:c r="C122" t="str"/>
+      <x:c r="D122" t="str">
+        <x:v>tech_recycle</x:v>
+      </x:c>
+      <x:c r="E122" t="str"/>
+      <x:c r="F122" t="str">
+        <x:v>ui/windows/technology/tech_recycle/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G122" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H122" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" t="n">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B123" t="str"/>
+      <x:c r="C123" t="str"/>
+      <x:c r="D123" t="str">
+        <x:v>tech_supply</x:v>
+      </x:c>
+      <x:c r="E123" t="str"/>
+      <x:c r="F123" t="str">
+        <x:v>ui/windows/technology/tech_supply/spriteFrame</x:v>
+      </x:c>
+      <x:c r="G123" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H123" t="n">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/ArtFrame.xlsx
+++ b/design/tables/ArtFrame.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtFrame" sheetId="1" r:id="R105571836db64488"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtFrame" sheetId="1" r:id="R11873898040a43af"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="2">
+  <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -24,8 +24,18 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -37,6 +47,11 @@
         <x:fgColor rgb="FF315C49"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF315B4A"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -44,10 +59,13 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
+  <x:cellXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -255,6 +273,10 @@
     <x:col min="4" max="4" width="22.5" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="22.5" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="60" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="23" customHeight="1">
@@ -282,6 +304,18 @@
       <x:c r="H1" s="2" t="str">
         <x:v>画布高</x:v>
       </x:c>
+      <x:c r="I1" s="5" t="str">
+        <x:v>可见左</x:v>
+      </x:c>
+      <x:c r="J1" s="5" t="str">
+        <x:v>可见上</x:v>
+      </x:c>
+      <x:c r="K1" s="5" t="str">
+        <x:v>可见宽</x:v>
+      </x:c>
+      <x:c r="L1" s="5" t="str">
+        <x:v>可见高</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="23" customHeight="1">
       <x:c r="A2" s="2" t="str">
@@ -308,6 +342,18 @@
       <x:c r="H2" s="2" t="str">
         <x:v>client</x:v>
       </x:c>
+      <x:c r="I2" s="5" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="J2" s="5" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="K2" s="5" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="L2" s="5" t="str">
+        <x:v>client</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="23" customHeight="1">
       <x:c r="A3" s="2" t="str">
@@ -334,6 +380,18 @@
       <x:c r="H3" s="2" t="str">
         <x:v>int</x:v>
       </x:c>
+      <x:c r="I3" s="5" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="J3" s="5" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="K3" s="5" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="L3" s="5" t="str">
+        <x:v>int</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="23" customHeight="1">
       <x:c r="A4" s="2" t="str">
@@ -360,6 +418,18 @@
       <x:c r="H4" s="2" t="str">
         <x:v>画布高</x:v>
       </x:c>
+      <x:c r="I4" s="5" t="str">
+        <x:v>可见左</x:v>
+      </x:c>
+      <x:c r="J4" s="5" t="str">
+        <x:v>可见上</x:v>
+      </x:c>
+      <x:c r="K4" s="5" t="str">
+        <x:v>可见宽</x:v>
+      </x:c>
+      <x:c r="L4" s="5" t="str">
+        <x:v>可见高</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="23" customHeight="1">
       <x:c r="A5" s="2" t="str">
@@ -386,6 +456,18 @@
       <x:c r="H5" s="2" t="str">
         <x:v>canvasHeight</x:v>
       </x:c>
+      <x:c r="I5" s="5" t="str">
+        <x:v>contentX</x:v>
+      </x:c>
+      <x:c r="J5" s="5" t="str">
+        <x:v>contentY</x:v>
+      </x:c>
+      <x:c r="K5" s="5" t="str">
+        <x:v>contentWidth</x:v>
+      </x:c>
+      <x:c r="L5" s="5" t="str">
+        <x:v>contentHeight</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="n">
@@ -400,7 +482,7 @@
       <x:c r="D6" t="str">
         <x:v>sprout</x:v>
       </x:c>
-      <x:c r="E6" t="str"/>
+      <x:c r="E6"/>
       <x:c r="F6" t="str">
         <x:v>gameplay/towers/characters/sprout/spriteFrame</x:v>
       </x:c>
@@ -409,6 +491,18 @@
       </x:c>
       <x:c r="H6" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I6" s="3" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J6" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K6" s="3" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="L6" s="3" t="n">
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -424,7 +518,7 @@
       <x:c r="D7" t="str">
         <x:v>frost</x:v>
       </x:c>
-      <x:c r="E7" t="str"/>
+      <x:c r="E7"/>
       <x:c r="F7" t="str">
         <x:v>gameplay/towers/characters/frost/spriteFrame</x:v>
       </x:c>
@@ -433,6 +527,18 @@
       </x:c>
       <x:c r="H7" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I7" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="3" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K7" s="3" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L7" s="3" t="n">
+        <x:v>224</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -448,7 +554,7 @@
       <x:c r="D8" t="str">
         <x:v>bloom</x:v>
       </x:c>
-      <x:c r="E8" t="str"/>
+      <x:c r="E8"/>
       <x:c r="F8" t="str">
         <x:v>gameplay/towers/characters/bloom/spriteFrame</x:v>
       </x:c>
@@ -457,6 +563,18 @@
       </x:c>
       <x:c r="H8" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I8" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J8" s="3" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="K8" s="3" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="L8" s="3" t="n">
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -466,9 +584,9 @@
       <x:c r="B9" t="str">
         <x:v>pad</x:v>
       </x:c>
-      <x:c r="C9" t="str"/>
-      <x:c r="D9" t="str"/>
-      <x:c r="E9" t="str"/>
+      <x:c r="C9"/>
+      <x:c r="D9"/>
+      <x:c r="E9"/>
       <x:c r="F9" t="str">
         <x:v>gameplay/obstacles/pad/spriteFrame</x:v>
       </x:c>
@@ -477,6 +595,18 @@
       </x:c>
       <x:c r="H9" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I9" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J9" s="3" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K9" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L9" s="3" t="n">
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -486,9 +616,9 @@
       <x:c r="B10" t="str">
         <x:v>crate</x:v>
       </x:c>
-      <x:c r="C10" t="str"/>
-      <x:c r="D10" t="str"/>
-      <x:c r="E10" t="str"/>
+      <x:c r="C10"/>
+      <x:c r="D10"/>
+      <x:c r="E10"/>
       <x:c r="F10" t="str">
         <x:v>gameplay/obstacles/crate/spriteFrame</x:v>
       </x:c>
@@ -497,6 +627,18 @@
       </x:c>
       <x:c r="H10" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I10" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J10" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K10" s="3" t="n">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="L10" s="3" t="n">
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -506,9 +648,9 @@
       <x:c r="B11" t="str">
         <x:v>basket</x:v>
       </x:c>
-      <x:c r="C11" t="str"/>
-      <x:c r="D11" t="str"/>
-      <x:c r="E11" t="str"/>
+      <x:c r="C11"/>
+      <x:c r="D11"/>
+      <x:c r="E11"/>
       <x:c r="F11" t="str">
         <x:v>gameplay/obstacles/basket/spriteFrame</x:v>
       </x:c>
@@ -517,6 +659,18 @@
       </x:c>
       <x:c r="H11" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I11" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J11" s="3" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="K11" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L11" s="3" t="n">
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -526,9 +680,9 @@
       <x:c r="B12" t="str">
         <x:v>plant</x:v>
       </x:c>
-      <x:c r="C12" t="str"/>
-      <x:c r="D12" t="str"/>
-      <x:c r="E12" t="str"/>
+      <x:c r="C12"/>
+      <x:c r="D12"/>
+      <x:c r="E12"/>
       <x:c r="F12" t="str">
         <x:v>gameplay/obstacles/plant/spriteFrame</x:v>
       </x:c>
@@ -538,6 +692,18 @@
       <x:c r="H12" t="n">
         <x:v>256</x:v>
       </x:c>
+      <x:c r="I12" s="3" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="J12" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K12" s="3" t="n">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="L12" s="3" t="n">
+        <x:v>239</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="n">
@@ -549,8 +715,8 @@
       <x:c r="C13" t="str">
         <x:v>enemy_normal</x:v>
       </x:c>
-      <x:c r="D13" t="str"/>
-      <x:c r="E13" t="str"/>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
       <x:c r="F13" t="str">
         <x:v>gameplay/enemies/characters/enemy_normal/spriteFrame</x:v>
       </x:c>
@@ -560,6 +726,18 @@
       <x:c r="H13" t="n">
         <x:v>256</x:v>
       </x:c>
+      <x:c r="I13" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J13" s="3" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K13" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L13" s="3" t="n">
+        <x:v>230</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="n">
@@ -571,8 +749,8 @@
       <x:c r="C14" t="str">
         <x:v>enemy_swift</x:v>
       </x:c>
-      <x:c r="D14" t="str"/>
-      <x:c r="E14" t="str"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
       <x:c r="F14" t="str">
         <x:v>gameplay/enemies/characters/enemy_swift/spriteFrame</x:v>
       </x:c>
@@ -581,6 +759,18 @@
       </x:c>
       <x:c r="H14" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I14" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J14" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K14" s="3" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="L14" s="3" t="n">
+        <x:v>237</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -593,8 +783,8 @@
       <x:c r="C15" t="str">
         <x:v>enemy_tank</x:v>
       </x:c>
-      <x:c r="D15" t="str"/>
-      <x:c r="E15" t="str"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
       <x:c r="F15" t="str">
         <x:v>gameplay/enemies/characters/enemy_tank/spriteFrame</x:v>
       </x:c>
@@ -603,6 +793,18 @@
       </x:c>
       <x:c r="H15" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I15" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J15" s="3" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K15" s="3" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="L15" s="3" t="n">
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -612,9 +814,9 @@
       <x:c r="B16" t="str">
         <x:v>enemy_normal_hit</x:v>
       </x:c>
-      <x:c r="C16" t="str"/>
-      <x:c r="D16" t="str"/>
-      <x:c r="E16" t="str"/>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
+      <x:c r="E16"/>
       <x:c r="F16" t="str">
         <x:v>gameplay/enemies/characters/enemy_normal_hit/spriteFrame</x:v>
       </x:c>
@@ -623,6 +825,18 @@
       </x:c>
       <x:c r="H16" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I16" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J16" s="3" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K16" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L16" s="3" t="n">
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -632,9 +846,9 @@
       <x:c r="B17" t="str">
         <x:v>enemy_swift_hit</x:v>
       </x:c>
-      <x:c r="C17" t="str"/>
-      <x:c r="D17" t="str"/>
-      <x:c r="E17" t="str"/>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
       <x:c r="F17" t="str">
         <x:v>gameplay/enemies/characters/enemy_swift_hit/spriteFrame</x:v>
       </x:c>
@@ -643,6 +857,18 @@
       </x:c>
       <x:c r="H17" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I17" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J17" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K17" s="3" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="L17" s="3" t="n">
+        <x:v>237</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -652,9 +878,9 @@
       <x:c r="B18" t="str">
         <x:v>enemy_tank_hit</x:v>
       </x:c>
-      <x:c r="C18" t="str"/>
-      <x:c r="D18" t="str"/>
-      <x:c r="E18" t="str"/>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
       <x:c r="F18" t="str">
         <x:v>gameplay/enemies/characters/enemy_tank_hit/spriteFrame</x:v>
       </x:c>
@@ -663,6 +889,18 @@
       </x:c>
       <x:c r="H18" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I18" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J18" s="3" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K18" s="3" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="L18" s="3" t="n">
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -678,7 +916,7 @@
       <x:c r="D19" t="str">
         <x:v>scope</x:v>
       </x:c>
-      <x:c r="E19" t="str"/>
+      <x:c r="E19"/>
       <x:c r="F19" t="str">
         <x:v>gameplay/towers/characters/scope/spriteFrame</x:v>
       </x:c>
@@ -687,6 +925,18 @@
       </x:c>
       <x:c r="H19" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I19" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J19" s="3" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K19" s="3" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="L19" s="3" t="n">
+        <x:v>223</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -702,7 +952,7 @@
       <x:c r="D20" t="str">
         <x:v>spark</x:v>
       </x:c>
-      <x:c r="E20" t="str"/>
+      <x:c r="E20"/>
       <x:c r="F20" t="str">
         <x:v>gameplay/towers/characters/spark/spriteFrame</x:v>
       </x:c>
@@ -711,6 +961,18 @@
       </x:c>
       <x:c r="H20" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I20" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J20" s="3" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K20" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L20" s="3" t="n">
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -726,7 +988,7 @@
       <x:c r="D21" t="str">
         <x:v>ember</x:v>
       </x:c>
-      <x:c r="E21" t="str"/>
+      <x:c r="E21"/>
       <x:c r="F21" t="str">
         <x:v>gameplay/towers/characters/ember/spriteFrame</x:v>
       </x:c>
@@ -735,6 +997,18 @@
       </x:c>
       <x:c r="H21" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I21" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J21" s="3" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K21" s="3" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="L21" s="3" t="n">
+        <x:v>224</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -750,7 +1024,7 @@
       <x:c r="D22" t="str">
         <x:v>mint</x:v>
       </x:c>
-      <x:c r="E22" t="str"/>
+      <x:c r="E22"/>
       <x:c r="F22" t="str">
         <x:v>gameplay/towers/characters/mint/spriteFrame</x:v>
       </x:c>
@@ -759,6 +1033,18 @@
       </x:c>
       <x:c r="H22" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I22" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J22" s="3" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K22" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L22" s="3" t="n">
+        <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -774,7 +1060,7 @@
       <x:c r="D23" t="str">
         <x:v>fan</x:v>
       </x:c>
-      <x:c r="E23" t="str"/>
+      <x:c r="E23"/>
       <x:c r="F23" t="str">
         <x:v>gameplay/towers/characters/fan/spriteFrame</x:v>
       </x:c>
@@ -783,6 +1069,18 @@
       </x:c>
       <x:c r="H23" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I23" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J23" s="3" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="K23" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L23" s="3" t="n">
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -795,8 +1093,8 @@
       <x:c r="C24" t="str">
         <x:v>enemy_shield</x:v>
       </x:c>
-      <x:c r="D24" t="str"/>
-      <x:c r="E24" t="str"/>
+      <x:c r="D24"/>
+      <x:c r="E24"/>
       <x:c r="F24" t="str">
         <x:v>gameplay/enemies/characters/enemy_shield/spriteFrame</x:v>
       </x:c>
@@ -805,6 +1103,18 @@
       </x:c>
       <x:c r="H24" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I24" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J24" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K24" s="3" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="L24" s="3" t="n">
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -817,8 +1127,8 @@
       <x:c r="C25" t="str">
         <x:v>enemy_jelly</x:v>
       </x:c>
-      <x:c r="D25" t="str"/>
-      <x:c r="E25" t="str"/>
+      <x:c r="D25"/>
+      <x:c r="E25"/>
       <x:c r="F25" t="str">
         <x:v>gameplay/enemies/characters/enemy_jelly/spriteFrame</x:v>
       </x:c>
@@ -827,6 +1137,18 @@
       </x:c>
       <x:c r="H25" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I25" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J25" s="3" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K25" s="3" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="L25" s="3" t="n">
+        <x:v>224</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -839,8 +1161,8 @@
       <x:c r="C26" t="str">
         <x:v>enemy_runner</x:v>
       </x:c>
-      <x:c r="D26" t="str"/>
-      <x:c r="E26" t="str"/>
+      <x:c r="D26"/>
+      <x:c r="E26"/>
       <x:c r="F26" t="str">
         <x:v>gameplay/enemies/characters/enemy_runner/spriteFrame</x:v>
       </x:c>
@@ -849,6 +1171,18 @@
       </x:c>
       <x:c r="H26" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I26" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J26" s="3" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="K26" s="3" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="L26" s="3" t="n">
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -861,8 +1195,8 @@
       <x:c r="C27" t="str">
         <x:v>enemy_postmaster</x:v>
       </x:c>
-      <x:c r="D27" t="str"/>
-      <x:c r="E27" t="str"/>
+      <x:c r="D27"/>
+      <x:c r="E27"/>
       <x:c r="F27" t="str">
         <x:v>gameplay/enemies/characters/enemy_postmaster/spriteFrame</x:v>
       </x:c>
@@ -871,6 +1205,18 @@
       </x:c>
       <x:c r="H27" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I27" s="3" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J27" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K27" s="3" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="L27" s="3" t="n">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -883,8 +1229,8 @@
       <x:c r="C28" t="str">
         <x:v>enemy_lantern</x:v>
       </x:c>
-      <x:c r="D28" t="str"/>
-      <x:c r="E28" t="str"/>
+      <x:c r="D28"/>
+      <x:c r="E28"/>
       <x:c r="F28" t="str">
         <x:v>gameplay/enemies/characters/enemy_lantern/spriteFrame</x:v>
       </x:c>
@@ -893,6 +1239,18 @@
       </x:c>
       <x:c r="H28" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I28" s="3" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J28" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K28" s="3" t="n">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="L28" s="3" t="n">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -905,8 +1263,8 @@
       <x:c r="C29" t="str">
         <x:v>enemy_chef</x:v>
       </x:c>
-      <x:c r="D29" t="str"/>
-      <x:c r="E29" t="str"/>
+      <x:c r="D29"/>
+      <x:c r="E29"/>
       <x:c r="F29" t="str">
         <x:v>gameplay/enemies/characters/enemy_chef/spriteFrame</x:v>
       </x:c>
@@ -915,6 +1273,18 @@
       </x:c>
       <x:c r="H29" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I29" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J29" s="3" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="K29" s="3" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L29" s="3" t="n">
+        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -927,8 +1297,8 @@
       <x:c r="C30" t="str">
         <x:v>enemy_clock</x:v>
       </x:c>
-      <x:c r="D30" t="str"/>
-      <x:c r="E30" t="str"/>
+      <x:c r="D30"/>
+      <x:c r="E30"/>
       <x:c r="F30" t="str">
         <x:v>gameplay/enemies/characters/enemy_clock/spriteFrame</x:v>
       </x:c>
@@ -937,18 +1307,30 @@
       </x:c>
       <x:c r="H30" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I30" s="3" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J30" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K30" s="3" t="n">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="L30" s="3" t="n">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B31" t="str"/>
-      <x:c r="C31" t="str"/>
+      <x:c r="B31"/>
+      <x:c r="C31"/>
       <x:c r="D31" t="str">
         <x:v>freeze</x:v>
       </x:c>
-      <x:c r="E31" t="str"/>
+      <x:c r="E31"/>
       <x:c r="F31" t="str">
         <x:v>ui/icons/props/freeze/spriteFrame</x:v>
       </x:c>
@@ -957,18 +1339,30 @@
       </x:c>
       <x:c r="H31" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I31" s="3" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="J31" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K31" s="3" t="n">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="L31" s="3" t="n">
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B32" t="str"/>
-      <x:c r="C32" t="str"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
       <x:c r="D32" t="str">
         <x:v>clear</x:v>
       </x:c>
-      <x:c r="E32" t="str"/>
+      <x:c r="E32"/>
       <x:c r="F32" t="str">
         <x:v>ui/icons/props/clear/spriteFrame</x:v>
       </x:c>
@@ -977,18 +1371,30 @@
       </x:c>
       <x:c r="H32" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I32" s="3" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="J32" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K32" s="3" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="L32" s="3" t="n">
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B33" t="str"/>
-      <x:c r="C33" t="str"/>
+      <x:c r="B33"/>
+      <x:c r="C33"/>
       <x:c r="D33" t="str">
         <x:v>cash</x:v>
       </x:c>
-      <x:c r="E33" t="str"/>
+      <x:c r="E33"/>
       <x:c r="F33" t="str">
         <x:v>ui/icons/props/cash/spriteFrame</x:v>
       </x:c>
@@ -997,15 +1403,27 @@
       </x:c>
       <x:c r="H33" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I33" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J33" s="3" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="K33" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L33" s="3" t="n">
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B34" t="str"/>
-      <x:c r="C34" t="str"/>
-      <x:c r="D34" t="str"/>
+      <x:c r="B34"/>
+      <x:c r="C34"/>
+      <x:c r="D34"/>
       <x:c r="E34" t="str">
         <x:v>entry</x:v>
       </x:c>
@@ -1017,15 +1435,27 @@
       </x:c>
       <x:c r="H34" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I34" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J34" s="3" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K34" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L34" s="3" t="n">
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B35" t="str"/>
-      <x:c r="C35" t="str"/>
-      <x:c r="D35" t="str"/>
+      <x:c r="B35"/>
+      <x:c r="C35"/>
+      <x:c r="D35"/>
       <x:c r="E35" t="str">
         <x:v>goal</x:v>
       </x:c>
@@ -1037,15 +1467,27 @@
       </x:c>
       <x:c r="H35" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I35" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J35" s="3" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K35" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L35" s="3" t="n">
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B36" t="str"/>
-      <x:c r="C36" t="str"/>
-      <x:c r="D36" t="str"/>
+      <x:c r="B36"/>
+      <x:c r="C36"/>
+      <x:c r="D36"/>
       <x:c r="E36" t="str">
         <x:v>planter</x:v>
       </x:c>
@@ -1057,15 +1499,27 @@
       </x:c>
       <x:c r="H36" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I36" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J36" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K36" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L36" s="3" t="n">
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B37" t="str"/>
-      <x:c r="C37" t="str"/>
-      <x:c r="D37" t="str"/>
+      <x:c r="B37"/>
+      <x:c r="C37"/>
+      <x:c r="D37"/>
       <x:c r="E37" t="str">
         <x:v>tree</x:v>
       </x:c>
@@ -1077,18 +1531,30 @@
       </x:c>
       <x:c r="H37" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I37" s="3" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J37" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K37" s="3" t="n">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="L37" s="3" t="n">
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B38" t="str"/>
+      <x:c r="B38"/>
       <x:c r="C38" t="str">
         <x:v>entry</x:v>
       </x:c>
-      <x:c r="D38" t="str"/>
-      <x:c r="E38" t="str"/>
+      <x:c r="D38"/>
+      <x:c r="E38"/>
       <x:c r="F38" t="str">
         <x:v>gameplay/towers/characters/entry/spriteFrame</x:v>
       </x:c>
@@ -1097,18 +1563,30 @@
       </x:c>
       <x:c r="H38" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I38" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J38" s="3" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K38" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L38" s="3" t="n">
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B39" t="str"/>
+      <x:c r="B39"/>
       <x:c r="C39" t="str">
         <x:v>shop</x:v>
       </x:c>
-      <x:c r="D39" t="str"/>
-      <x:c r="E39" t="str"/>
+      <x:c r="D39"/>
+      <x:c r="E39"/>
       <x:c r="F39" t="str">
         <x:v>gameplay/towers/characters/shop/spriteFrame</x:v>
       </x:c>
@@ -1117,18 +1595,30 @@
       </x:c>
       <x:c r="H39" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I39" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J39" s="3" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K39" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L39" s="3" t="n">
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B40" t="str"/>
+      <x:c r="B40"/>
       <x:c r="C40" t="str">
         <x:v>tree</x:v>
       </x:c>
-      <x:c r="D40" t="str"/>
-      <x:c r="E40" t="str"/>
+      <x:c r="D40"/>
+      <x:c r="E40"/>
       <x:c r="F40" t="str">
         <x:v>gameplay/towers/characters/tree/spriteFrame</x:v>
       </x:c>
@@ -1137,6 +1627,18 @@
       </x:c>
       <x:c r="H40" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I40" s="3" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J40" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K40" s="3" t="n">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="L40" s="3" t="n">
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -1152,7 +1654,7 @@
       <x:c r="D41" t="str">
         <x:v>sprout_heavy</x:v>
       </x:c>
-      <x:c r="E41" t="str"/>
+      <x:c r="E41"/>
       <x:c r="F41" t="str">
         <x:v>gameplay/towers/characters/sprout_heavy/spriteFrame</x:v>
       </x:c>
@@ -1161,6 +1663,18 @@
       </x:c>
       <x:c r="H41" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I41" s="3" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J41" s="3" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K41" s="3" t="n">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="L41" s="3" t="n">
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -1176,7 +1690,7 @@
       <x:c r="D42" t="str">
         <x:v>sprout_burst</x:v>
       </x:c>
-      <x:c r="E42" t="str"/>
+      <x:c r="E42"/>
       <x:c r="F42" t="str">
         <x:v>gameplay/towers/characters/sprout_burst/spriteFrame</x:v>
       </x:c>
@@ -1185,6 +1699,18 @@
       </x:c>
       <x:c r="H42" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I42" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J42" s="3" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K42" s="3" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L42" s="3" t="n">
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -1200,7 +1726,7 @@
       <x:c r="D43" t="str">
         <x:v>frost_deep</x:v>
       </x:c>
-      <x:c r="E43" t="str"/>
+      <x:c r="E43"/>
       <x:c r="F43" t="str">
         <x:v>gameplay/towers/characters/frost_deep/spriteFrame</x:v>
       </x:c>
@@ -1209,6 +1735,18 @@
       </x:c>
       <x:c r="H43" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I43" s="3" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J43" s="3" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K43" s="3" t="n">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="L43" s="3" t="n">
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -1224,7 +1762,7 @@
       <x:c r="D44" t="str">
         <x:v>frost_dual</x:v>
       </x:c>
-      <x:c r="E44" t="str"/>
+      <x:c r="E44"/>
       <x:c r="F44" t="str">
         <x:v>gameplay/towers/characters/frost_dual/spriteFrame</x:v>
       </x:c>
@@ -1233,6 +1771,18 @@
       </x:c>
       <x:c r="H44" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I44" s="3" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J44" s="3" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K44" s="3" t="n">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="L44" s="3" t="n">
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -1248,7 +1798,7 @@
       <x:c r="D45" t="str">
         <x:v>bloom_focus</x:v>
       </x:c>
-      <x:c r="E45" t="str"/>
+      <x:c r="E45"/>
       <x:c r="F45" t="str">
         <x:v>gameplay/towers/characters/bloom_focus/spriteFrame</x:v>
       </x:c>
@@ -1257,6 +1807,18 @@
       </x:c>
       <x:c r="H45" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I45" s="3" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J45" s="3" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K45" s="3" t="n">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="L45" s="3" t="n">
+        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -1272,7 +1834,7 @@
       <x:c r="D46" t="str">
         <x:v>bloom_wide</x:v>
       </x:c>
-      <x:c r="E46" t="str"/>
+      <x:c r="E46"/>
       <x:c r="F46" t="str">
         <x:v>gameplay/towers/characters/bloom_wide/spriteFrame</x:v>
       </x:c>
@@ -1281,6 +1843,18 @@
       </x:c>
       <x:c r="H46" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I46" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J46" s="3" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K46" s="3" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L46" s="3" t="n">
+        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -1296,7 +1870,7 @@
       <x:c r="D47" t="str">
         <x:v>scope_precision</x:v>
       </x:c>
-      <x:c r="E47" t="str"/>
+      <x:c r="E47"/>
       <x:c r="F47" t="str">
         <x:v>gameplay/towers/characters/scope_precision/spriteFrame</x:v>
       </x:c>
@@ -1305,6 +1879,18 @@
       </x:c>
       <x:c r="H47" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I47" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J47" s="3" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K47" s="3" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L47" s="3" t="n">
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -1320,7 +1906,7 @@
       <x:c r="D48" t="str">
         <x:v>scope_pierce</x:v>
       </x:c>
-      <x:c r="E48" t="str"/>
+      <x:c r="E48"/>
       <x:c r="F48" t="str">
         <x:v>gameplay/towers/characters/scope_pierce/spriteFrame</x:v>
       </x:c>
@@ -1329,6 +1915,18 @@
       </x:c>
       <x:c r="H48" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I48" s="3" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J48" s="3" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K48" s="3" t="n">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="L48" s="3" t="n">
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -1344,7 +1942,7 @@
       <x:c r="D49" t="str">
         <x:v>spark_focus</x:v>
       </x:c>
-      <x:c r="E49" t="str"/>
+      <x:c r="E49"/>
       <x:c r="F49" t="str">
         <x:v>gameplay/towers/characters/spark_focus/spriteFrame</x:v>
       </x:c>
@@ -1353,6 +1951,18 @@
       </x:c>
       <x:c r="H49" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I49" s="3" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J49" s="3" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K49" s="3" t="n">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="L49" s="3" t="n">
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -1368,7 +1978,7 @@
       <x:c r="D50" t="str">
         <x:v>spark_chain</x:v>
       </x:c>
-      <x:c r="E50" t="str"/>
+      <x:c r="E50"/>
       <x:c r="F50" t="str">
         <x:v>gameplay/towers/characters/spark_chain/spriteFrame</x:v>
       </x:c>
@@ -1377,6 +1987,18 @@
       </x:c>
       <x:c r="H50" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I50" s="3" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J50" s="3" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K50" s="3" t="n">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="L50" s="3" t="n">
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -1392,7 +2014,7 @@
       <x:c r="D51" t="str">
         <x:v>ember_scorch</x:v>
       </x:c>
-      <x:c r="E51" t="str"/>
+      <x:c r="E51"/>
       <x:c r="F51" t="str">
         <x:v>gameplay/towers/characters/ember_scorch/spriteFrame</x:v>
       </x:c>
@@ -1401,6 +2023,18 @@
       </x:c>
       <x:c r="H51" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I51" s="3" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J51" s="3" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K51" s="3" t="n">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="L51" s="3" t="n">
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -1416,7 +2050,7 @@
       <x:c r="D52" t="str">
         <x:v>ember_burst</x:v>
       </x:c>
-      <x:c r="E52" t="str"/>
+      <x:c r="E52"/>
       <x:c r="F52" t="str">
         <x:v>gameplay/towers/characters/ember_burst/spriteFrame</x:v>
       </x:c>
@@ -1425,6 +2059,18 @@
       </x:c>
       <x:c r="H52" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I52" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J52" s="3" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K52" s="3" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="L52" s="3" t="n">
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -1440,7 +2086,7 @@
       <x:c r="D53" t="str">
         <x:v>mint_focus</x:v>
       </x:c>
-      <x:c r="E53" t="str"/>
+      <x:c r="E53"/>
       <x:c r="F53" t="str">
         <x:v>gameplay/towers/characters/mint_focus/spriteFrame</x:v>
       </x:c>
@@ -1449,6 +2095,18 @@
       </x:c>
       <x:c r="H53" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I53" s="3" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J53" s="3" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="K53" s="3" t="n">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="L53" s="3" t="n">
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -1464,7 +2122,7 @@
       <x:c r="D54" t="str">
         <x:v>mint_dual</x:v>
       </x:c>
-      <x:c r="E54" t="str"/>
+      <x:c r="E54"/>
       <x:c r="F54" t="str">
         <x:v>gameplay/towers/characters/mint_dual/spriteFrame</x:v>
       </x:c>
@@ -1473,6 +2131,18 @@
       </x:c>
       <x:c r="H54" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I54" s="3" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J54" s="3" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K54" s="3" t="n">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="L54" s="3" t="n">
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -1488,7 +2158,7 @@
       <x:c r="D55" t="str">
         <x:v>fan_spread</x:v>
       </x:c>
-      <x:c r="E55" t="str"/>
+      <x:c r="E55"/>
       <x:c r="F55" t="str">
         <x:v>gameplay/towers/characters/fan_spread/spriteFrame</x:v>
       </x:c>
@@ -1497,6 +2167,18 @@
       </x:c>
       <x:c r="H55" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I55" s="3" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J55" s="3" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K55" s="3" t="n">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="L55" s="3" t="n">
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -1512,7 +2194,7 @@
       <x:c r="D56" t="str">
         <x:v>fan_volley</x:v>
       </x:c>
-      <x:c r="E56" t="str"/>
+      <x:c r="E56"/>
       <x:c r="F56" t="str">
         <x:v>gameplay/towers/characters/fan_volley/spriteFrame</x:v>
       </x:c>
@@ -1521,18 +2203,30 @@
       </x:c>
       <x:c r="H56" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I56" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J56" s="3" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="K56" s="3" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L56" s="3" t="n">
+        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" t="n">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B57" t="str"/>
-      <x:c r="C57" t="str"/>
+      <x:c r="B57"/>
+      <x:c r="C57"/>
       <x:c r="D57" t="str">
         <x:v>perk_S01</x:v>
       </x:c>
-      <x:c r="E57" t="str"/>
+      <x:c r="E57"/>
       <x:c r="F57" t="str">
         <x:v>ui/icons/perks/perk_S01/spriteFrame</x:v>
       </x:c>
@@ -1541,18 +2235,30 @@
       </x:c>
       <x:c r="H57" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I57" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J57" s="3" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K57" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L57" s="3" t="n">
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" t="n">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B58" t="str"/>
-      <x:c r="C58" t="str"/>
+      <x:c r="B58"/>
+      <x:c r="C58"/>
       <x:c r="D58" t="str">
         <x:v>perk_S02</x:v>
       </x:c>
-      <x:c r="E58" t="str"/>
+      <x:c r="E58"/>
       <x:c r="F58" t="str">
         <x:v>ui/icons/perks/perk_S02/spriteFrame</x:v>
       </x:c>
@@ -1561,18 +2267,30 @@
       </x:c>
       <x:c r="H58" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I58" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J58" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K58" s="3" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="L58" s="3" t="n">
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" t="n">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B59" t="str"/>
-      <x:c r="C59" t="str"/>
+      <x:c r="B59"/>
+      <x:c r="C59"/>
       <x:c r="D59" t="str">
         <x:v>perk_S03</x:v>
       </x:c>
-      <x:c r="E59" t="str"/>
+      <x:c r="E59"/>
       <x:c r="F59" t="str">
         <x:v>ui/icons/perks/perk_S03/spriteFrame</x:v>
       </x:c>
@@ -1581,18 +2299,30 @@
       </x:c>
       <x:c r="H59" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I59" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J59" s="3" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K59" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L59" s="3" t="n">
+        <x:v>224</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" t="n">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B60" t="str"/>
-      <x:c r="C60" t="str"/>
+      <x:c r="B60"/>
+      <x:c r="C60"/>
       <x:c r="D60" t="str">
         <x:v>perk_S04</x:v>
       </x:c>
-      <x:c r="E60" t="str"/>
+      <x:c r="E60"/>
       <x:c r="F60" t="str">
         <x:v>ui/icons/perks/perk_S04/spriteFrame</x:v>
       </x:c>
@@ -1601,18 +2331,30 @@
       </x:c>
       <x:c r="H60" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I60" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J60" s="3" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K60" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L60" s="3" t="n">
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" t="n">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B61" t="str"/>
-      <x:c r="C61" t="str"/>
+      <x:c r="B61"/>
+      <x:c r="C61"/>
       <x:c r="D61" t="str">
         <x:v>perk_S05</x:v>
       </x:c>
-      <x:c r="E61" t="str"/>
+      <x:c r="E61"/>
       <x:c r="F61" t="str">
         <x:v>ui/icons/perks/perk_S05/spriteFrame</x:v>
       </x:c>
@@ -1621,18 +2363,30 @@
       </x:c>
       <x:c r="H61" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I61" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J61" s="3" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K61" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L61" s="3" t="n">
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" t="n">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B62" t="str"/>
-      <x:c r="C62" t="str"/>
+      <x:c r="B62"/>
+      <x:c r="C62"/>
       <x:c r="D62" t="str">
         <x:v>perk_S06</x:v>
       </x:c>
-      <x:c r="E62" t="str"/>
+      <x:c r="E62"/>
       <x:c r="F62" t="str">
         <x:v>ui/icons/perks/perk_S06/spriteFrame</x:v>
       </x:c>
@@ -1641,18 +2395,30 @@
       </x:c>
       <x:c r="H62" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I62" s="3" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J62" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K62" s="3" t="n">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="L62" s="3" t="n">
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" t="n">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B63" t="str"/>
-      <x:c r="C63" t="str"/>
+      <x:c r="B63"/>
+      <x:c r="C63"/>
       <x:c r="D63" t="str">
         <x:v>perk_S07</x:v>
       </x:c>
-      <x:c r="E63" t="str"/>
+      <x:c r="E63"/>
       <x:c r="F63" t="str">
         <x:v>ui/icons/perks/perk_S07/spriteFrame</x:v>
       </x:c>
@@ -1661,18 +2427,30 @@
       </x:c>
       <x:c r="H63" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I63" s="3" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="J63" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K63" s="3" t="n">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="L63" s="3" t="n">
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" t="n">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B64" t="str"/>
-      <x:c r="C64" t="str"/>
+      <x:c r="B64"/>
+      <x:c r="C64"/>
       <x:c r="D64" t="str">
         <x:v>perk_S08</x:v>
       </x:c>
-      <x:c r="E64" t="str"/>
+      <x:c r="E64"/>
       <x:c r="F64" t="str">
         <x:v>ui/icons/perks/perk_S08/spriteFrame</x:v>
       </x:c>
@@ -1681,18 +2459,30 @@
       </x:c>
       <x:c r="H64" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I64" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J64" s="3" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K64" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L64" s="3" t="n">
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B65" t="str"/>
-      <x:c r="C65" t="str"/>
+      <x:c r="B65"/>
+      <x:c r="C65"/>
       <x:c r="D65" t="str">
         <x:v>perk_G01</x:v>
       </x:c>
-      <x:c r="E65" t="str"/>
+      <x:c r="E65"/>
       <x:c r="F65" t="str">
         <x:v>ui/icons/perks/perk_G01/spriteFrame</x:v>
       </x:c>
@@ -1701,18 +2491,30 @@
       </x:c>
       <x:c r="H65" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I65" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J65" s="3" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K65" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L65" s="3" t="n">
+        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" t="n">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="B66" t="str"/>
-      <x:c r="C66" t="str"/>
+      <x:c r="B66"/>
+      <x:c r="C66"/>
       <x:c r="D66" t="str">
         <x:v>perk_G02</x:v>
       </x:c>
-      <x:c r="E66" t="str"/>
+      <x:c r="E66"/>
       <x:c r="F66" t="str">
         <x:v>ui/icons/perks/perk_G02/spriteFrame</x:v>
       </x:c>
@@ -1721,18 +2523,30 @@
       </x:c>
       <x:c r="H66" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I66" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J66" s="3" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="K66" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L66" s="3" t="n">
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" t="n">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B67" t="str"/>
-      <x:c r="C67" t="str"/>
+      <x:c r="B67"/>
+      <x:c r="C67"/>
       <x:c r="D67" t="str">
         <x:v>perk_G03</x:v>
       </x:c>
-      <x:c r="E67" t="str"/>
+      <x:c r="E67"/>
       <x:c r="F67" t="str">
         <x:v>ui/icons/perks/perk_G03/spriteFrame</x:v>
       </x:c>
@@ -1741,18 +2555,30 @@
       </x:c>
       <x:c r="H67" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I67" s="3" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J67" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K67" s="3" t="n">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="L67" s="3" t="n">
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" t="n">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B68" t="str"/>
-      <x:c r="C68" t="str"/>
+      <x:c r="B68"/>
+      <x:c r="C68"/>
       <x:c r="D68" t="str">
         <x:v>perk_G04</x:v>
       </x:c>
-      <x:c r="E68" t="str"/>
+      <x:c r="E68"/>
       <x:c r="F68" t="str">
         <x:v>ui/icons/perks/perk_G04/spriteFrame</x:v>
       </x:c>
@@ -1761,18 +2587,30 @@
       </x:c>
       <x:c r="H68" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I68" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J68" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K68" s="3" t="n">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="L68" s="3" t="n">
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" t="n">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B69" t="str"/>
-      <x:c r="C69" t="str"/>
+      <x:c r="B69"/>
+      <x:c r="C69"/>
       <x:c r="D69" t="str">
         <x:v>perk_G05</x:v>
       </x:c>
-      <x:c r="E69" t="str"/>
+      <x:c r="E69"/>
       <x:c r="F69" t="str">
         <x:v>ui/icons/perks/perk_G05/spriteFrame</x:v>
       </x:c>
@@ -1781,18 +2619,30 @@
       </x:c>
       <x:c r="H69" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I69" s="3" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J69" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K69" s="3" t="n">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="L69" s="3" t="n">
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" t="n">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B70" t="str"/>
-      <x:c r="C70" t="str"/>
+      <x:c r="B70"/>
+      <x:c r="C70"/>
       <x:c r="D70" t="str">
         <x:v>perk_G06</x:v>
       </x:c>
-      <x:c r="E70" t="str"/>
+      <x:c r="E70"/>
       <x:c r="F70" t="str">
         <x:v>ui/icons/perks/perk_G06/spriteFrame</x:v>
       </x:c>
@@ -1801,18 +2651,30 @@
       </x:c>
       <x:c r="H70" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I70" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J70" s="3" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K70" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L70" s="3" t="n">
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" t="n">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B71" t="str"/>
-      <x:c r="C71" t="str"/>
+      <x:c r="B71"/>
+      <x:c r="C71"/>
       <x:c r="D71" t="str">
         <x:v>perk_E01</x:v>
       </x:c>
-      <x:c r="E71" t="str"/>
+      <x:c r="E71"/>
       <x:c r="F71" t="str">
         <x:v>ui/icons/perks/perk_E01/spriteFrame</x:v>
       </x:c>
@@ -1821,18 +2683,30 @@
       </x:c>
       <x:c r="H71" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I71" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J71" s="3" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K71" s="3" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="L71" s="3" t="n">
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" t="n">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B72" t="str"/>
-      <x:c r="C72" t="str"/>
+      <x:c r="B72"/>
+      <x:c r="C72"/>
       <x:c r="D72" t="str">
         <x:v>perk_E02</x:v>
       </x:c>
-      <x:c r="E72" t="str"/>
+      <x:c r="E72"/>
       <x:c r="F72" t="str">
         <x:v>ui/icons/perks/perk_E02/spriteFrame</x:v>
       </x:c>
@@ -1841,18 +2715,30 @@
       </x:c>
       <x:c r="H72" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I72" s="3" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="J72" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K72" s="3" t="n">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="L72" s="3" t="n">
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" t="n">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="B73" t="str"/>
-      <x:c r="C73" t="str"/>
+      <x:c r="B73"/>
+      <x:c r="C73"/>
       <x:c r="D73" t="str">
         <x:v>perk_E03</x:v>
       </x:c>
-      <x:c r="E73" t="str"/>
+      <x:c r="E73"/>
       <x:c r="F73" t="str">
         <x:v>ui/icons/perks/perk_E03/spriteFrame</x:v>
       </x:c>
@@ -1861,18 +2747,30 @@
       </x:c>
       <x:c r="H73" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I73" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J73" s="3" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K73" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L73" s="3" t="n">
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" t="n">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="B74" t="str"/>
-      <x:c r="C74" t="str"/>
+      <x:c r="B74"/>
+      <x:c r="C74"/>
       <x:c r="D74" t="str">
         <x:v>perk_E04</x:v>
       </x:c>
-      <x:c r="E74" t="str"/>
+      <x:c r="E74"/>
       <x:c r="F74" t="str">
         <x:v>ui/icons/perks/perk_E04/spriteFrame</x:v>
       </x:c>
@@ -1881,18 +2779,30 @@
       </x:c>
       <x:c r="H74" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I74" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J74" s="3" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="K74" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L74" s="3" t="n">
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="B75" t="str"/>
-      <x:c r="C75" t="str"/>
+      <x:c r="B75"/>
+      <x:c r="C75"/>
       <x:c r="D75" t="str">
         <x:v>perk_E05</x:v>
       </x:c>
-      <x:c r="E75" t="str"/>
+      <x:c r="E75"/>
       <x:c r="F75" t="str">
         <x:v>ui/icons/perks/perk_E05/spriteFrame</x:v>
       </x:c>
@@ -1901,18 +2811,30 @@
       </x:c>
       <x:c r="H75" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I75" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J75" s="3" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K75" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L75" s="3" t="n">
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" t="n">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="B76" t="str"/>
-      <x:c r="C76" t="str"/>
+      <x:c r="B76"/>
+      <x:c r="C76"/>
       <x:c r="D76" t="str">
         <x:v>perk_E06</x:v>
       </x:c>
-      <x:c r="E76" t="str"/>
+      <x:c r="E76"/>
       <x:c r="F76" t="str">
         <x:v>ui/icons/perks/perk_E06/spriteFrame</x:v>
       </x:c>
@@ -1921,18 +2843,30 @@
       </x:c>
       <x:c r="H76" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I76" s="3" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J76" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K76" s="3" t="n">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="L76" s="3" t="n">
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" t="n">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B77" t="str"/>
-      <x:c r="C77" t="str"/>
+      <x:c r="B77"/>
+      <x:c r="C77"/>
       <x:c r="D77" t="str">
         <x:v>perk_X01</x:v>
       </x:c>
-      <x:c r="E77" t="str"/>
+      <x:c r="E77"/>
       <x:c r="F77" t="str">
         <x:v>ui/icons/perks/perk_X01/spriteFrame</x:v>
       </x:c>
@@ -1941,18 +2875,30 @@
       </x:c>
       <x:c r="H77" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I77" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J77" s="3" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K77" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L77" s="3" t="n">
+        <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" t="n">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="B78" t="str"/>
-      <x:c r="C78" t="str"/>
+      <x:c r="B78"/>
+      <x:c r="C78"/>
       <x:c r="D78" t="str">
         <x:v>perk_X02</x:v>
       </x:c>
-      <x:c r="E78" t="str"/>
+      <x:c r="E78"/>
       <x:c r="F78" t="str">
         <x:v>ui/icons/perks/perk_X02/spriteFrame</x:v>
       </x:c>
@@ -1961,18 +2907,30 @@
       </x:c>
       <x:c r="H78" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I78" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J78" s="3" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K78" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L78" s="3" t="n">
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" t="n">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="B79" t="str"/>
-      <x:c r="C79" t="str"/>
+      <x:c r="B79"/>
+      <x:c r="C79"/>
       <x:c r="D79" t="str">
         <x:v>perk_X03</x:v>
       </x:c>
-      <x:c r="E79" t="str"/>
+      <x:c r="E79"/>
       <x:c r="F79" t="str">
         <x:v>ui/icons/perks/perk_X03/spriteFrame</x:v>
       </x:c>
@@ -1981,18 +2939,30 @@
       </x:c>
       <x:c r="H79" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I79" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J79" s="3" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K79" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L79" s="3" t="n">
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" t="n">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B80" t="str"/>
-      <x:c r="C80" t="str"/>
+      <x:c r="B80"/>
+      <x:c r="C80"/>
       <x:c r="D80" t="str">
         <x:v>perk_X04</x:v>
       </x:c>
-      <x:c r="E80" t="str"/>
+      <x:c r="E80"/>
       <x:c r="F80" t="str">
         <x:v>ui/icons/perks/perk_X04/spriteFrame</x:v>
       </x:c>
@@ -2001,18 +2971,30 @@
       </x:c>
       <x:c r="H80" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I80" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J80" s="3" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K80" s="3" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="L80" s="3" t="n">
+        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" t="n">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="B81" t="str"/>
-      <x:c r="C81" t="str"/>
+      <x:c r="B81"/>
+      <x:c r="C81"/>
       <x:c r="D81" t="str">
         <x:v>perk_X05</x:v>
       </x:c>
-      <x:c r="E81" t="str"/>
+      <x:c r="E81"/>
       <x:c r="F81" t="str">
         <x:v>ui/icons/perks/perk_X05/spriteFrame</x:v>
       </x:c>
@@ -2021,18 +3003,30 @@
       </x:c>
       <x:c r="H81" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I81" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J81" s="3" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K81" s="3" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="L81" s="3" t="n">
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" t="n">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B82" t="str"/>
-      <x:c r="C82" t="str"/>
+      <x:c r="B82"/>
+      <x:c r="C82"/>
       <x:c r="D82" t="str">
         <x:v>perk_X06</x:v>
       </x:c>
-      <x:c r="E82" t="str"/>
+      <x:c r="E82"/>
       <x:c r="F82" t="str">
         <x:v>ui/icons/perks/perk_X06/spriteFrame</x:v>
       </x:c>
@@ -2041,18 +3035,30 @@
       </x:c>
       <x:c r="H82" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I82" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J82" s="3" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K82" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L82" s="3" t="n">
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B83" t="str"/>
-      <x:c r="C83" t="str"/>
+      <x:c r="B83"/>
+      <x:c r="C83"/>
       <x:c r="D83" t="str">
         <x:v>perk_F01</x:v>
       </x:c>
-      <x:c r="E83" t="str"/>
+      <x:c r="E83"/>
       <x:c r="F83" t="str">
         <x:v>ui/icons/perks/perk_F01/spriteFrame</x:v>
       </x:c>
@@ -2061,18 +3067,30 @@
       </x:c>
       <x:c r="H83" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I83" s="3" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J83" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K83" s="3" t="n">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="L83" s="3" t="n">
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" t="n">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="B84" t="str"/>
-      <x:c r="C84" t="str"/>
+      <x:c r="B84"/>
+      <x:c r="C84"/>
       <x:c r="D84" t="str">
         <x:v>perk_F02</x:v>
       </x:c>
-      <x:c r="E84" t="str"/>
+      <x:c r="E84"/>
       <x:c r="F84" t="str">
         <x:v>ui/icons/perks/perk_F02/spriteFrame</x:v>
       </x:c>
@@ -2081,18 +3099,30 @@
       </x:c>
       <x:c r="H84" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I84" s="3" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="J84" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K84" s="3" t="n">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="L84" s="3" t="n">
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B85" t="str"/>
-      <x:c r="C85" t="str"/>
+      <x:c r="B85"/>
+      <x:c r="C85"/>
       <x:c r="D85" t="str">
         <x:v>perk_F03</x:v>
       </x:c>
-      <x:c r="E85" t="str"/>
+      <x:c r="E85"/>
       <x:c r="F85" t="str">
         <x:v>ui/icons/perks/perk_F03/spriteFrame</x:v>
       </x:c>
@@ -2101,18 +3131,30 @@
       </x:c>
       <x:c r="H85" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I85" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J85" s="3" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="K85" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L85" s="3" t="n">
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" t="n">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="B86" t="str"/>
-      <x:c r="C86" t="str"/>
+      <x:c r="B86"/>
+      <x:c r="C86"/>
       <x:c r="D86" t="str">
         <x:v>perk_F04</x:v>
       </x:c>
-      <x:c r="E86" t="str"/>
+      <x:c r="E86"/>
       <x:c r="F86" t="str">
         <x:v>ui/icons/perks/perk_F04/spriteFrame</x:v>
       </x:c>
@@ -2121,18 +3163,30 @@
       </x:c>
       <x:c r="H86" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I86" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J86" s="3" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K86" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L86" s="3" t="n">
+        <x:v>193</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" t="n">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="B87" t="str"/>
-      <x:c r="C87" t="str"/>
+      <x:c r="B87"/>
+      <x:c r="C87"/>
       <x:c r="D87" t="str">
         <x:v>perk_F05</x:v>
       </x:c>
-      <x:c r="E87" t="str"/>
+      <x:c r="E87"/>
       <x:c r="F87" t="str">
         <x:v>ui/icons/perks/perk_F05/spriteFrame</x:v>
       </x:c>
@@ -2141,18 +3195,30 @@
       </x:c>
       <x:c r="H87" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I87" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J87" s="3" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K87" s="3" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="L87" s="3" t="n">
+        <x:v>209</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" t="n">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="B88" t="str"/>
-      <x:c r="C88" t="str"/>
+      <x:c r="B88"/>
+      <x:c r="C88"/>
       <x:c r="D88" t="str">
         <x:v>perk_F06</x:v>
       </x:c>
-      <x:c r="E88" t="str"/>
+      <x:c r="E88"/>
       <x:c r="F88" t="str">
         <x:v>ui/icons/perks/perk_F06/spriteFrame</x:v>
       </x:c>
@@ -2161,6 +3227,18 @@
       </x:c>
       <x:c r="H88" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I88" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J88" s="3" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="K88" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L88" s="3" t="n">
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -2176,7 +3254,7 @@
       <x:c r="D89" t="str">
         <x:v>sprout_level2</x:v>
       </x:c>
-      <x:c r="E89" t="str"/>
+      <x:c r="E89"/>
       <x:c r="F89" t="str">
         <x:v>gameplay/towers/characters/sprout_level2/spriteFrame</x:v>
       </x:c>
@@ -2185,6 +3263,18 @@
       </x:c>
       <x:c r="H89" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I89" s="3" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J89" s="3" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K89" s="3" t="n">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="L89" s="3" t="n">
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -2200,7 +3290,7 @@
       <x:c r="D90" t="str">
         <x:v>frost_level2</x:v>
       </x:c>
-      <x:c r="E90" t="str"/>
+      <x:c r="E90"/>
       <x:c r="F90" t="str">
         <x:v>gameplay/towers/characters/frost_level2/spriteFrame</x:v>
       </x:c>
@@ -2209,6 +3299,18 @@
       </x:c>
       <x:c r="H90" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I90" s="3" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J90" s="3" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K90" s="3" t="n">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="L90" s="3" t="n">
+        <x:v>213</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -2224,7 +3326,7 @@
       <x:c r="D91" t="str">
         <x:v>bloom_level2</x:v>
       </x:c>
-      <x:c r="E91" t="str"/>
+      <x:c r="E91"/>
       <x:c r="F91" t="str">
         <x:v>gameplay/towers/characters/bloom_level2/spriteFrame</x:v>
       </x:c>
@@ -2233,6 +3335,18 @@
       </x:c>
       <x:c r="H91" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I91" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J91" s="3" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K91" s="3" t="n">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="L91" s="3" t="n">
+        <x:v>223</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -2248,7 +3362,7 @@
       <x:c r="D92" t="str">
         <x:v>scope_level2</x:v>
       </x:c>
-      <x:c r="E92" t="str"/>
+      <x:c r="E92"/>
       <x:c r="F92" t="str">
         <x:v>gameplay/towers/characters/scope_level2/spriteFrame</x:v>
       </x:c>
@@ -2257,6 +3371,18 @@
       </x:c>
       <x:c r="H92" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I92" s="3" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J92" s="3" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="K92" s="3" t="n">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="L92" s="3" t="n">
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -2272,7 +3398,7 @@
       <x:c r="D93" t="str">
         <x:v>spark_level2</x:v>
       </x:c>
-      <x:c r="E93" t="str"/>
+      <x:c r="E93"/>
       <x:c r="F93" t="str">
         <x:v>gameplay/towers/characters/spark_level2/spriteFrame</x:v>
       </x:c>
@@ -2281,6 +3407,18 @@
       </x:c>
       <x:c r="H93" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I93" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J93" s="3" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K93" s="3" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="L93" s="3" t="n">
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -2296,7 +3434,7 @@
       <x:c r="D94" t="str">
         <x:v>ember_level2</x:v>
       </x:c>
-      <x:c r="E94" t="str"/>
+      <x:c r="E94"/>
       <x:c r="F94" t="str">
         <x:v>gameplay/towers/characters/ember_level2/spriteFrame</x:v>
       </x:c>
@@ -2305,6 +3443,18 @@
       </x:c>
       <x:c r="H94" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I94" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J94" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K94" s="3" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L94" s="3" t="n">
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -2320,7 +3470,7 @@
       <x:c r="D95" t="str">
         <x:v>mint_level2</x:v>
       </x:c>
-      <x:c r="E95" t="str"/>
+      <x:c r="E95"/>
       <x:c r="F95" t="str">
         <x:v>gameplay/towers/characters/mint_level2/spriteFrame</x:v>
       </x:c>
@@ -2329,6 +3479,18 @@
       </x:c>
       <x:c r="H95" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I95" s="3" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J95" s="3" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K95" s="3" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="L95" s="3" t="n">
+        <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -2344,7 +3506,7 @@
       <x:c r="D96" t="str">
         <x:v>fan_level2</x:v>
       </x:c>
-      <x:c r="E96" t="str"/>
+      <x:c r="E96"/>
       <x:c r="F96" t="str">
         <x:v>gameplay/towers/characters/fan_level2/spriteFrame</x:v>
       </x:c>
@@ -2353,6 +3515,18 @@
       </x:c>
       <x:c r="H96" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I96" s="3" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J96" s="3" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="K96" s="3" t="n">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="L96" s="3" t="n">
+        <x:v>213</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -2365,8 +3539,8 @@
       <x:c r="C97" t="str">
         <x:v>enemy_puff</x:v>
       </x:c>
-      <x:c r="D97" t="str"/>
-      <x:c r="E97" t="str"/>
+      <x:c r="D97"/>
+      <x:c r="E97"/>
       <x:c r="F97" t="str">
         <x:v>gameplay/enemies/characters/enemy_puff/spriteFrame</x:v>
       </x:c>
@@ -2375,6 +3549,18 @@
       </x:c>
       <x:c r="H97" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I97" s="3" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J97" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K97" s="3" t="n">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="L97" s="3" t="n">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -2387,8 +3573,8 @@
       <x:c r="C98" t="str">
         <x:v>enemy_pudding</x:v>
       </x:c>
-      <x:c r="D98" t="str"/>
-      <x:c r="E98" t="str"/>
+      <x:c r="D98"/>
+      <x:c r="E98"/>
       <x:c r="F98" t="str">
         <x:v>gameplay/enemies/characters/enemy_pudding/spriteFrame</x:v>
       </x:c>
@@ -2397,6 +3583,18 @@
       </x:c>
       <x:c r="H98" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I98" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J98" s="3" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K98" s="3" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L98" s="3" t="n">
+        <x:v>223</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -2409,8 +3607,8 @@
       <x:c r="C99" t="str">
         <x:v>enemy_biscuit</x:v>
       </x:c>
-      <x:c r="D99" t="str"/>
-      <x:c r="E99" t="str"/>
+      <x:c r="D99"/>
+      <x:c r="E99"/>
       <x:c r="F99" t="str">
         <x:v>gameplay/enemies/characters/enemy_biscuit/spriteFrame</x:v>
       </x:c>
@@ -2419,6 +3617,18 @@
       </x:c>
       <x:c r="H99" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I99" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J99" s="3" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K99" s="3" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L99" s="3" t="n">
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -2431,8 +3641,8 @@
       <x:c r="C100" t="str">
         <x:v>enemy_soda</x:v>
       </x:c>
-      <x:c r="D100" t="str"/>
-      <x:c r="E100" t="str"/>
+      <x:c r="D100"/>
+      <x:c r="E100"/>
       <x:c r="F100" t="str">
         <x:v>gameplay/enemies/characters/enemy_soda/spriteFrame</x:v>
       </x:c>
@@ -2441,6 +3651,18 @@
       </x:c>
       <x:c r="H100" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I100" s="3" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="J100" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K100" s="3" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="L100" s="3" t="n">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -2453,8 +3675,8 @@
       <x:c r="C101" t="str">
         <x:v>enemy_coffee</x:v>
       </x:c>
-      <x:c r="D101" t="str"/>
-      <x:c r="E101" t="str"/>
+      <x:c r="D101"/>
+      <x:c r="E101"/>
       <x:c r="F101" t="str">
         <x:v>gameplay/enemies/characters/enemy_coffee/spriteFrame</x:v>
       </x:c>
@@ -2463,6 +3685,18 @@
       </x:c>
       <x:c r="H101" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I101" s="3" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="J101" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K101" s="3" t="n">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="L101" s="3" t="n">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -2475,8 +3709,8 @@
       <x:c r="C102" t="str">
         <x:v>enemy_tea</x:v>
       </x:c>
-      <x:c r="D102" t="str"/>
-      <x:c r="E102" t="str"/>
+      <x:c r="D102"/>
+      <x:c r="E102"/>
       <x:c r="F102" t="str">
         <x:v>gameplay/enemies/characters/enemy_tea/spriteFrame</x:v>
       </x:c>
@@ -2485,6 +3719,18 @@
       </x:c>
       <x:c r="H102" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I102" s="3" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="J102" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K102" s="3" t="n">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="L102" s="3" t="n">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -2497,8 +3743,8 @@
       <x:c r="C103" t="str">
         <x:v>enemy_berrymilk</x:v>
       </x:c>
-      <x:c r="D103" t="str"/>
-      <x:c r="E103" t="str"/>
+      <x:c r="D103"/>
+      <x:c r="E103"/>
       <x:c r="F103" t="str">
         <x:v>gameplay/enemies/characters/enemy_berrymilk/spriteFrame</x:v>
       </x:c>
@@ -2507,6 +3753,18 @@
       </x:c>
       <x:c r="H103" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I103" s="3" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J103" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K103" s="3" t="n">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="L103" s="3" t="n">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -2519,8 +3777,8 @@
       <x:c r="C104" t="str">
         <x:v>enemy_tin</x:v>
       </x:c>
-      <x:c r="D104" t="str"/>
-      <x:c r="E104" t="str"/>
+      <x:c r="D104"/>
+      <x:c r="E104"/>
       <x:c r="F104" t="str">
         <x:v>gameplay/enemies/characters/enemy_tin/spriteFrame</x:v>
       </x:c>
@@ -2529,6 +3787,18 @@
       </x:c>
       <x:c r="H104" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I104" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J104" s="3" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="K104" s="3" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L104" s="3" t="n">
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -2541,8 +3811,8 @@
       <x:c r="C105" t="str">
         <x:v>enemy_juice</x:v>
       </x:c>
-      <x:c r="D105" t="str"/>
-      <x:c r="E105" t="str"/>
+      <x:c r="D105"/>
+      <x:c r="E105"/>
       <x:c r="F105" t="str">
         <x:v>gameplay/enemies/characters/enemy_juice/spriteFrame</x:v>
       </x:c>
@@ -2551,6 +3821,18 @@
       </x:c>
       <x:c r="H105" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I105" s="3" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="J105" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K105" s="3" t="n">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="L105" s="3" t="n">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -2563,8 +3845,8 @@
       <x:c r="C106" t="str">
         <x:v>enemy_peach</x:v>
       </x:c>
-      <x:c r="D106" t="str"/>
-      <x:c r="E106" t="str"/>
+      <x:c r="D106"/>
+      <x:c r="E106"/>
       <x:c r="F106" t="str">
         <x:v>gameplay/enemies/characters/enemy_peach/spriteFrame</x:v>
       </x:c>
@@ -2573,6 +3855,18 @@
       </x:c>
       <x:c r="H106" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I106" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J106" s="3" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K106" s="3" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L106" s="3" t="n">
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
@@ -2585,8 +3879,8 @@
       <x:c r="C107" t="str">
         <x:v>enemy_grape</x:v>
       </x:c>
-      <x:c r="D107" t="str"/>
-      <x:c r="E107" t="str"/>
+      <x:c r="D107"/>
+      <x:c r="E107"/>
       <x:c r="F107" t="str">
         <x:v>gameplay/enemies/characters/enemy_grape/spriteFrame</x:v>
       </x:c>
@@ -2595,6 +3889,18 @@
       </x:c>
       <x:c r="H107" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I107" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J107" s="3" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K107" s="3" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L107" s="3" t="n">
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -2607,8 +3913,8 @@
       <x:c r="C108" t="str">
         <x:v>enemy_blue</x:v>
       </x:c>
-      <x:c r="D108" t="str"/>
-      <x:c r="E108" t="str"/>
+      <x:c r="D108"/>
+      <x:c r="E108"/>
       <x:c r="F108" t="str">
         <x:v>gameplay/enemies/characters/enemy_blue/spriteFrame</x:v>
       </x:c>
@@ -2617,6 +3923,18 @@
       </x:c>
       <x:c r="H108" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I108" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J108" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K108" s="3" t="n">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="L108" s="3" t="n">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -2629,8 +3947,8 @@
       <x:c r="C109" t="str">
         <x:v>enemy_ricebox</x:v>
       </x:c>
-      <x:c r="D109" t="str"/>
-      <x:c r="E109" t="str"/>
+      <x:c r="D109"/>
+      <x:c r="E109"/>
       <x:c r="F109" t="str">
         <x:v>gameplay/enemies/characters/enemy_ricebox/spriteFrame</x:v>
       </x:c>
@@ -2639,6 +3957,18 @@
       </x:c>
       <x:c r="H109" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I109" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J109" s="3" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K109" s="3" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L109" s="3" t="n">
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -2651,8 +3981,8 @@
       <x:c r="C110" t="str">
         <x:v>enemy_deliverybag</x:v>
       </x:c>
-      <x:c r="D110" t="str"/>
-      <x:c r="E110" t="str"/>
+      <x:c r="D110"/>
+      <x:c r="E110"/>
       <x:c r="F110" t="str">
         <x:v>gameplay/enemies/characters/enemy_deliverybag/spriteFrame</x:v>
       </x:c>
@@ -2661,18 +3991,30 @@
       </x:c>
       <x:c r="H110" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I110" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J110" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K110" s="3" t="n">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="L110" s="3" t="n">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
       <x:c r="A111" t="n">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="B111" t="str"/>
-      <x:c r="C111" t="str"/>
+      <x:c r="B111"/>
+      <x:c r="C111"/>
       <x:c r="D111" t="str">
         <x:v>perk_R01</x:v>
       </x:c>
-      <x:c r="E111" t="str"/>
+      <x:c r="E111"/>
       <x:c r="F111" t="str">
         <x:v>ui/icons/perks/perk_E01/spriteFrame</x:v>
       </x:c>
@@ -2681,18 +4023,30 @@
       </x:c>
       <x:c r="H111" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I111" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J111" s="3" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K111" s="3" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="L111" s="3" t="n">
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
       <x:c r="A112" t="n">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="B112" t="str"/>
-      <x:c r="C112" t="str"/>
+      <x:c r="B112"/>
+      <x:c r="C112"/>
       <x:c r="D112" t="str">
         <x:v>perk_R02</x:v>
       </x:c>
-      <x:c r="E112" t="str"/>
+      <x:c r="E112"/>
       <x:c r="F112" t="str">
         <x:v>ui/icons/perks/perk_S02/spriteFrame</x:v>
       </x:c>
@@ -2701,18 +4055,30 @@
       </x:c>
       <x:c r="H112" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I112" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J112" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K112" s="3" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="L112" s="3" t="n">
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
       <x:c r="A113" t="n">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="B113" t="str"/>
-      <x:c r="C113" t="str"/>
+      <x:c r="B113"/>
+      <x:c r="C113"/>
       <x:c r="D113" t="str">
         <x:v>perk_R03</x:v>
       </x:c>
-      <x:c r="E113" t="str"/>
+      <x:c r="E113"/>
       <x:c r="F113" t="str">
         <x:v>ui/icons/perks/perk_X02/spriteFrame</x:v>
       </x:c>
@@ -2721,6 +4087,18 @@
       </x:c>
       <x:c r="H113" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I113" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J113" s="3" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K113" s="3" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L113" s="3" t="n">
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -2733,8 +4111,8 @@
       <x:c r="C114" t="str">
         <x:v>enemy_mochi</x:v>
       </x:c>
-      <x:c r="D114" t="str"/>
-      <x:c r="E114" t="str"/>
+      <x:c r="D114"/>
+      <x:c r="E114"/>
       <x:c r="F114" t="str">
         <x:v>gameplay/enemies/characters/enemy_mochi/spriteFrame</x:v>
       </x:c>
@@ -2743,6 +4121,18 @@
       </x:c>
       <x:c r="H114" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I114" s="3" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J114" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K114" s="3" t="n">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="L114" s="3" t="n">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -2755,8 +4145,8 @@
       <x:c r="C115" t="str">
         <x:v>enemy_popcorn</x:v>
       </x:c>
-      <x:c r="D115" t="str"/>
-      <x:c r="E115" t="str"/>
+      <x:c r="D115"/>
+      <x:c r="E115"/>
       <x:c r="F115" t="str">
         <x:v>gameplay/enemies/characters/enemy_popcorn/spriteFrame</x:v>
       </x:c>
@@ -2765,6 +4155,18 @@
       </x:c>
       <x:c r="H115" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I115" s="3" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J115" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K115" s="3" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L115" s="3" t="n">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -2777,8 +4179,8 @@
       <x:c r="C116" t="str">
         <x:v>enemy_noodlecup</x:v>
       </x:c>
-      <x:c r="D116" t="str"/>
-      <x:c r="E116" t="str"/>
+      <x:c r="D116"/>
+      <x:c r="E116"/>
       <x:c r="F116" t="str">
         <x:v>gameplay/enemies/characters/enemy_noodlecup/spriteFrame</x:v>
       </x:c>
@@ -2787,6 +4189,18 @@
       </x:c>
       <x:c r="H116" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I116" s="3" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J116" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K116" s="3" t="n">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="L116" s="3" t="n">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -2799,8 +4213,8 @@
       <x:c r="C117" t="str">
         <x:v>enemy_frostdonut</x:v>
       </x:c>
-      <x:c r="D117" t="str"/>
-      <x:c r="E117" t="str"/>
+      <x:c r="D117"/>
+      <x:c r="E117"/>
       <x:c r="F117" t="str">
         <x:v>gameplay/enemies/characters/enemy_frostdonut/spriteFrame</x:v>
       </x:c>
@@ -2809,6 +4223,18 @@
       </x:c>
       <x:c r="H117" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I117" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J117" s="3" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K117" s="3" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L117" s="3" t="n">
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -2821,8 +4247,8 @@
       <x:c r="C118" t="str">
         <x:v>enemy_freezer</x:v>
       </x:c>
-      <x:c r="D118" t="str"/>
-      <x:c r="E118" t="str"/>
+      <x:c r="D118"/>
+      <x:c r="E118"/>
       <x:c r="F118" t="str">
         <x:v>gameplay/enemies/characters/enemy_freezer/spriteFrame</x:v>
       </x:c>
@@ -2831,6 +4257,18 @@
       </x:c>
       <x:c r="H118" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I118" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J118" s="3" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K118" s="3" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L118" s="3" t="n">
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -2843,8 +4281,8 @@
       <x:c r="C119" t="str">
         <x:v>enemy_vending</x:v>
       </x:c>
-      <x:c r="D119" t="str"/>
-      <x:c r="E119" t="str"/>
+      <x:c r="D119"/>
+      <x:c r="E119"/>
       <x:c r="F119" t="str">
         <x:v>gameplay/enemies/characters/enemy_vending/spriteFrame</x:v>
       </x:c>
@@ -2853,18 +4291,30 @@
       </x:c>
       <x:c r="H119" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I119" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J119" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K119" s="3" t="n">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="L119" s="3" t="n">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
       <x:c r="A120" t="n">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="B120" t="str"/>
-      <x:c r="C120" t="str"/>
+      <x:c r="B120"/>
+      <x:c r="C120"/>
       <x:c r="D120" t="str">
         <x:v>tech_boss</x:v>
       </x:c>
-      <x:c r="E120" t="str"/>
+      <x:c r="E120"/>
       <x:c r="F120" t="str">
         <x:v>ui/windows/technology/tech_boss/spriteFrame</x:v>
       </x:c>
@@ -2873,18 +4323,30 @@
       </x:c>
       <x:c r="H120" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I120" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J120" s="3" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K120" s="3" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L120" s="3" t="n">
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="121">
       <x:c r="A121" t="n">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="B121" t="str"/>
-      <x:c r="C121" t="str"/>
+      <x:c r="B121"/>
+      <x:c r="C121"/>
       <x:c r="D121" t="str">
         <x:v>tech_clear</x:v>
       </x:c>
-      <x:c r="E121" t="str"/>
+      <x:c r="E121"/>
       <x:c r="F121" t="str">
         <x:v>ui/windows/technology/tech_clear/spriteFrame</x:v>
       </x:c>
@@ -2893,18 +4355,30 @@
       </x:c>
       <x:c r="H121" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I121" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J121" s="3" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K121" s="3" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L121" s="3" t="n">
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="122">
       <x:c r="A122" t="n">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="B122" t="str"/>
-      <x:c r="C122" t="str"/>
+      <x:c r="B122"/>
+      <x:c r="C122"/>
       <x:c r="D122" t="str">
         <x:v>tech_recycle</x:v>
       </x:c>
-      <x:c r="E122" t="str"/>
+      <x:c r="E122"/>
       <x:c r="F122" t="str">
         <x:v>ui/windows/technology/tech_recycle/spriteFrame</x:v>
       </x:c>
@@ -2913,18 +4387,30 @@
       </x:c>
       <x:c r="H122" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I122" s="3" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J122" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K122" s="3" t="n">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="L122" s="3" t="n">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
       <x:c r="A123" t="n">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="B123" t="str"/>
-      <x:c r="C123" t="str"/>
+      <x:c r="B123"/>
+      <x:c r="C123"/>
       <x:c r="D123" t="str">
         <x:v>tech_supply</x:v>
       </x:c>
-      <x:c r="E123" t="str"/>
+      <x:c r="E123"/>
       <x:c r="F123" t="str">
         <x:v>ui/windows/technology/tech_supply/spriteFrame</x:v>
       </x:c>
@@ -2933,6 +4419,18 @@
       </x:c>
       <x:c r="H123" t="n">
         <x:v>256</x:v>
+      </x:c>
+      <x:c r="I123" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J123" s="3" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K123" s="3" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L123" s="3" t="n">
+        <x:v>200</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
